--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="373">
   <si>
     <t>pH</t>
   </si>
@@ -220,9 +220,6 @@
     <t>9c</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Household deep cove</t>
   </si>
   <si>
@@ -274,9 +271,6 @@
     <t>Fiberglass</t>
   </si>
   <si>
-    <t>I don't know</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -304,57 +298,33 @@
     <t>Technician/Mason</t>
   </si>
   <si>
-    <t>Don't know - bought house less than 6 years ago</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leach field - second tank is aerated </t>
   </si>
   <si>
     <t>Bleach, CLR</t>
   </si>
   <si>
-    <t>Every 15 years</t>
-  </si>
-  <si>
-    <t>Na</t>
-  </si>
-  <si>
     <t xml:space="preserve">Drainage field </t>
   </si>
   <si>
     <t>Kitchen Laundry Bathing Toilet</t>
   </si>
   <si>
-    <t xml:space="preserve">5 years </t>
-  </si>
-  <si>
     <t>Concrete</t>
   </si>
   <si>
     <t>Leach field</t>
   </si>
   <si>
-    <t xml:space="preserve">Na </t>
-  </si>
-  <si>
     <t>Toilet Bathing</t>
   </si>
   <si>
-    <t xml:space="preserve">I don't know </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 ish years </t>
-  </si>
-  <si>
     <t xml:space="preserve">Leach field </t>
   </si>
   <si>
     <t>Paper Water</t>
   </si>
   <si>
-    <t xml:space="preserve">Every 5 years </t>
-  </si>
-  <si>
     <t xml:space="preserve">Leech field </t>
   </si>
   <si>
@@ -367,18 +337,12 @@
     <t>Leech field</t>
   </si>
   <si>
-    <t>Every ten years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bionest treatment plant </t>
   </si>
   <si>
     <t>Toilet</t>
   </si>
   <si>
-    <t>Twice per year</t>
-  </si>
-  <si>
     <t xml:space="preserve">Treatment plant </t>
   </si>
   <si>
@@ -391,57 +355,33 @@
     <t xml:space="preserve">Septonic </t>
   </si>
   <si>
-    <t>5 years</t>
-  </si>
-  <si>
     <t>1 2oz pack every 3-4 months</t>
   </si>
   <si>
     <t xml:space="preserve">Pro-pump septic packets </t>
   </si>
   <si>
-    <t>5-6 years</t>
-  </si>
-  <si>
     <t>Leach</t>
   </si>
   <si>
     <t xml:space="preserve">Regular cleaners </t>
   </si>
   <si>
-    <t xml:space="preserve">5-6 years </t>
-  </si>
-  <si>
     <t>Toilet Kitchen</t>
   </si>
   <si>
-    <t>5-7 years</t>
-  </si>
-  <si>
     <t>PVC or plastic</t>
   </si>
   <si>
-    <t>3-5 years</t>
-  </si>
-  <si>
     <t xml:space="preserve">Regular household cleaners </t>
   </si>
   <si>
-    <t xml:space="preserve">Every 2-3 years </t>
-  </si>
-  <si>
     <t>Rent</t>
   </si>
   <si>
     <t>Water</t>
   </si>
   <si>
-    <t>9-10 years</t>
-  </si>
-  <si>
-    <t>Every 5 years</t>
-  </si>
-  <si>
     <t>Toilet Laundry Kitchen</t>
   </si>
   <si>
@@ -967,34 +907,7 @@
     <t>1 - 5 years old</t>
   </si>
   <si>
-    <t>Every two years</t>
-  </si>
-  <si>
-    <t>Every 2 years</t>
-  </si>
-  <si>
-    <t>1 every two years</t>
-  </si>
-  <si>
     <t>System has never been emptied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Just new </t>
-  </si>
-  <si>
-    <t>Every 4 months</t>
-  </si>
-  <si>
-    <t>1 in every 6 years</t>
-  </si>
-  <si>
-    <t>Once a year</t>
-  </si>
-  <si>
-    <t>Every 5 months</t>
-  </si>
-  <si>
-    <t>3 times a year</t>
   </si>
   <si>
     <t>Feminine products, condoms, plastic, etc.</t>
@@ -1745,127 +1658,127 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="U1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="V1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="W1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="X1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="Y1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="Z1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.35">
@@ -1891,100 +1804,91 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>74</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>75</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>76</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" t="s">
         <v>77</v>
       </c>
-      <c r="M2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" t="s">
         <v>79</v>
       </c>
-      <c r="P2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>81</v>
-      </c>
       <c r="R2" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" s="12">
+        <v>1</v>
+      </c>
+      <c r="T2" s="12">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" t="s">
+        <v>87</v>
+      </c>
+      <c r="X2" t="s">
         <v>82</v>
       </c>
-      <c r="S2" s="12">
-        <v>1</v>
-      </c>
-      <c r="T2" s="12">
-        <v>0</v>
-      </c>
-      <c r="U2" t="s">
-        <v>73</v>
-      </c>
-      <c r="W2" t="s">
-        <v>90</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD2" t="s">
+      <c r="AH2" t="s">
         <v>85</v>
       </c>
-      <c r="AE2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>91</v>
+        <v>77</v>
+      </c>
+      <c r="AK2">
+        <v>15</v>
       </c>
       <c r="AL2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO2" t="s">
         <v>14</v>
@@ -2013,103 +1917,91 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" t="s">
         <v>74</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>75</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>76</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" t="s">
         <v>77</v>
       </c>
-      <c r="M3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>78</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>79</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>80</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" s="12">
+        <v>1</v>
+      </c>
+      <c r="T3" s="12">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" t="s">
         <v>81</v>
       </c>
-      <c r="R3" t="s">
+      <c r="X3" t="s">
         <v>82</v>
       </c>
-      <c r="S3" s="12">
-        <v>1</v>
-      </c>
-      <c r="T3" s="12">
-        <v>0</v>
-      </c>
-      <c r="U3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="Y3" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD3" t="s">
         <v>83</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AE3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="s">
         <v>84</v>
       </c>
-      <c r="Y3" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD3" t="s">
+      <c r="AH3" t="s">
         <v>85</v>
       </c>
-      <c r="AE3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AL3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="AO3" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.35">
@@ -2135,100 +2027,85 @@
         <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" t="s">
+        <v>77</v>
+      </c>
+      <c r="P4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K4" t="s">
-        <v>78</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="R4" t="s">
+        <v>80</v>
+      </c>
+      <c r="S4" s="12">
+        <v>1</v>
+      </c>
+      <c r="T4" s="12">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>72</v>
+      </c>
+      <c r="X4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y4" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="s">
         <v>77</v>
       </c>
-      <c r="M4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N4" t="s">
-        <v>78</v>
-      </c>
-      <c r="O4" t="s">
-        <v>79</v>
-      </c>
-      <c r="P4" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>81</v>
-      </c>
-      <c r="R4" t="s">
-        <v>82</v>
-      </c>
-      <c r="S4" s="12">
-        <v>1</v>
-      </c>
-      <c r="T4" s="12">
-        <v>0</v>
-      </c>
-      <c r="U4" t="s">
-        <v>73</v>
-      </c>
-      <c r="W4" t="s">
-        <v>60</v>
-      </c>
-      <c r="X4" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y4" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>79</v>
-      </c>
       <c r="AD4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH4" t="s">
         <v>85</v>
       </c>
-      <c r="AE4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>95</v>
+        <v>77</v>
+      </c>
+      <c r="AK4">
+        <v>5</v>
       </c>
       <c r="AL4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM4" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO4" t="s">
         <v>15</v>
@@ -2257,37 +2134,37 @@
         <v>6</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q5" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L5" t="s">
-        <v>96</v>
-      </c>
-      <c r="M5" t="s">
-        <v>73</v>
-      </c>
-      <c r="N5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" t="s">
-        <v>79</v>
-      </c>
-      <c r="P5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>81</v>
-      </c>
       <c r="R5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S5" s="12">
         <v>1</v>
@@ -2296,13 +2173,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="s">
-        <v>73</v>
-      </c>
-      <c r="W5" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="X5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Y5" s="12">
         <v>1</v>
@@ -2317,40 +2191,34 @@
         <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE5" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH5" t="s">
         <v>85</v>
       </c>
-      <c r="AE5" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>100</v>
-      </c>
       <c r="AJ5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>101</v>
+        <v>77</v>
+      </c>
+      <c r="AK5">
+        <v>6</v>
       </c>
       <c r="AL5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM5" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO5" t="s">
         <v>16</v>
@@ -2367,7 +2235,7 @@
         <v>45035</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -2379,37 +2247,37 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" t="s">
         <v>74</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>75</v>
       </c>
-      <c r="K6" t="s">
-        <v>76</v>
-      </c>
       <c r="L6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N6" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" t="s">
+        <v>77</v>
+      </c>
+      <c r="P6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" t="s">
         <v>79</v>
       </c>
-      <c r="O6" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>81</v>
-      </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S6" s="12">
         <v>1</v>
@@ -2418,61 +2286,52 @@
         <v>1</v>
       </c>
       <c r="U6" t="s">
-        <v>73</v>
-      </c>
-      <c r="W6" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y6" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="s">
         <v>84</v>
       </c>
-      <c r="Y6" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AH6" t="s">
         <v>85</v>
       </c>
-      <c r="AE6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>100</v>
-      </c>
       <c r="AJ6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>104</v>
+        <v>77</v>
+      </c>
+      <c r="AK6">
+        <v>5</v>
       </c>
       <c r="AL6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO6" t="s">
         <v>25</v>
@@ -2489,10 +2348,10 @@
         <v>45035</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F7" s="6">
         <f>410</f>
@@ -2502,38 +2361,34 @@
         <f>1/12</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
       <c r="J7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s">
         <v>75</v>
       </c>
-      <c r="K7" t="s">
-        <v>76</v>
-      </c>
       <c r="L7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q7" t="s">
         <v>79</v>
       </c>
-      <c r="O7" t="s">
-        <v>79</v>
-      </c>
-      <c r="P7" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>81</v>
-      </c>
       <c r="R7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S7" s="12">
         <v>1</v>
@@ -2542,13 +2397,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="s">
-        <v>73</v>
-      </c>
-      <c r="W7" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X7" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="Y7" s="12">
         <v>1</v>
@@ -2563,10 +2415,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AE7" s="12">
         <v>1</v>
@@ -2575,31 +2427,25 @@
         <v>0</v>
       </c>
       <c r="AG7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>112</v>
+        <v>77</v>
+      </c>
+      <c r="AK7">
+        <v>0.5</v>
       </c>
       <c r="AL7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO7" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.35">
@@ -2625,100 +2471,94 @@
         <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" t="s">
         <v>74</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>75</v>
       </c>
-      <c r="K8" t="s">
-        <v>76</v>
-      </c>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N8" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q8" t="s">
         <v>79</v>
       </c>
-      <c r="O8" t="s">
-        <v>79</v>
-      </c>
-      <c r="P8" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>81</v>
-      </c>
       <c r="R8" t="s">
+        <v>80</v>
+      </c>
+      <c r="S8" s="12">
+        <v>1</v>
+      </c>
+      <c r="T8" s="12">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>72</v>
+      </c>
+      <c r="X8" t="s">
         <v>82</v>
       </c>
-      <c r="S8" s="12">
-        <v>1</v>
-      </c>
-      <c r="T8" s="12">
-        <v>0</v>
-      </c>
-      <c r="U8" t="s">
-        <v>73</v>
-      </c>
-      <c r="W8" t="s">
-        <v>92</v>
-      </c>
-      <c r="X8" t="s">
+      <c r="Y8" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="s">
         <v>84</v>
       </c>
-      <c r="Y8" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD8" t="s">
+      <c r="AH8" t="s">
         <v>85</v>
-      </c>
-      <c r="AE8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>87</v>
       </c>
       <c r="AI8">
         <v>4.5</v>
       </c>
       <c r="AJ8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>109</v>
+        <v>77</v>
+      </c>
+      <c r="AK8">
+        <v>10</v>
       </c>
       <c r="AL8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO8" t="s">
         <v>26</v>
@@ -2747,53 +2587,50 @@
         <v>8</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" t="s">
         <v>74</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>75</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>76</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" t="s">
         <v>77</v>
       </c>
-      <c r="M9" t="s">
-        <v>73</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q9" t="s">
         <v>79</v>
       </c>
-      <c r="O9" t="s">
-        <v>79</v>
-      </c>
-      <c r="P9" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>81</v>
-      </c>
       <c r="R9" t="s">
+        <v>80</v>
+      </c>
+      <c r="S9" s="12">
+        <v>1</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>72</v>
+      </c>
+      <c r="X9" t="s">
         <v>82</v>
       </c>
-      <c r="S9" s="12">
-        <v>1</v>
-      </c>
-      <c r="T9" s="12">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>73</v>
-      </c>
-      <c r="W9" t="s">
-        <v>92</v>
-      </c>
-      <c r="X9" t="s">
-        <v>84</v>
-      </c>
       <c r="Y9" s="12">
         <v>1</v>
       </c>
@@ -2807,10 +2644,10 @@
         <v>1</v>
       </c>
       <c r="AC9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AE9" s="12">
         <v>1</v>
@@ -2819,28 +2656,16 @@
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AH9" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AL9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO9" t="s">
         <v>27</v>
@@ -2868,101 +2693,82 @@
       <c r="G10" s="6">
         <v>2.5</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O10" t="s">
+        <v>77</v>
+      </c>
+      <c r="P10" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q10" t="s">
         <v>79</v>
       </c>
-      <c r="O10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P10" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>81</v>
-      </c>
       <c r="R10" t="s">
+        <v>80</v>
+      </c>
+      <c r="S10" s="12">
+        <v>1</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X10" t="s">
         <v>82</v>
       </c>
-      <c r="S10" s="12">
-        <v>1</v>
-      </c>
-      <c r="T10" s="12">
-        <v>0</v>
-      </c>
-      <c r="U10" t="s">
-        <v>73</v>
-      </c>
-      <c r="W10" t="s">
-        <v>92</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="Y10" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="s">
         <v>84</v>
       </c>
-      <c r="Y10" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>86</v>
-      </c>
       <c r="AH10" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AL10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO10" t="s">
         <v>33</v>
@@ -2990,101 +2796,82 @@
       <c r="G11" s="6">
         <v>3</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
       <c r="J11" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N11" t="s">
+        <v>77</v>
+      </c>
+      <c r="O11" t="s">
+        <v>77</v>
+      </c>
+      <c r="P11" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q11" t="s">
         <v>79</v>
       </c>
-      <c r="O11" t="s">
-        <v>79</v>
-      </c>
-      <c r="P11" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>81</v>
-      </c>
       <c r="R11" t="s">
+        <v>80</v>
+      </c>
+      <c r="S11" s="12">
+        <v>1</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>72</v>
+      </c>
+      <c r="X11" t="s">
         <v>82</v>
       </c>
-      <c r="S11" s="12">
-        <v>1</v>
-      </c>
-      <c r="T11" s="12">
-        <v>0</v>
-      </c>
-      <c r="U11" t="s">
-        <v>73</v>
-      </c>
-      <c r="W11" t="s">
-        <v>92</v>
-      </c>
-      <c r="X11" t="s">
+      <c r="Y11" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="s">
         <v>84</v>
       </c>
-      <c r="Y11" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>86</v>
-      </c>
       <c r="AH11" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AL11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO11" t="s">
         <v>34</v>
@@ -3113,106 +2900,103 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" t="s">
         <v>74</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>75</v>
       </c>
-      <c r="K12" t="s">
-        <v>76</v>
-      </c>
       <c r="L12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N12" t="s">
+        <v>77</v>
+      </c>
+      <c r="O12" t="s">
+        <v>77</v>
+      </c>
+      <c r="P12" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q12" t="s">
         <v>79</v>
       </c>
-      <c r="O12" t="s">
-        <v>79</v>
-      </c>
-      <c r="P12" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>81</v>
-      </c>
       <c r="R12" t="s">
+        <v>94</v>
+      </c>
+      <c r="S12" s="12">
+        <v>1</v>
+      </c>
+      <c r="T12" s="12">
+        <v>1</v>
+      </c>
+      <c r="U12" t="s">
         <v>103</v>
       </c>
-      <c r="S12" s="12">
-        <v>1</v>
-      </c>
-      <c r="T12" s="12">
-        <v>1</v>
-      </c>
-      <c r="U12" t="s">
-        <v>115</v>
-      </c>
       <c r="V12" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="W12" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="X12" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="s">
         <v>84</v>
       </c>
-      <c r="Y12" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD12" t="s">
+      <c r="AH12" t="s">
         <v>85</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>87</v>
       </c>
       <c r="AI12">
         <v>2.2000000000000002</v>
       </c>
       <c r="AJ12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>120</v>
+        <v>77</v>
+      </c>
+      <c r="AK12">
+        <v>5.5</v>
       </c>
       <c r="AL12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO12" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.35">
@@ -3238,106 +3022,94 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" t="s">
         <v>74</v>
       </c>
-      <c r="J13" t="s">
-        <v>75</v>
-      </c>
-      <c r="K13" t="s">
-        <v>78</v>
-      </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O13" t="s">
+        <v>77</v>
+      </c>
+      <c r="P13" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q13" t="s">
         <v>79</v>
       </c>
-      <c r="O13" t="s">
-        <v>79</v>
-      </c>
-      <c r="P13" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>81</v>
-      </c>
       <c r="R13" t="s">
+        <v>80</v>
+      </c>
+      <c r="S13" s="12">
+        <v>1</v>
+      </c>
+      <c r="T13" s="12">
+        <v>0</v>
+      </c>
+      <c r="U13" t="s">
+        <v>103</v>
+      </c>
+      <c r="V13" t="s">
+        <v>104</v>
+      </c>
+      <c r="X13" t="s">
         <v>82</v>
       </c>
-      <c r="S13" s="12">
-        <v>1</v>
-      </c>
-      <c r="T13" s="12">
-        <v>0</v>
-      </c>
-      <c r="U13" t="s">
-        <v>115</v>
-      </c>
-      <c r="V13" t="s">
-        <v>116</v>
-      </c>
-      <c r="W13" t="s">
-        <v>98</v>
-      </c>
-      <c r="X13" t="s">
+      <c r="Y13" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="s">
         <v>84</v>
       </c>
-      <c r="Y13" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>85</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>86</v>
-      </c>
       <c r="AH13" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>117</v>
+        <v>77</v>
+      </c>
+      <c r="AK13">
+        <v>5</v>
       </c>
       <c r="AL13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO13" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.35">
@@ -3362,38 +3134,34 @@
       <c r="G14" s="6">
         <v>5</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" t="s">
         <v>75</v>
       </c>
-      <c r="K14" t="s">
-        <v>76</v>
-      </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N14" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" t="s">
+        <v>77</v>
+      </c>
+      <c r="P14" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q14" t="s">
         <v>79</v>
       </c>
-      <c r="O14" t="s">
-        <v>79</v>
-      </c>
-      <c r="P14" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>81</v>
-      </c>
       <c r="R14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S14" s="12">
         <v>1</v>
@@ -3402,13 +3170,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="s">
-        <v>73</v>
-      </c>
-      <c r="W14" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X14" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="Y14" s="12">
         <v>1</v>
@@ -3423,40 +3188,37 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE14" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH14" t="s">
         <v>85</v>
-      </c>
-      <c r="AE14" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>87</v>
       </c>
       <c r="AI14">
         <v>8</v>
       </c>
       <c r="AJ14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>125</v>
+        <v>77</v>
+      </c>
+      <c r="AK14">
+        <v>6</v>
       </c>
       <c r="AL14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO14" t="s">
         <v>47</v>
@@ -3485,100 +3247,94 @@
         <v>3</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M15" t="s">
+        <v>72</v>
+      </c>
+      <c r="N15" t="s">
+        <v>77</v>
+      </c>
+      <c r="O15" t="s">
+        <v>77</v>
+      </c>
+      <c r="P15" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q15" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s">
-        <v>75</v>
-      </c>
-      <c r="K15" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15" t="s">
-        <v>96</v>
-      </c>
-      <c r="M15" t="s">
-        <v>73</v>
-      </c>
-      <c r="N15" t="s">
-        <v>79</v>
-      </c>
-      <c r="O15" t="s">
-        <v>79</v>
-      </c>
-      <c r="P15" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>81</v>
-      </c>
       <c r="R15" t="s">
+        <v>80</v>
+      </c>
+      <c r="S15" s="12">
+        <v>1</v>
+      </c>
+      <c r="T15" s="12">
+        <v>0</v>
+      </c>
+      <c r="U15" t="s">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s">
+        <v>108</v>
+      </c>
+      <c r="X15" t="s">
         <v>82</v>
       </c>
-      <c r="S15" s="12">
-        <v>1</v>
-      </c>
-      <c r="T15" s="12">
-        <v>0</v>
-      </c>
-      <c r="U15" t="s">
-        <v>73</v>
-      </c>
-      <c r="W15" t="s">
-        <v>122</v>
-      </c>
-      <c r="X15" t="s">
+      <c r="Y15" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="s">
         <v>84</v>
       </c>
-      <c r="Y15" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s">
+      <c r="AH15" t="s">
         <v>85</v>
       </c>
-      <c r="AE15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>123</v>
+        <v>77</v>
+      </c>
+      <c r="AK15">
+        <v>5.5</v>
       </c>
       <c r="AL15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO15" t="s">
         <v>48</v>
@@ -3598,7 +3354,7 @@
         <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F16" s="6">
         <v>10</v>
@@ -3606,38 +3362,31 @@
       <c r="G16" s="6">
         <v>0.5</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
       <c r="J16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s">
         <v>75</v>
       </c>
-      <c r="K16" t="s">
-        <v>76</v>
-      </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M16" t="s">
-        <v>73</v>
-      </c>
-      <c r="N16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="O16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P16" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q16" t="s">
         <v>79</v>
       </c>
-      <c r="P16" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>81</v>
-      </c>
       <c r="R16" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S16" s="12">
         <v>1</v>
@@ -3646,13 +3395,10 @@
         <v>1</v>
       </c>
       <c r="U16" t="s">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X16" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="Y16" s="12">
         <v>1</v>
@@ -3667,40 +3413,31 @@
         <v>0</v>
       </c>
       <c r="AC16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD16" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE16" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH16" t="s">
         <v>85</v>
       </c>
-      <c r="AE16" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>100</v>
-      </c>
       <c r="AJ16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM16" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO16" t="s">
         <v>49</v>
@@ -3729,103 +3466,94 @@
         <v>3.5</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" t="s">
         <v>74</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>75</v>
       </c>
-      <c r="K17" t="s">
-        <v>76</v>
-      </c>
       <c r="L17" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N17" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q17" t="s">
         <v>79</v>
       </c>
-      <c r="O17" t="s">
-        <v>79</v>
-      </c>
-      <c r="P17" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>81</v>
-      </c>
       <c r="R17" t="s">
+        <v>80</v>
+      </c>
+      <c r="S17" s="12">
+        <v>1</v>
+      </c>
+      <c r="T17" s="12">
+        <v>0</v>
+      </c>
+      <c r="U17" t="s">
+        <v>72</v>
+      </c>
+      <c r="X17" t="s">
         <v>82</v>
       </c>
-      <c r="S17" s="12">
-        <v>1</v>
-      </c>
-      <c r="T17" s="12">
-        <v>0</v>
-      </c>
-      <c r="U17" t="s">
-        <v>73</v>
-      </c>
-      <c r="W17" t="s">
-        <v>92</v>
-      </c>
-      <c r="X17" t="s">
+      <c r="Y17" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="s">
         <v>84</v>
       </c>
-      <c r="Y17" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD17" t="s">
+      <c r="AH17" t="s">
         <v>85</v>
       </c>
-      <c r="AE17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ17" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>127</v>
+        <v>77</v>
+      </c>
+      <c r="AK17">
+        <v>4</v>
       </c>
       <c r="AL17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM17" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.35">
@@ -3851,103 +3579,94 @@
         <v>5</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" t="s">
         <v>74</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>75</v>
       </c>
-      <c r="K18" t="s">
-        <v>76</v>
-      </c>
       <c r="L18" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N18" t="s">
+        <v>77</v>
+      </c>
+      <c r="O18" t="s">
+        <v>77</v>
+      </c>
+      <c r="P18" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q18" t="s">
         <v>79</v>
       </c>
-      <c r="O18" t="s">
-        <v>79</v>
-      </c>
-      <c r="P18" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>81</v>
-      </c>
       <c r="R18" t="s">
+        <v>80</v>
+      </c>
+      <c r="S18" s="12">
+        <v>1</v>
+      </c>
+      <c r="T18" s="12">
+        <v>0</v>
+      </c>
+      <c r="U18" t="s">
+        <v>72</v>
+      </c>
+      <c r="X18" t="s">
         <v>82</v>
       </c>
-      <c r="S18" s="12">
-        <v>1</v>
-      </c>
-      <c r="T18" s="12">
-        <v>0</v>
-      </c>
-      <c r="U18" t="s">
-        <v>73</v>
-      </c>
-      <c r="W18" t="s">
-        <v>92</v>
-      </c>
-      <c r="X18" t="s">
+      <c r="Y18" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="s">
         <v>84</v>
       </c>
-      <c r="Y18" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD18" t="s">
+      <c r="AH18" t="s">
         <v>85</v>
       </c>
-      <c r="AE18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ18" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>104</v>
+        <v>77</v>
+      </c>
+      <c r="AK18">
+        <v>5</v>
       </c>
       <c r="AL18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.35">
@@ -3973,106 +3692,97 @@
         <v>2</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" t="s">
         <v>74</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>75</v>
       </c>
-      <c r="K19" t="s">
-        <v>76</v>
-      </c>
       <c r="L19" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N19" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" t="s">
+        <v>77</v>
+      </c>
+      <c r="P19" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q19" t="s">
         <v>79</v>
       </c>
-      <c r="O19" t="s">
-        <v>79</v>
-      </c>
-      <c r="P19" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>81</v>
-      </c>
       <c r="R19" t="s">
+        <v>80</v>
+      </c>
+      <c r="S19" s="12">
+        <v>1</v>
+      </c>
+      <c r="T19" s="12">
+        <v>0</v>
+      </c>
+      <c r="U19" t="s">
+        <v>103</v>
+      </c>
+      <c r="W19" t="s">
+        <v>111</v>
+      </c>
+      <c r="X19" t="s">
         <v>82</v>
       </c>
-      <c r="S19" s="12">
-        <v>1</v>
-      </c>
-      <c r="T19" s="12">
-        <v>0</v>
-      </c>
-      <c r="U19" t="s">
-        <v>115</v>
-      </c>
-      <c r="V19" t="s">
-        <v>100</v>
-      </c>
-      <c r="W19" t="s">
-        <v>128</v>
-      </c>
-      <c r="X19" t="s">
+      <c r="Y19" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="s">
         <v>84</v>
       </c>
-      <c r="Y19" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD19" t="s">
+      <c r="AH19" t="s">
         <v>85</v>
       </c>
-      <c r="AE19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>129</v>
+        <v>77</v>
+      </c>
+      <c r="AK19">
+        <v>2.5</v>
       </c>
       <c r="AL19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.35">
@@ -4098,37 +3808,37 @@
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s">
+        <v>75</v>
+      </c>
+      <c r="L20" t="s">
+        <v>90</v>
+      </c>
+      <c r="M20" t="s">
+        <v>72</v>
+      </c>
+      <c r="N20" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" t="s">
+        <v>77</v>
+      </c>
+      <c r="P20" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q20" t="s">
         <v>79</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J20" t="s">
-        <v>75</v>
-      </c>
-      <c r="K20" t="s">
-        <v>76</v>
-      </c>
-      <c r="L20" t="s">
-        <v>96</v>
-      </c>
-      <c r="M20" t="s">
-        <v>73</v>
-      </c>
-      <c r="N20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O20" t="s">
-        <v>79</v>
-      </c>
-      <c r="P20" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>81</v>
-      </c>
       <c r="R20" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="S20" s="12">
         <v>0</v>
@@ -4137,64 +3847,58 @@
         <v>1</v>
       </c>
       <c r="U20" t="s">
-        <v>73</v>
-      </c>
-      <c r="W20" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y20" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="s">
         <v>84</v>
       </c>
-      <c r="Y20" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD20" t="s">
+      <c r="AH20" t="s">
         <v>85</v>
-      </c>
-      <c r="AE20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>87</v>
       </c>
       <c r="AI20">
         <v>2.4</v>
       </c>
       <c r="AJ20" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>132</v>
+        <v>77</v>
+      </c>
+      <c r="AK20">
+        <v>9.5</v>
       </c>
       <c r="AL20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM20" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.35">
@@ -4220,100 +3924,94 @@
         <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" t="s">
         <v>74</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>75</v>
       </c>
-      <c r="K21" t="s">
-        <v>76</v>
-      </c>
       <c r="L21" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N21" t="s">
+        <v>77</v>
+      </c>
+      <c r="O21" t="s">
+        <v>77</v>
+      </c>
+      <c r="P21" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q21" t="s">
         <v>79</v>
       </c>
-      <c r="O21" t="s">
-        <v>79</v>
-      </c>
-      <c r="P21" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>81</v>
-      </c>
       <c r="R21" t="s">
+        <v>80</v>
+      </c>
+      <c r="S21" s="12">
+        <v>1</v>
+      </c>
+      <c r="T21" s="12">
+        <v>0</v>
+      </c>
+      <c r="U21" t="s">
+        <v>72</v>
+      </c>
+      <c r="X21" t="s">
         <v>82</v>
       </c>
-      <c r="S21" s="12">
-        <v>1</v>
-      </c>
-      <c r="T21" s="12">
-        <v>0</v>
-      </c>
-      <c r="U21" t="s">
-        <v>73</v>
-      </c>
-      <c r="W21" t="s">
-        <v>92</v>
-      </c>
-      <c r="X21" t="s">
+      <c r="Y21" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="s">
         <v>84</v>
       </c>
-      <c r="Y21" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD21" t="s">
+      <c r="AH21" t="s">
         <v>85</v>
-      </c>
-      <c r="AE21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF21" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>87</v>
       </c>
       <c r="AI21">
         <v>2.4</v>
       </c>
       <c r="AJ21" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>133</v>
+        <v>77</v>
+      </c>
+      <c r="AK21">
+        <v>5</v>
       </c>
       <c r="AL21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM21" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO21" t="s">
         <v>48</v>
@@ -4321,10 +4019,10 @@
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -4333,7 +4031,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F22" s="6">
         <v>200</v>
@@ -4341,38 +4039,34 @@
       <c r="G22" s="6">
         <v>0.25</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
       <c r="J22" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s">
         <v>75</v>
       </c>
-      <c r="K22" t="s">
-        <v>76</v>
-      </c>
       <c r="L22" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" t="s">
+        <v>77</v>
+      </c>
+      <c r="P22" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q22" t="s">
         <v>79</v>
       </c>
-      <c r="O22" t="s">
-        <v>79</v>
-      </c>
-      <c r="P22" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>81</v>
-      </c>
       <c r="R22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S22" s="12">
         <v>1</v>
@@ -4381,13 +4075,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>73</v>
-      </c>
-      <c r="W22" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X22" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="Y22" s="12">
         <v>1</v>
@@ -4402,57 +4093,54 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE22" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH22" t="s">
         <v>85</v>
-      </c>
-      <c r="AE22" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF22" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>87</v>
       </c>
       <c r="AI22">
         <v>5</v>
       </c>
       <c r="AJ22" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>120</v>
+        <v>72</v>
+      </c>
+      <c r="AK22">
+        <v>5.5</v>
       </c>
       <c r="AL22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM22" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
@@ -4464,37 +4152,37 @@
         <v>0.25</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" t="s">
         <v>74</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>75</v>
       </c>
-      <c r="K23" t="s">
-        <v>76</v>
-      </c>
       <c r="L23" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N23" t="s">
+        <v>77</v>
+      </c>
+      <c r="O23" t="s">
+        <v>77</v>
+      </c>
+      <c r="P23" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q23" t="s">
         <v>79</v>
       </c>
-      <c r="O23" t="s">
-        <v>79</v>
-      </c>
-      <c r="P23" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>81</v>
-      </c>
       <c r="R23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S23" s="12">
         <v>1</v>
@@ -4503,13 +4191,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>73</v>
-      </c>
-      <c r="W23" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X23" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="Y23" s="12">
         <v>1</v>
@@ -4524,60 +4209,51 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE23" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH23" t="s">
         <v>85</v>
       </c>
-      <c r="AE23" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>78</v>
-      </c>
       <c r="AJ23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AL23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM23" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F24" s="6">
         <v>23</v>
@@ -4586,37 +4262,35 @@
         <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I24" s="2"/>
       <c r="J24" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s">
         <v>75</v>
       </c>
-      <c r="K24" t="s">
-        <v>76</v>
-      </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O24" t="s">
+        <v>77</v>
+      </c>
+      <c r="P24" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q24" t="s">
         <v>79</v>
       </c>
-      <c r="P24" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>81</v>
-      </c>
       <c r="R24" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S24" s="12">
         <v>1</v>
@@ -4625,13 +4299,13 @@
         <v>1</v>
       </c>
       <c r="U24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W24" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X24" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="Y24" s="12">
         <v>1</v>
@@ -4646,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="AC24" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD24" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE24" s="12">
         <v>1</v>
@@ -4658,45 +4332,36 @@
         <v>1</v>
       </c>
       <c r="AG24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH24" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AL24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN24" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="AO24" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -4708,37 +4373,37 @@
         <v>3</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J25" t="s">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M25" t="s">
+        <v>72</v>
+      </c>
+      <c r="N25" t="s">
+        <v>72</v>
+      </c>
+      <c r="O25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P25" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q25" t="s">
         <v>79</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J25" t="s">
-        <v>75</v>
-      </c>
-      <c r="K25" t="s">
-        <v>76</v>
-      </c>
-      <c r="L25" t="s">
-        <v>96</v>
-      </c>
-      <c r="M25" t="s">
-        <v>73</v>
-      </c>
-      <c r="N25" t="s">
-        <v>73</v>
-      </c>
-      <c r="O25" t="s">
-        <v>79</v>
-      </c>
-      <c r="P25" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>81</v>
-      </c>
       <c r="R25" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S25" s="12">
         <v>1</v>
@@ -4747,13 +4412,13 @@
         <v>1</v>
       </c>
       <c r="U25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W25" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X25" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="Y25" s="12">
         <v>1</v>
@@ -4768,10 +4433,10 @@
         <v>1</v>
       </c>
       <c r="AC25" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD25" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE25" s="12">
         <v>1</v>
@@ -4780,45 +4445,42 @@
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ25" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>309</v>
+        <v>72</v>
+      </c>
+      <c r="AK25">
+        <v>2</v>
       </c>
       <c r="AL25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="AO25" t="s">
-        <v>333</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -4830,37 +4492,37 @@
         <v>3</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s">
+        <v>75</v>
+      </c>
+      <c r="L26" t="s">
+        <v>90</v>
+      </c>
+      <c r="M26" t="s">
+        <v>72</v>
+      </c>
+      <c r="N26" t="s">
+        <v>72</v>
+      </c>
+      <c r="O26" t="s">
+        <v>77</v>
+      </c>
+      <c r="P26" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q26" t="s">
         <v>79</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J26" t="s">
-        <v>75</v>
-      </c>
-      <c r="K26" t="s">
-        <v>76</v>
-      </c>
-      <c r="L26" t="s">
-        <v>96</v>
-      </c>
-      <c r="M26" t="s">
-        <v>73</v>
-      </c>
-      <c r="N26" t="s">
-        <v>73</v>
-      </c>
-      <c r="O26" t="s">
-        <v>79</v>
-      </c>
-      <c r="P26" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>81</v>
-      </c>
       <c r="R26" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S26" s="12">
         <v>1</v>
@@ -4869,13 +4531,13 @@
         <v>1</v>
       </c>
       <c r="U26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W26" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X26" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="Y26" s="12">
         <v>1</v>
@@ -4890,10 +4552,10 @@
         <v>1</v>
       </c>
       <c r="AC26" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE26" s="12">
         <v>1</v>
@@ -4902,45 +4564,42 @@
         <v>1</v>
       </c>
       <c r="AG26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH26" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ26" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>310</v>
+        <v>72</v>
+      </c>
+      <c r="AK26">
+        <v>2</v>
       </c>
       <c r="AL26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN26" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -4952,37 +4611,37 @@
         <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J27" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" t="s">
+        <v>90</v>
+      </c>
+      <c r="M27" t="s">
+        <v>72</v>
+      </c>
+      <c r="N27" t="s">
+        <v>72</v>
+      </c>
+      <c r="O27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P27" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q27" t="s">
         <v>79</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J27" t="s">
-        <v>75</v>
-      </c>
-      <c r="K27" t="s">
-        <v>76</v>
-      </c>
-      <c r="L27" t="s">
-        <v>96</v>
-      </c>
-      <c r="M27" t="s">
-        <v>73</v>
-      </c>
-      <c r="N27" t="s">
-        <v>73</v>
-      </c>
-      <c r="O27" t="s">
-        <v>79</v>
-      </c>
-      <c r="P27" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>81</v>
-      </c>
       <c r="R27" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S27" s="12">
         <v>1</v>
@@ -4991,13 +4650,13 @@
         <v>1</v>
       </c>
       <c r="U27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W27" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X27" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="Y27" s="12">
         <v>1</v>
@@ -5012,57 +4671,54 @@
         <v>1</v>
       </c>
       <c r="AC27" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD27" t="s">
+        <v>286</v>
+      </c>
+      <c r="AE27" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK27">
+        <v>2</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO27" t="s">
         <v>306</v>
-      </c>
-      <c r="AE27" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="12">
-        <v>1</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>310</v>
-      </c>
-      <c r="AL27" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM27" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>320</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -5074,37 +4730,37 @@
         <v>3</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J28" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s">
+        <v>75</v>
+      </c>
+      <c r="L28" t="s">
+        <v>90</v>
+      </c>
+      <c r="M28" t="s">
+        <v>72</v>
+      </c>
+      <c r="N28" t="s">
+        <v>72</v>
+      </c>
+      <c r="O28" t="s">
+        <v>77</v>
+      </c>
+      <c r="P28" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q28" t="s">
         <v>79</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J28" t="s">
-        <v>75</v>
-      </c>
-      <c r="K28" t="s">
-        <v>76</v>
-      </c>
-      <c r="L28" t="s">
-        <v>96</v>
-      </c>
-      <c r="M28" t="s">
-        <v>73</v>
-      </c>
-      <c r="N28" t="s">
-        <v>73</v>
-      </c>
-      <c r="O28" t="s">
-        <v>79</v>
-      </c>
-      <c r="P28" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>81</v>
-      </c>
       <c r="R28" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S28" s="12">
         <v>1</v>
@@ -5113,13 +4769,13 @@
         <v>1</v>
       </c>
       <c r="U28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W28" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X28" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="Y28" s="12">
         <v>1</v>
@@ -5134,10 +4790,10 @@
         <v>1</v>
       </c>
       <c r="AC28" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD28" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE28" s="12">
         <v>1</v>
@@ -5146,45 +4802,42 @@
         <v>1</v>
       </c>
       <c r="AG28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH28" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AJ28" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>310</v>
+        <v>72</v>
+      </c>
+      <c r="AK28">
+        <v>2</v>
       </c>
       <c r="AL28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -5196,37 +4849,37 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J29" t="s">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s">
+        <v>75</v>
+      </c>
+      <c r="L29" t="s">
+        <v>90</v>
+      </c>
+      <c r="M29" t="s">
+        <v>77</v>
+      </c>
+      <c r="N29" t="s">
+        <v>72</v>
+      </c>
+      <c r="O29" t="s">
+        <v>77</v>
+      </c>
+      <c r="P29" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q29" t="s">
         <v>79</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J29" t="s">
-        <v>75</v>
-      </c>
-      <c r="K29" t="s">
-        <v>76</v>
-      </c>
-      <c r="L29" t="s">
-        <v>96</v>
-      </c>
-      <c r="M29" t="s">
-        <v>79</v>
-      </c>
-      <c r="N29" t="s">
-        <v>73</v>
-      </c>
-      <c r="O29" t="s">
-        <v>79</v>
-      </c>
-      <c r="P29" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>81</v>
-      </c>
       <c r="R29" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S29" s="12">
         <v>1</v>
@@ -5235,13 +4888,13 @@
         <v>1</v>
       </c>
       <c r="U29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W29" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X29" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="Y29" s="12">
         <v>1</v>
@@ -5256,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="AC29" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD29" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE29" s="12">
         <v>1</v>
@@ -5268,45 +4921,39 @@
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH29" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI29" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AJ29" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK29" t="s">
-        <v>311</v>
+        <v>77</v>
+      </c>
+      <c r="AK29">
+        <v>1</v>
       </c>
       <c r="AL29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM29" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO29" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
@@ -5318,37 +4965,37 @@
         <v>10</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J30" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" t="s">
+        <v>90</v>
+      </c>
+      <c r="M30" t="s">
+        <v>72</v>
+      </c>
+      <c r="N30" t="s">
+        <v>72</v>
+      </c>
+      <c r="O30" t="s">
+        <v>77</v>
+      </c>
+      <c r="P30" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q30" t="s">
         <v>79</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J30" t="s">
-        <v>75</v>
-      </c>
-      <c r="K30" t="s">
-        <v>76</v>
-      </c>
-      <c r="L30" t="s">
-        <v>96</v>
-      </c>
-      <c r="M30" t="s">
-        <v>73</v>
-      </c>
-      <c r="N30" t="s">
-        <v>73</v>
-      </c>
-      <c r="O30" t="s">
-        <v>79</v>
-      </c>
-      <c r="P30" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>81</v>
-      </c>
       <c r="R30" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S30" s="12">
         <v>1</v>
@@ -5357,16 +5004,13 @@
         <v>1</v>
       </c>
       <c r="U30" t="s">
-        <v>79</v>
-      </c>
-      <c r="V30" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="W30" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="X30" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="Y30" s="12">
         <v>1</v>
@@ -5381,10 +5025,10 @@
         <v>1</v>
       </c>
       <c r="AC30" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD30" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE30" s="12">
         <v>1</v>
@@ -5393,45 +5037,39 @@
         <v>1</v>
       </c>
       <c r="AG30" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="AH30" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ30" t="s">
-        <v>312</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="AO30" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -5443,37 +5081,37 @@
         <v>10</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J31" t="s">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s">
+        <v>75</v>
+      </c>
+      <c r="L31" t="s">
+        <v>90</v>
+      </c>
+      <c r="M31" t="s">
+        <v>72</v>
+      </c>
+      <c r="N31" t="s">
+        <v>72</v>
+      </c>
+      <c r="O31" t="s">
+        <v>77</v>
+      </c>
+      <c r="P31" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q31" t="s">
         <v>79</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J31" t="s">
-        <v>75</v>
-      </c>
-      <c r="K31" t="s">
-        <v>76</v>
-      </c>
-      <c r="L31" t="s">
-        <v>96</v>
-      </c>
-      <c r="M31" t="s">
-        <v>73</v>
-      </c>
-      <c r="N31" t="s">
-        <v>73</v>
-      </c>
-      <c r="O31" t="s">
-        <v>79</v>
-      </c>
-      <c r="P31" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>81</v>
-      </c>
       <c r="R31" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S31" s="12">
         <v>1</v>
@@ -5482,13 +5120,10 @@
         <v>1</v>
       </c>
       <c r="U31" t="s">
-        <v>73</v>
-      </c>
-      <c r="W31" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="X31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y31" s="12">
         <v>1</v>
@@ -5503,10 +5138,10 @@
         <v>1</v>
       </c>
       <c r="AC31" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD31" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE31" s="12">
         <v>1</v>
@@ -5515,48 +5150,42 @@
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="AH31" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ31" t="s">
-        <v>312</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>60</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN31" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="AO31" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F32" s="6">
         <v>35</v>
@@ -5565,117 +5194,103 @@
         <v>6</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I32" s="2"/>
       <c r="J32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K32" t="s">
+        <v>275</v>
+      </c>
+      <c r="L32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M32" t="s">
+        <v>72</v>
+      </c>
+      <c r="N32" t="s">
+        <v>72</v>
+      </c>
+      <c r="O32" t="s">
+        <v>77</v>
+      </c>
+      <c r="P32" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>79</v>
+      </c>
+      <c r="R32" t="s">
+        <v>94</v>
+      </c>
+      <c r="S32" s="12">
+        <v>1</v>
+      </c>
+      <c r="T32" s="12">
+        <v>1</v>
+      </c>
+      <c r="W32" t="s">
+        <v>280</v>
+      </c>
+      <c r="X32" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y32" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>286</v>
+      </c>
+      <c r="AE32" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK32">
+        <v>5</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN32" t="s">
         <v>295</v>
       </c>
-      <c r="L32" t="s">
-        <v>296</v>
-      </c>
-      <c r="M32" t="s">
-        <v>73</v>
-      </c>
-      <c r="N32" t="s">
-        <v>73</v>
-      </c>
-      <c r="O32" t="s">
-        <v>79</v>
-      </c>
-      <c r="P32" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>81</v>
-      </c>
-      <c r="R32" t="s">
-        <v>103</v>
-      </c>
-      <c r="S32" s="12">
-        <v>1</v>
-      </c>
-      <c r="T32" s="12">
-        <v>1</v>
-      </c>
-      <c r="U32" t="s">
-        <v>78</v>
-      </c>
-      <c r="W32" t="s">
-        <v>300</v>
-      </c>
-      <c r="X32" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y32" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>306</v>
-      </c>
-      <c r="AE32" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF32" s="12">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>117</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM32" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>324</v>
-      </c>
       <c r="AO32" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
@@ -5687,37 +5302,37 @@
         <v>2</v>
       </c>
       <c r="H33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J33" t="s">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s">
+        <v>75</v>
+      </c>
+      <c r="L33" t="s">
+        <v>90</v>
+      </c>
+      <c r="M33" t="s">
+        <v>72</v>
+      </c>
+      <c r="N33" t="s">
+        <v>72</v>
+      </c>
+      <c r="O33" t="s">
+        <v>77</v>
+      </c>
+      <c r="P33" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q33" t="s">
         <v>79</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J33" t="s">
-        <v>75</v>
-      </c>
-      <c r="K33" t="s">
-        <v>76</v>
-      </c>
-      <c r="L33" t="s">
-        <v>96</v>
-      </c>
-      <c r="M33" t="s">
-        <v>73</v>
-      </c>
-      <c r="N33" t="s">
-        <v>73</v>
-      </c>
-      <c r="O33" t="s">
-        <v>79</v>
-      </c>
-      <c r="P33" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>81</v>
-      </c>
       <c r="R33" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S33" s="12">
         <v>1</v>
@@ -5726,13 +5341,13 @@
         <v>1</v>
       </c>
       <c r="U33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W33" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X33" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="Y33" s="12">
         <v>0</v>
@@ -5747,10 +5362,10 @@
         <v>1</v>
       </c>
       <c r="AC33" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD33" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE33" s="12">
         <v>1</v>
@@ -5759,45 +5374,42 @@
         <v>1</v>
       </c>
       <c r="AG33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH33" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="AI33">
         <v>20</v>
       </c>
       <c r="AJ33" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>309</v>
+        <v>72</v>
+      </c>
+      <c r="AK33">
+        <v>2</v>
       </c>
       <c r="AL33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM33" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN33" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO33" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -5809,37 +5421,37 @@
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J34" t="s">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s">
+        <v>75</v>
+      </c>
+      <c r="L34" t="s">
+        <v>90</v>
+      </c>
+      <c r="M34" t="s">
+        <v>72</v>
+      </c>
+      <c r="N34" t="s">
+        <v>72</v>
+      </c>
+      <c r="O34" t="s">
+        <v>77</v>
+      </c>
+      <c r="P34" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q34" t="s">
         <v>79</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J34" t="s">
-        <v>75</v>
-      </c>
-      <c r="K34" t="s">
-        <v>76</v>
-      </c>
-      <c r="L34" t="s">
-        <v>96</v>
-      </c>
-      <c r="M34" t="s">
-        <v>73</v>
-      </c>
-      <c r="N34" t="s">
-        <v>73</v>
-      </c>
-      <c r="O34" t="s">
-        <v>79</v>
-      </c>
-      <c r="P34" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>81</v>
-      </c>
       <c r="R34" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S34" s="12">
         <v>1</v>
@@ -5848,13 +5460,13 @@
         <v>1</v>
       </c>
       <c r="U34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W34" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X34" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="Y34" s="12">
         <v>1</v>
@@ -5869,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="AC34" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD34" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE34" s="12">
         <v>1</v>
@@ -5881,48 +5493,45 @@
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH34" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AJ34" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>309</v>
+        <v>72</v>
+      </c>
+      <c r="AK34">
+        <v>2</v>
       </c>
       <c r="AL34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="AO34" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F35" s="6">
         <v>88</v>
@@ -5931,37 +5540,32 @@
         <v>0.25</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I35" s="2"/>
       <c r="J35" t="s">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s">
         <v>75</v>
       </c>
-      <c r="K35" t="s">
-        <v>76</v>
-      </c>
       <c r="L35" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O35" t="s">
-        <v>73</v>
-      </c>
-      <c r="P35" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="Q35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R35" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S35" s="12">
         <v>1</v>
@@ -5970,13 +5574,13 @@
         <v>1</v>
       </c>
       <c r="U35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W35" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X35" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="Y35" s="12">
         <v>1</v>
@@ -5991,10 +5595,10 @@
         <v>1</v>
       </c>
       <c r="AC35" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD35" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE35" s="12">
         <v>1</v>
@@ -6003,45 +5607,42 @@
         <v>1</v>
       </c>
       <c r="AG35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK35" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK35">
+        <v>0.33</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO35" t="s">
         <v>314</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM35" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>326</v>
-      </c>
-      <c r="AO35" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -6053,117 +5654,114 @@
         <v>3</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="J36" t="s">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s">
         <v>75</v>
       </c>
-      <c r="K36" t="s">
-        <v>76</v>
-      </c>
       <c r="L36" t="s">
+        <v>90</v>
+      </c>
+      <c r="M36" t="s">
+        <v>72</v>
+      </c>
+      <c r="N36" t="s">
+        <v>72</v>
+      </c>
+      <c r="O36" t="s">
+        <v>77</v>
+      </c>
+      <c r="P36" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>278</v>
+      </c>
+      <c r="R36" t="s">
+        <v>94</v>
+      </c>
+      <c r="S36" s="12">
+        <v>1</v>
+      </c>
+      <c r="T36" s="12">
+        <v>1</v>
+      </c>
+      <c r="U36" t="s">
+        <v>72</v>
+      </c>
+      <c r="W36" t="s">
+        <v>280</v>
+      </c>
+      <c r="X36" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y36" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>287</v>
+      </c>
+      <c r="AE36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="s">
         <v>96</v>
       </c>
-      <c r="M36" t="s">
-        <v>73</v>
-      </c>
-      <c r="N36" t="s">
-        <v>73</v>
-      </c>
-      <c r="O36" t="s">
-        <v>79</v>
-      </c>
-      <c r="P36" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q36" t="s">
+      <c r="AH36" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK36">
+        <v>6</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN36" t="s">
         <v>298</v>
       </c>
-      <c r="R36" t="s">
-        <v>103</v>
-      </c>
-      <c r="S36" s="12">
-        <v>1</v>
-      </c>
-      <c r="T36" s="12">
-        <v>1</v>
-      </c>
-      <c r="U36" t="s">
-        <v>73</v>
-      </c>
-      <c r="W36" t="s">
-        <v>300</v>
-      </c>
-      <c r="X36" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y36" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>307</v>
-      </c>
-      <c r="AE36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="12">
-        <v>1</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK36" t="s">
+      <c r="AO36" t="s">
         <v>315</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM36" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>327</v>
-      </c>
-      <c r="AO36" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -6175,37 +5773,37 @@
         <v>3</v>
       </c>
       <c r="H37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" t="s">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s">
+        <v>75</v>
+      </c>
+      <c r="L37" t="s">
+        <v>90</v>
+      </c>
+      <c r="M37" t="s">
+        <v>77</v>
+      </c>
+      <c r="N37" t="s">
+        <v>72</v>
+      </c>
+      <c r="O37" t="s">
+        <v>77</v>
+      </c>
+      <c r="P37" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q37" t="s">
         <v>79</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J37" t="s">
-        <v>75</v>
-      </c>
-      <c r="K37" t="s">
-        <v>76</v>
-      </c>
-      <c r="L37" t="s">
-        <v>96</v>
-      </c>
-      <c r="M37" t="s">
-        <v>79</v>
-      </c>
-      <c r="N37" t="s">
-        <v>73</v>
-      </c>
-      <c r="O37" t="s">
-        <v>79</v>
-      </c>
-      <c r="P37" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>81</v>
-      </c>
       <c r="R37" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S37" s="12">
         <v>1</v>
@@ -6214,81 +5812,72 @@
         <v>1</v>
       </c>
       <c r="U37" t="s">
-        <v>79</v>
-      </c>
-      <c r="V37" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="W37" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X37" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y37" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>286</v>
+      </c>
+      <c r="AE37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="s">
         <v>84</v>
       </c>
-      <c r="Y37" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>306</v>
-      </c>
-      <c r="AE37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>86</v>
-      </c>
       <c r="AH37" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI37" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ37" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>117</v>
+        <v>77</v>
+      </c>
+      <c r="AK37">
+        <v>5</v>
       </c>
       <c r="AL37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM37" t="s">
-        <v>73</v>
-      </c>
-      <c r="AN37" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="AO37" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -6300,37 +5889,37 @@
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="J38" t="s">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s">
         <v>75</v>
       </c>
-      <c r="K38" t="s">
-        <v>76</v>
-      </c>
       <c r="L38" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P38" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="Q38" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="R38" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S38" s="12">
         <v>1</v>
@@ -6338,14 +5927,11 @@
       <c r="T38" s="12">
         <v>1</v>
       </c>
-      <c r="U38" t="s">
-        <v>78</v>
-      </c>
       <c r="W38" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="X38" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="Y38" s="12">
         <v>1</v>
@@ -6360,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="AC38" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD38" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="AE38" s="12">
         <v>0</v>
@@ -6372,48 +5958,39 @@
         <v>1</v>
       </c>
       <c r="AG38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH38" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI38" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AL38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="AO38" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F39" s="6">
         <v>10</v>
@@ -6422,37 +5999,35 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I39" s="2"/>
       <c r="J39" t="s">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s">
         <v>75</v>
       </c>
-      <c r="K39" t="s">
-        <v>76</v>
-      </c>
       <c r="L39" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M39" t="s">
+        <v>77</v>
+      </c>
+      <c r="N39" t="s">
+        <v>72</v>
+      </c>
+      <c r="O39" t="s">
+        <v>77</v>
+      </c>
+      <c r="P39" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q39" t="s">
         <v>79</v>
       </c>
-      <c r="N39" t="s">
-        <v>73</v>
-      </c>
-      <c r="O39" t="s">
-        <v>79</v>
-      </c>
-      <c r="P39" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>81</v>
-      </c>
       <c r="R39" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S39" s="12">
         <v>1</v>
@@ -6460,79 +6035,73 @@
       <c r="T39" s="12">
         <v>1</v>
       </c>
-      <c r="U39" t="s">
-        <v>78</v>
-      </c>
       <c r="W39" t="s">
+        <v>280</v>
+      </c>
+      <c r="X39" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y39" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>286</v>
+      </c>
+      <c r="AE39" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK39">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN39" t="s">
         <v>300</v>
       </c>
-      <c r="X39" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y39" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>306</v>
-      </c>
-      <c r="AE39" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF39" s="12">
-        <v>1</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>316</v>
-      </c>
-      <c r="AL39" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM39" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN39" t="s">
-        <v>329</v>
-      </c>
       <c r="AO39" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -6544,37 +6113,34 @@
         <v>1</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s">
         <v>75</v>
       </c>
-      <c r="K40" t="s">
-        <v>76</v>
-      </c>
       <c r="L40" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O40" t="s">
-        <v>73</v>
-      </c>
-      <c r="P40" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="Q40" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="R40" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S40" s="12">
         <v>1</v>
@@ -6583,17 +6149,14 @@
         <v>1</v>
       </c>
       <c r="U40" t="s">
-        <v>79</v>
-      </c>
-      <c r="V40" t="s">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s">
+        <v>280</v>
+      </c>
+      <c r="X40" t="s">
         <v>100</v>
       </c>
-      <c r="W40" t="s">
-        <v>300</v>
-      </c>
-      <c r="X40" t="s">
-        <v>111</v>
-      </c>
       <c r="Y40" s="12">
         <v>1</v>
       </c>
@@ -6607,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AC40" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD40" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AE40" s="12">
         <v>1</v>
@@ -6619,48 +6182,45 @@
         <v>1</v>
       </c>
       <c r="AG40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH40" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ40" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK40" t="s">
-        <v>316</v>
+        <v>77</v>
+      </c>
+      <c r="AK40">
+        <v>1</v>
       </c>
       <c r="AL40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="AO40" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F41" s="6">
         <v>52</v>
@@ -6669,37 +6229,35 @@
         <v>0.5</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>60</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I41" s="2"/>
       <c r="J41" t="s">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s">
         <v>75</v>
       </c>
-      <c r="K41" t="s">
-        <v>76</v>
-      </c>
       <c r="L41" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P41" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="Q41" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="R41" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S41" s="12">
         <v>1</v>
@@ -6708,17 +6266,14 @@
         <v>1</v>
       </c>
       <c r="U41" t="s">
-        <v>79</v>
-      </c>
-      <c r="V41" t="s">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s">
+        <v>280</v>
+      </c>
+      <c r="X41" t="s">
         <v>100</v>
       </c>
-      <c r="W41" t="s">
-        <v>300</v>
-      </c>
-      <c r="X41" t="s">
-        <v>111</v>
-      </c>
       <c r="Y41" s="12">
         <v>1</v>
       </c>
@@ -6732,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="AC41" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD41" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="AE41" s="12">
         <v>0</v>
@@ -6744,45 +6299,42 @@
         <v>1</v>
       </c>
       <c r="AG41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH41" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ41" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>317</v>
+        <v>77</v>
+      </c>
+      <c r="AK41">
+        <v>0.5</v>
       </c>
       <c r="AL41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN41" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="AO41" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -6794,37 +6346,37 @@
         <v>0.25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="J42" t="s">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s">
         <v>75</v>
       </c>
-      <c r="K42" t="s">
-        <v>76</v>
-      </c>
       <c r="L42" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P42" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="Q42" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="R42" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S42" s="12">
         <v>1</v>
@@ -6832,15 +6384,9 @@
       <c r="T42" s="12">
         <v>1</v>
       </c>
-      <c r="U42" t="s">
-        <v>78</v>
-      </c>
-      <c r="W42" t="s">
+      <c r="X42" t="s">
         <v>92</v>
       </c>
-      <c r="X42" t="s">
-        <v>99</v>
-      </c>
       <c r="Y42" s="12">
         <v>1</v>
       </c>
@@ -6854,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="AC42" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="AE42" s="12">
         <v>0</v>
@@ -6866,31 +6412,28 @@
         <v>1</v>
       </c>
       <c r="AG42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AH42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI42" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>318</v>
+        <v>72</v>
+      </c>
+      <c r="AK42">
+        <v>0.33</v>
       </c>
       <c r="AL42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AN42" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="AO42" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -6918,34 +6461,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -7592,10 +7135,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -7624,10 +7167,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
@@ -7656,10 +7199,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -7688,10 +7231,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -7720,10 +7263,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -7752,10 +7295,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -7784,10 +7327,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -7816,10 +7359,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -7848,10 +7391,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -7880,10 +7423,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -7912,10 +7455,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -7944,10 +7487,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -7976,10 +7519,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -8008,10 +7551,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -8040,10 +7583,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -8072,10 +7615,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -8104,10 +7647,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -8136,10 +7679,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -8168,10 +7711,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -8200,10 +7743,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -8232,10 +7775,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -8283,25 +7826,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -8767,10 +8310,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -8790,10 +8333,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
@@ -8813,10 +8356,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -8836,10 +8379,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -8859,10 +8402,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -8882,10 +8425,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -8905,10 +8448,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -8928,10 +8471,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -8951,10 +8494,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -8974,10 +8517,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -8997,10 +8540,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -9020,10 +8563,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -9043,10 +8586,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -9066,10 +8609,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -9089,10 +8632,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -9112,10 +8655,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -9135,10 +8678,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -9158,10 +8701,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -9181,10 +8724,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -9204,10 +8747,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -9227,10 +8770,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -9911,91 +9454,91 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="Y1" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AB1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="AC1" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="V1" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
@@ -10063,7 +9606,7 @@
         <v>13.599999999999994</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="W2" s="22">
         <v>0.20867383512542267</v>
@@ -10152,7 +9695,7 @@
         <v>11.899999999999995</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="W3" s="22">
         <v>0.22000000000019782</v>
@@ -10241,7 +9784,7 @@
         <v>66.100000000000009</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="W4" s="22">
         <v>0.66333333333309008</v>
@@ -10864,7 +10407,7 @@
         <v>125.4</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="W11" s="22">
         <v>0.99032258064503076</v>
@@ -10953,7 +10496,7 @@
         <v>78.2</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="W12" s="22">
         <v>0.50000000000009537</v>
@@ -11044,7 +10587,7 @@
         <v>180</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="W13" s="22">
         <v>3.1046953405016224</v>
@@ -11133,7 +10676,7 @@
         <v>460.00000000000006</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="W14" s="22">
         <v>2.723333333333263</v>
@@ -11224,7 +10767,7 @@
         <v>457</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="W15" s="22">
         <v>3.7199999999998568</v>
@@ -11313,7 +10856,7 @@
         <v>457.5</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="W16" s="22">
         <v>1.25161290322564</v>
@@ -12472,7 +12015,7 @@
         <v>924</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="W29" s="22">
         <v>17.812903225806423</v>
@@ -12561,7 +12104,7 @@
         <v>400</v>
       </c>
       <c r="V30" s="5" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="W30" s="22">
         <v>1.4549999999997472</v>
@@ -12650,7 +12193,7 @@
         <v>877</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="W31" s="22">
         <v>27.430000000000138</v>
@@ -13095,7 +12638,7 @@
         <v>187.99999999999997</v>
       </c>
       <c r="V36" s="5" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="W36" s="22">
         <v>1.1333333333335343</v>
@@ -13184,7 +12727,7 @@
         <v>171.00000000000009</v>
       </c>
       <c r="V37" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="W37" s="22">
         <v>1.0933333333336275</v>
@@ -13273,7 +12816,7 @@
         <v>314.99999999999994</v>
       </c>
       <c r="V38" s="5" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="W38" s="22">
         <v>1.4544444444442524</v>
@@ -13362,7 +12905,7 @@
         <v>913.99999999999989</v>
       </c>
       <c r="V39" s="5" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="W39" s="22">
         <v>6.2937499999997648</v>
@@ -13451,7 +12994,7 @@
         <v>671.99999999999989</v>
       </c>
       <c r="V40" s="5" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="W40" s="22">
         <v>2.1166666666663523</v>
@@ -13540,7 +13083,7 @@
         <v>862.33</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="W41" s="22">
         <v>2.4999999999999369</v>
@@ -13718,7 +13261,7 @@
         <v>169.00000000000003</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="W43" s="22">
         <v>0.56333333333308622</v>
@@ -13807,7 +13350,7 @@
         <v>445.00000000000011</v>
       </c>
       <c r="V44" s="5" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="W44" s="22">
         <v>1.2199999999997619</v>
@@ -13896,7 +13439,7 @@
         <v>632.99999999999989</v>
       </c>
       <c r="V45" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="W45" s="22">
         <v>1.2000000000000455</v>
@@ -13985,7 +13528,7 @@
         <v>603.99999999999989</v>
       </c>
       <c r="V46" s="5" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="W46" s="22">
         <v>0.79666666666658636</v>
@@ -14074,7 +13617,7 @@
         <v>309.00000000000006</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="W47" s="22">
         <v>0.81333333333333258</v>
@@ -14163,7 +13706,7 @@
         <v>1748</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="W48" s="22">
         <v>4.956666666666365</v>
@@ -14341,7 +13884,7 @@
         <v>1755.9999999999998</v>
       </c>
       <c r="V50" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="W50" s="22">
         <v>9.8999999999999009</v>
@@ -14430,7 +13973,7 @@
         <v>781</v>
       </c>
       <c r="V51" s="5" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="W51" s="22">
         <v>1.9193548387096737</v>
@@ -14519,7 +14062,7 @@
         <v>756.99999999999989</v>
       </c>
       <c r="V52" s="5" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="W52" s="22">
         <v>1.8777777777777436</v>
@@ -14608,7 +14151,7 @@
         <v>874</v>
       </c>
       <c r="V53" s="5" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="W53" s="22">
         <v>3.9393939393938018</v>
@@ -14697,7 +14240,7 @@
         <v>1754.67</v>
       </c>
       <c r="V54" s="5" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="W54" s="22">
         <v>14.73666666666702</v>
@@ -14786,7 +14329,7 @@
         <v>1766</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="W55" s="22">
         <v>4.1111111111110032</v>
@@ -14990,10 +14533,10 @@
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" s="13">
         <v>45098</v>
@@ -15053,7 +14596,7 @@
         <v>902.99999999999989</v>
       </c>
       <c r="V58" s="5" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="W58" s="22">
         <v>2.23111111111128</v>
@@ -15079,10 +14622,10 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" s="13">
         <v>45098</v>
@@ -15143,7 +14686,7 @@
         <v>718.33</v>
       </c>
       <c r="V59" s="5" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="W59" s="22">
         <v>1.832258064516443</v>
@@ -15169,10 +14712,10 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C60" s="13">
         <v>45098</v>
@@ -15232,7 +14775,7 @@
         <v>650</v>
       </c>
       <c r="V60" s="5" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="W60" s="22">
         <v>1.5031249999997165</v>
@@ -15258,10 +14801,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61" s="13">
         <v>45098</v>
@@ -15321,7 +14864,7 @@
         <v>413.99999999999994</v>
       </c>
       <c r="V61" s="5" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="W61" s="22">
         <v>0.97509632616516206</v>
@@ -15347,10 +14890,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" s="13">
         <v>45098</v>
@@ -15411,7 +14954,7 @@
         <v>367.99999999999994</v>
       </c>
       <c r="V62" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="W62" s="22">
         <v>0.93333333333352664</v>
@@ -15437,10 +14980,10 @@
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" s="13">
         <v>45098</v>
@@ -15526,10 +15069,10 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C64" s="13">
         <v>45306</v>
@@ -15587,7 +15130,7 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="23" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="W64" s="22">
         <v>2.51612903225816</v>
@@ -15613,10 +15156,10 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C65" s="13">
         <v>45306</v>
@@ -15674,7 +15217,7 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="23" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="W65" s="22">
         <v>19.096774193548345</v>
@@ -15700,10 +15243,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C66" s="13">
         <v>45306</v>
@@ -15787,10 +15330,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C67" s="13">
         <v>45307</v>
@@ -15848,7 +15391,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="23" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="W67" s="22">
         <v>0.55000000000025773</v>
@@ -15874,10 +15417,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C68" s="13">
         <v>45307</v>
@@ -15937,7 +15480,7 @@
         <v>436</v>
       </c>
       <c r="V68" s="23" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="W68" s="22">
         <v>0.52459999999999996</v>
@@ -15963,10 +15506,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C69" s="13">
         <v>45307</v>
@@ -16026,7 +15569,7 @@
         <v>495</v>
       </c>
       <c r="V69" s="23" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="W69" s="22">
         <v>0.50000000000009537</v>
@@ -16052,10 +15595,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C70" s="13">
         <v>45307</v>
@@ -16113,7 +15656,7 @@
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="23" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="W70" s="22">
         <v>0.67096774193575381</v>
@@ -16139,10 +15682,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C71" s="13">
         <v>45307</v>
@@ -16200,7 +15743,7 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="23" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="W71" s="22">
         <v>0.643750000000054</v>
@@ -16226,10 +15769,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C72" s="13">
         <v>45307</v>
@@ -16287,7 +15830,7 @@
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="23" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="W72" s="22">
         <v>110.50000000000011</v>
@@ -16313,10 +15856,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C73" s="13">
         <v>45307</v>
@@ -16374,7 +15917,7 @@
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="23" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="W73" s="22">
         <v>0.64193548387096155</v>
@@ -16400,10 +15943,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C74" s="13">
         <v>45307</v>
@@ -16461,7 +16004,7 @@
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="23" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="W74" s="22">
         <v>79.343333333333277</v>
@@ -16487,10 +16030,10 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C75" s="13">
         <v>45307</v>
@@ -16550,7 +16093,7 @@
         <v>5439.9999999999991</v>
       </c>
       <c r="V75" s="23" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="W75" s="22">
         <v>216.45199134199115</v>
@@ -16576,10 +16119,10 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C76" s="13">
         <v>45307</v>
@@ -16637,7 +16180,7 @@
         <v>1016</v>
       </c>
       <c r="V76" s="23" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="W76" s="22">
         <v>0.60303030303029714</v>
@@ -16663,10 +16206,10 @@
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C77" s="13">
         <v>45307</v>
@@ -16726,7 +16269,7 @@
         <v>2375</v>
       </c>
       <c r="V77" s="23" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="W77" s="22">
         <v>48.758620689655217</v>
@@ -16752,10 +16295,10 @@
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C78" s="13">
         <v>45307</v>
@@ -16815,7 +16358,7 @@
         <v>685</v>
       </c>
       <c r="V78" s="23" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="W78" s="22">
         <v>136.87692307692299</v>
@@ -16841,10 +16384,10 @@
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C79" s="13">
         <v>45313</v>
@@ -16904,7 +16447,7 @@
         <v>296.00000000000006</v>
       </c>
       <c r="V79" s="23" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="W79" s="22">
         <v>1.1862068965516548</v>
@@ -16930,10 +16473,10 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C80" s="13">
         <v>45313</v>
@@ -16993,7 +16536,7 @@
         <v>260.00000000000006</v>
       </c>
       <c r="V80" s="23" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="W80" s="22">
         <v>1.2645161290320615</v>
@@ -17019,10 +16562,10 @@
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C81" s="13">
         <v>45313</v>
@@ -17082,7 +16625,7 @@
         <v>2103.3333333333335</v>
       </c>
       <c r="V81" s="23" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="W81" s="22">
         <v>4.5483870967743663</v>
@@ -17108,10 +16651,10 @@
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C82" s="13">
         <v>45314</v>
@@ -17171,7 +16714,7 @@
         <v>236.00000000000003</v>
       </c>
       <c r="V82" s="23" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="W82" s="22">
         <v>0.70909090909097905</v>
@@ -17197,10 +16740,10 @@
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C83" s="13">
         <v>45314</v>
@@ -17260,7 +16803,7 @@
         <v>294.00000000000006</v>
       </c>
       <c r="V83" s="23" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="W83" s="22">
         <v>0.71999999999997988</v>
@@ -17286,10 +16829,10 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C84" s="13">
         <v>45314</v>
@@ -17349,7 +16892,7 @@
         <v>4746.666666666667</v>
       </c>
       <c r="V84" s="23" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="W84" s="22">
         <v>37.889841269841206</v>
@@ -17375,10 +16918,10 @@
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C85" s="13">
         <v>45320</v>
@@ -17438,7 +16981,7 @@
         <v>108.99999999999999</v>
       </c>
       <c r="V85" s="23" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="W85" s="22">
         <v>0.87419354838700769</v>
@@ -17464,10 +17007,10 @@
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C86" s="13">
         <v>45320</v>
@@ -17527,7 +17070,7 @@
         <v>795.00000000000034</v>
       </c>
       <c r="V86" s="23" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="W86" s="22">
         <v>10.465624999999923</v>
@@ -17553,10 +17096,10 @@
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C87" s="13">
         <v>45320</v>
@@ -17587,10 +17130,10 @@
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C88" s="13">
         <v>45320</v>
@@ -17650,7 +17193,7 @@
         <v>83</v>
       </c>
       <c r="V88" s="23" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="W88" s="22">
         <v>0.6062500000001414</v>
@@ -17676,10 +17219,10 @@
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C89" s="13">
         <v>45320</v>
@@ -17739,7 +17282,7 @@
         <v>2429.9999999999995</v>
       </c>
       <c r="V89" s="23" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="W89" s="22">
         <v>110.45000000000016</v>
@@ -17765,10 +17308,10 @@
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C90" s="13">
         <v>45320</v>
@@ -17799,10 +17342,10 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C91" s="13">
         <v>45321</v>
@@ -17862,7 +17405,7 @@
         <v>340.00000000000006</v>
       </c>
       <c r="V91" s="23" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="W91" s="22">
         <v>0.75937499999989555</v>
@@ -17888,10 +17431,10 @@
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C92" s="13">
         <v>45321</v>
@@ -17951,7 +17494,7 @@
         <v>255.99999999999994</v>
       </c>
       <c r="V92" s="23" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="W92" s="22">
         <v>0.75333333333347241</v>
@@ -17977,10 +17520,10 @@
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C93" s="13">
         <v>45321</v>
@@ -18040,7 +17583,7 @@
         <v>3620</v>
       </c>
       <c r="V93" s="23" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="W93" s="22">
         <v>27.085714285714094</v>
@@ -18066,10 +17609,10 @@
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C94" s="13">
         <v>45321</v>
@@ -18129,7 +17672,7 @@
         <v>671</v>
       </c>
       <c r="V94" s="23" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="W94" s="22">
         <v>2.4827586206895043</v>
@@ -18155,10 +17698,10 @@
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C95" s="13">
         <v>45321</v>
@@ -18218,7 +17761,7 @@
         <v>597</v>
       </c>
       <c r="V95" s="23" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="W95" s="22">
         <v>1.0322580645162445</v>
@@ -18244,10 +17787,10 @@
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C96" s="13">
         <v>45321</v>
@@ -18307,7 +17850,7 @@
         <v>6336.666666666667</v>
       </c>
       <c r="V96" s="23" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="W96" s="22">
         <v>13.079063146997981</v>
@@ -18333,10 +17876,10 @@
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C97" s="13">
         <v>45321</v>
@@ -18396,7 +17939,7 @@
         <v>417</v>
       </c>
       <c r="V97" s="23" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="W97" s="22">
         <v>1.403333333333497</v>
@@ -18422,10 +17965,10 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C98" s="13">
         <v>45321</v>
@@ -18485,7 +18028,7 @@
         <v>238.99999999999997</v>
       </c>
       <c r="V98" s="23" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="W98" s="22">
         <v>1.0333333333332935</v>
@@ -18511,10 +18054,10 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C99" s="13">
         <v>45321</v>
@@ -18600,10 +18143,10 @@
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C100" s="13">
         <v>45327</v>
@@ -18663,7 +18206,7 @@
         <v>2530</v>
       </c>
       <c r="V100" s="23" t="s">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="W100" s="22">
         <v>42.168965517241475</v>
@@ -18689,10 +18232,10 @@
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C101" s="13">
         <v>45327</v>
@@ -18750,7 +18293,7 @@
         <v>7460</v>
       </c>
       <c r="V101" s="23" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="W101" s="22">
         <v>29.444444444444507</v>
@@ -18776,10 +18319,10 @@
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C102" s="13">
         <v>45327</v>
@@ -18810,10 +18353,10 @@
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C103" s="13">
         <v>45328</v>
@@ -18873,7 +18416,7 @@
         <v>1325</v>
       </c>
       <c r="V103" s="23" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="W103" s="22">
         <v>7.5764705882354004</v>
@@ -18899,10 +18442,10 @@
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C104" s="13">
         <v>45328</v>
@@ -18962,7 +18505,7 @@
         <v>960.00000000000034</v>
       </c>
       <c r="V104" s="23" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="W104" s="22">
         <v>1.0531250000000991</v>
@@ -18988,10 +18531,10 @@
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C105" s="13">
         <v>45328</v>
@@ -19051,7 +18594,7 @@
         <v>5140.0000000000009</v>
       </c>
       <c r="V105" s="23" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="W105" s="22">
         <v>138.51052631578958</v>
@@ -19077,10 +18620,10 @@
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C106" s="13">
         <v>45328</v>
@@ -19140,7 +18683,7 @@
         <v>2189.9999999999995</v>
       </c>
       <c r="V106" s="23" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="W106" s="22">
         <v>36.022727272727131</v>
@@ -19166,10 +18709,10 @@
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C107" s="13">
         <v>45328</v>
@@ -19229,7 +18772,7 @@
         <v>7280</v>
       </c>
       <c r="V107" s="23" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="W107" s="22">
         <v>126.63333333333307</v>
@@ -19255,10 +18798,10 @@
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C108" s="13">
         <v>45328</v>
@@ -19289,10 +18832,10 @@
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C109" s="13">
         <v>45334</v>
@@ -19352,7 +18895,7 @@
         <v>95.499999999999957</v>
       </c>
       <c r="V109" s="23" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="W109" s="22">
         <v>0.59687500000005222</v>
@@ -19378,10 +18921,10 @@
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C110" s="13">
         <v>45334</v>
@@ -19441,7 +18984,7 @@
         <v>64.5</v>
       </c>
       <c r="V110" s="23" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="W110" s="22">
         <v>0.53225806451614921</v>
@@ -19467,10 +19010,10 @@
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C111" s="13">
         <v>45334</v>
@@ -19530,7 +19073,7 @@
         <v>1359.9999999999998</v>
       </c>
       <c r="V111" s="23" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="W111" s="22">
         <v>25.639999999999926</v>
@@ -19556,10 +19099,10 @@
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="C112" s="13">
         <v>45334</v>
@@ -19619,7 +19162,7 @@
         <v>139</v>
       </c>
       <c r="V112" s="23" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="W112" s="22">
         <v>1.0555555555554639</v>
@@ -19645,10 +19188,10 @@
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="C113" s="13">
         <v>45334</v>
@@ -19708,7 +19251,7 @@
         <v>147.5</v>
       </c>
       <c r="V113" s="23" t="s">
-        <v>395</v>
+        <v>366</v>
       </c>
       <c r="W113" s="22">
         <v>0.95000000000000639</v>
@@ -19734,10 +19277,10 @@
     </row>
     <row r="114" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="C114" s="13">
         <v>45334</v>
@@ -19797,7 +19340,7 @@
         <v>124.00000000000001</v>
       </c>
       <c r="V114" s="23" t="s">
-        <v>396</v>
+        <v>367</v>
       </c>
       <c r="W114" s="22">
         <v>0.82999999999984198</v>
@@ -19823,10 +19366,10 @@
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C115" s="13">
         <v>45335</v>
@@ -19886,7 +19429,7 @@
         <v>2770</v>
       </c>
       <c r="V115" s="23" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="W115" s="22">
         <v>8.7866666666665569</v>
@@ -19912,10 +19455,10 @@
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C116" s="13">
         <v>45335</v>
@@ -19975,7 +19518,7 @@
         <v>2929.9999999999995</v>
       </c>
       <c r="V116" s="23" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="W116" s="22">
         <v>6.4066666666666565</v>
@@ -20001,10 +19544,10 @@
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="C117" s="13">
         <v>45335</v>
@@ -20064,7 +19607,7 @@
         <v>2719.9999999999995</v>
       </c>
       <c r="V117" s="23" t="s">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="W117" s="22">
         <v>14.151808278867122</v>
@@ -20090,10 +19633,10 @@
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C118" s="13">
         <v>45335</v>
@@ -20179,10 +19722,10 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C119" s="13">
         <v>45335</v>
@@ -20242,7 +19785,7 @@
         <v>305.99999999999994</v>
       </c>
       <c r="V119" s="23" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="W119" s="22">
         <v>2.8219999999999619</v>
@@ -20268,10 +19811,10 @@
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C120" s="13">
         <v>45335</v>
@@ -20331,7 +19874,7 @@
         <v>1980.0000000000005</v>
       </c>
       <c r="V120" s="23" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="W120" s="22">
         <v>95.649999999999835</v>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="661" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="661"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="324">
   <si>
     <t>pH</t>
   </si>
@@ -82,15 +82,6 @@
     <t>Saanich</t>
   </si>
   <si>
-    <t>Old pipe, holding tank with pump, suspects leaking groundwater in winter, contents of tank very clear</t>
-  </si>
-  <si>
-    <t>Septic field above - pumps up, 6 bathrooms, 2 kitchens, second chamber sampled</t>
-  </si>
-  <si>
-    <t>Cement lined lid, two chambered</t>
-  </si>
-  <si>
     <t>05-SSI-19042023</t>
   </si>
   <si>
@@ -115,15 +106,6 @@
     <t>4b</t>
   </si>
   <si>
-    <t>Thick scum layer</t>
-  </si>
-  <si>
-    <t>Pump issue, pink scum layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household, small pink scum layer </t>
-  </si>
-  <si>
     <t>09-PL-09052023</t>
   </si>
   <si>
@@ -139,12 +121,6 @@
     <t>School</t>
   </si>
   <si>
-    <t>Sampled from aerobic settling chamber - see image of layout taken from control box. pH probe was not reading right - offset by a factor of 2 likely due to a loose connection</t>
-  </si>
-  <si>
-    <t>Scum layer had floating solids</t>
-  </si>
-  <si>
     <t>6a</t>
   </si>
   <si>
@@ -181,15 +157,6 @@
     <t>Office building</t>
   </si>
   <si>
-    <t xml:space="preserve">Community Hall Pender Island </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Library Pender </t>
-  </si>
-  <si>
     <t>16-DC-07062023</t>
   </si>
   <si>
@@ -220,18 +187,6 @@
     <t>9c</t>
   </si>
   <si>
-    <t>Household deep cove</t>
-  </si>
-  <si>
-    <t>really old tank household deep cove</t>
-  </si>
-  <si>
-    <t>Pender Island household</t>
-  </si>
-  <si>
-    <t>Could not measure volume; double thick scum layer</t>
-  </si>
-  <si>
     <t>21-PI-21062023</t>
   </si>
   <si>
@@ -247,12 +202,6 @@
     <t>Metchosin</t>
   </si>
   <si>
-    <t>Golf Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old tank </t>
-  </si>
-  <si>
     <t>Salt Spring Island</t>
   </si>
   <si>
@@ -274,9 +223,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Septic leach field </t>
-  </si>
-  <si>
     <t>Cistern flush</t>
   </si>
   <si>
@@ -289,24 +235,15 @@
     <t>Toilet Bathing Laundry Kitchen</t>
   </si>
   <si>
-    <t>Tap inside building</t>
-  </si>
-  <si>
     <t>More than 10 years old</t>
   </si>
   <si>
     <t>Technician/Mason</t>
   </si>
   <si>
-    <t xml:space="preserve">Leach field - second tank is aerated </t>
-  </si>
-  <si>
     <t>Bleach, CLR</t>
   </si>
   <si>
-    <t xml:space="preserve">Drainage field </t>
-  </si>
-  <si>
     <t>Kitchen Laundry Bathing Toilet</t>
   </si>
   <si>
@@ -361,9 +298,6 @@
     <t xml:space="preserve">Pro-pump septic packets </t>
   </si>
   <si>
-    <t>Leach</t>
-  </si>
-  <si>
     <t xml:space="preserve">Regular cleaners </t>
   </si>
   <si>
@@ -385,18 +319,6 @@
     <t>Toilet Laundry Kitchen</t>
   </si>
   <si>
-    <t xml:space="preserve">Thick scum layer, two households connected (one main and one airbnb, equalization tank pumps both to septic field. </t>
-  </si>
-  <si>
-    <t>Commercial place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very shallow, only took one sample, bio additives added. </t>
-  </si>
-  <si>
-    <t>Thick scum, bio additives added</t>
-  </si>
-  <si>
     <t>38.7</t>
   </si>
   <si>
@@ -604,9 +526,6 @@
     <t>water_connection</t>
   </si>
   <si>
-    <t>where</t>
-  </si>
-  <si>
     <t>tap_inside_building</t>
   </si>
   <si>
@@ -637,9 +556,6 @@
     <t>type</t>
   </si>
   <si>
-    <t>notes</t>
-  </si>
-  <si>
     <t>area</t>
   </si>
   <si>
@@ -898,12 +814,6 @@
     <t>Kitchen Bathing Laundry</t>
   </si>
   <si>
-    <t>Tap inside building Standpipe outside building</t>
-  </si>
-  <si>
-    <t>Standpipe outside building</t>
-  </si>
-  <si>
     <t>1 - 5 years old</t>
   </si>
   <si>
@@ -947,63 +857,6 @@
   </si>
   <si>
     <t>Plastic and feminine products</t>
-  </si>
-  <si>
-    <t>Guesthouse - Destiny</t>
-  </si>
-  <si>
-    <t>4 tanks in one compound - large tank</t>
-  </si>
-  <si>
-    <t>4 tanks compound - 2nd tank</t>
-  </si>
-  <si>
-    <t>4 tank compound - first of two connected tanks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 tank compound - 2nd of divided tanks </t>
-  </si>
-  <si>
-    <t>Apartments "sandec"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eric's place </t>
-  </si>
-  <si>
-    <t>Apartments - Barber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hostel - Fatuma </t>
-  </si>
-  <si>
-    <t>Apartments - two tanks (grey water)</t>
-  </si>
-  <si>
-    <t>Apartments - Two tanks (blackwater)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hostel - Elizabeth exotic </t>
-  </si>
-  <si>
-    <t>Chairman's place</t>
-  </si>
-  <si>
-    <t>Old lady's house</t>
-  </si>
-  <si>
-    <t>Boda boda house</t>
-  </si>
-  <si>
-    <t>Guesthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert's place </t>
-  </si>
-  <si>
-    <t>MLK Hostel</t>
-  </si>
-  <si>
-    <t>Open houses</t>
   </si>
   <si>
     <t>18-KK130202024</t>
@@ -1613,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO42"/>
+  <dimension ref="A1:AM42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" bestFit="1" customWidth="1"/>
@@ -1627,6 +1480,7 @@
     <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.90625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.36328125" bestFit="1" customWidth="1"/>
@@ -1642,146 +1496,138 @@
     <col min="26" max="27" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="7" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="41.7265625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="146.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="41.7265625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="35.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="AA1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="AB1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="AC1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="AD1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="AE1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="AF1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
@@ -1792,7 +1638,7 @@
         <v>45022</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>12</v>
@@ -1804,34 +1650,37 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="M2" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="N2" t="s">
+        <v>60</v>
       </c>
       <c r="O2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" t="s">
         <v>77</v>
       </c>
-      <c r="P2" t="s">
-        <v>86</v>
-      </c>
       <c r="Q2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S2" s="12">
         <v>1</v>
@@ -1840,13 +1689,13 @@
         <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="X2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y2" s="12">
         <v>1</v>
@@ -1861,40 +1710,34 @@
         <v>1</v>
       </c>
       <c r="AC2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD2" s="12">
+        <v>1</v>
       </c>
       <c r="AE2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>65</v>
       </c>
       <c r="AG2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK2">
+        <v>66</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ2">
         <v>15</v>
       </c>
+      <c r="AK2" t="s">
+        <v>55</v>
+      </c>
       <c r="AL2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1905,7 +1748,7 @@
         <v>45022</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>12</v>
@@ -1917,34 +1760,37 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="M3" t="s">
-        <v>72</v>
+        <v>55</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
       </c>
       <c r="O3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P3" t="s">
         <v>77</v>
       </c>
-      <c r="P3" t="s">
-        <v>78</v>
-      </c>
       <c r="Q3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S3" s="12">
         <v>1</v>
@@ -1953,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="X3" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y3" s="12">
         <v>1</v>
@@ -1974,37 +1820,31 @@
         <v>1</v>
       </c>
       <c r="AC3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD3" s="12">
+        <v>1</v>
       </c>
       <c r="AE3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>65</v>
       </c>
       <c r="AG3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>77</v>
+        <v>66</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>55</v>
       </c>
       <c r="AL3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -2027,31 +1867,37 @@
         <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P4" t="s">
-        <v>88</v>
-      </c>
       <c r="Q4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R4" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S4" s="12">
         <v>1</v>
@@ -2060,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="Y4" s="12">
         <v>1</v>
@@ -2078,40 +1924,34 @@
         <v>1</v>
       </c>
       <c r="AC4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD4" s="12">
+        <v>1</v>
       </c>
       <c r="AE4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>65</v>
       </c>
       <c r="AG4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK4">
+        <v>66</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4">
         <v>5</v>
       </c>
+      <c r="AK4" t="s">
+        <v>55</v>
+      </c>
       <c r="AL4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2134,37 +1974,37 @@
         <v>6</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L5" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M5" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="O5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P5" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S5" s="12">
         <v>1</v>
@@ -2173,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X5" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="Y5" s="12">
         <v>1</v>
@@ -2191,51 +2031,45 @@
         <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD5" s="12">
+        <v>1</v>
       </c>
       <c r="AE5" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>65</v>
       </c>
       <c r="AG5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK5">
+        <v>66</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ5">
         <v>6</v>
       </c>
+      <c r="AK5" t="s">
+        <v>55</v>
+      </c>
       <c r="AL5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="13">
         <v>45035</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -2247,38 +2081,38 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" t="s">
+        <v>60</v>
+      </c>
+      <c r="P6" t="s">
         <v>72</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="Q6" t="s">
+        <v>61</v>
+      </c>
+      <c r="R6" t="s">
         <v>73</v>
       </c>
-      <c r="J6" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" t="s">
-        <v>75</v>
-      </c>
-      <c r="L6" t="s">
-        <v>90</v>
-      </c>
-      <c r="M6" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6" t="s">
-        <v>77</v>
-      </c>
-      <c r="O6" t="s">
-        <v>77</v>
-      </c>
-      <c r="P6" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>79</v>
-      </c>
-      <c r="R6" t="s">
-        <v>94</v>
-      </c>
       <c r="S6" s="12">
         <v>1</v>
       </c>
@@ -2286,10 +2120,10 @@
         <v>1</v>
       </c>
       <c r="U6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X6" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y6" s="12">
         <v>1</v>
@@ -2304,54 +2138,48 @@
         <v>1</v>
       </c>
       <c r="AC6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD6" s="12">
+        <v>1</v>
       </c>
       <c r="AE6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>65</v>
       </c>
       <c r="AG6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK6">
+        <v>66</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ6">
         <v>5</v>
       </c>
+      <c r="AK6" t="s">
+        <v>55</v>
+      </c>
       <c r="AL6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="13">
         <v>45035</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F7" s="6">
         <f>410</f>
@@ -2361,47 +2189,49 @@
         <f>1/12</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L7" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M7" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="O7" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="Q7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R7" t="s">
+        <v>62</v>
+      </c>
+      <c r="S7" s="12">
+        <v>1</v>
+      </c>
+      <c r="T7" s="12">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>55</v>
+      </c>
+      <c r="X7" t="s">
         <v>79</v>
       </c>
-      <c r="R7" t="s">
-        <v>80</v>
-      </c>
-      <c r="S7" s="12">
-        <v>1</v>
-      </c>
-      <c r="T7" s="12">
-        <v>0</v>
-      </c>
-      <c r="U7" t="s">
-        <v>72</v>
-      </c>
-      <c r="X7" t="s">
-        <v>100</v>
-      </c>
       <c r="Y7" s="12">
         <v>1</v>
       </c>
@@ -2415,45 +2245,39 @@
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD7" s="12">
+        <v>1</v>
       </c>
       <c r="AE7" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>65</v>
       </c>
       <c r="AG7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK7">
+        <v>76</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ7">
         <v>0.5</v>
       </c>
+      <c r="AK7" t="s">
+        <v>55</v>
+      </c>
       <c r="AL7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="13">
         <v>45042</v>
@@ -2471,37 +2295,37 @@
         <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J8" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K8" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L8" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M8" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" t="s">
         <v>77</v>
       </c>
-      <c r="O8" t="s">
-        <v>77</v>
-      </c>
-      <c r="P8" t="s">
-        <v>98</v>
-      </c>
       <c r="Q8" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R8" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S8" s="12">
         <v>1</v>
@@ -2510,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X8" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y8" s="12">
         <v>1</v>
@@ -2528,48 +2352,42 @@
         <v>1</v>
       </c>
       <c r="AC8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD8" s="12">
+        <v>1</v>
       </c>
       <c r="AE8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>65</v>
       </c>
       <c r="AG8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI8">
+        <v>66</v>
+      </c>
+      <c r="AH8">
         <v>4.5</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK8">
+      <c r="AI8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ8">
         <v>10</v>
       </c>
+      <c r="AK8" t="s">
+        <v>55</v>
+      </c>
       <c r="AL8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" s="13">
         <v>45042</v>
@@ -2587,96 +2405,93 @@
         <v>8</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+      <c r="O9" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" t="s">
         <v>74</v>
       </c>
-      <c r="K9" t="s">
+      <c r="Q9" t="s">
+        <v>61</v>
+      </c>
+      <c r="R9" t="s">
+        <v>62</v>
+      </c>
+      <c r="S9" s="12">
+        <v>1</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>55</v>
+      </c>
+      <c r="X9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y9" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="s">
         <v>75</v>
       </c>
-      <c r="L9" t="s">
+      <c r="AG9" t="s">
         <v>76</v>
       </c>
-      <c r="M9" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9" t="s">
-        <v>77</v>
-      </c>
-      <c r="O9" t="s">
-        <v>77</v>
-      </c>
-      <c r="P9" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>79</v>
-      </c>
-      <c r="R9" t="s">
-        <v>80</v>
-      </c>
-      <c r="S9" s="12">
-        <v>1</v>
-      </c>
-      <c r="T9" s="12">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>72</v>
-      </c>
-      <c r="X9" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y9" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>97</v>
+      <c r="AI9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>55</v>
       </c>
       <c r="AL9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C10" s="13">
         <v>45055</v>
@@ -2685,7 +2500,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F10" s="6">
         <v>304</v>
@@ -2693,34 +2508,36 @@
       <c r="G10" s="6">
         <v>2.5</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="K10" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L10" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" t="s">
         <v>72</v>
       </c>
-      <c r="N10" t="s">
-        <v>77</v>
-      </c>
-      <c r="O10" t="s">
-        <v>77</v>
-      </c>
-      <c r="P10" t="s">
-        <v>93</v>
-      </c>
       <c r="Q10" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R10" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S10" s="12">
         <v>1</v>
@@ -2729,10 +2546,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X10" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y10" s="12">
         <v>1</v>
@@ -2747,39 +2564,36 @@
         <v>1</v>
       </c>
       <c r="AC10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD10" s="12">
+        <v>1</v>
       </c>
       <c r="AE10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>65</v>
       </c>
       <c r="AG10" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>97</v>
+        <v>76</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>55</v>
       </c>
       <c r="AL10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C11" s="13">
         <v>45055</v>
@@ -2788,7 +2602,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F11" s="6">
         <v>368</v>
@@ -2796,34 +2610,36 @@
       <c r="G11" s="6">
         <v>3</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L11" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+      <c r="O11" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11" t="s">
         <v>72</v>
       </c>
-      <c r="N11" t="s">
-        <v>77</v>
-      </c>
-      <c r="O11" t="s">
-        <v>77</v>
-      </c>
-      <c r="P11" t="s">
-        <v>93</v>
-      </c>
       <c r="Q11" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R11" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S11" s="12">
         <v>1</v>
@@ -2832,10 +2648,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X11" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y11" s="12">
         <v>1</v>
@@ -2850,39 +2666,36 @@
         <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD11" s="12">
+        <v>1</v>
       </c>
       <c r="AE11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>65</v>
       </c>
       <c r="AG11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>97</v>
+        <v>76</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>55</v>
       </c>
       <c r="AL11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C12" s="13">
         <v>45071</v>
@@ -2900,38 +2713,38 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" t="s">
+        <v>60</v>
+      </c>
+      <c r="O12" t="s">
+        <v>60</v>
+      </c>
+      <c r="P12" t="s">
         <v>72</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="Q12" t="s">
+        <v>61</v>
+      </c>
+      <c r="R12" t="s">
         <v>73</v>
       </c>
-      <c r="J12" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" t="s">
-        <v>75</v>
-      </c>
-      <c r="L12" t="s">
-        <v>90</v>
-      </c>
-      <c r="M12" t="s">
-        <v>72</v>
-      </c>
-      <c r="N12" t="s">
-        <v>77</v>
-      </c>
-      <c r="O12" t="s">
-        <v>77</v>
-      </c>
-      <c r="P12" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>79</v>
-      </c>
-      <c r="R12" t="s">
-        <v>94</v>
-      </c>
       <c r="S12" s="12">
         <v>1</v>
       </c>
@@ -2939,16 +2752,16 @@
         <v>1</v>
       </c>
       <c r="U12" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="V12" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="W12" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="X12" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y12" s="12">
         <v>1</v>
@@ -2963,48 +2776,42 @@
         <v>1</v>
       </c>
       <c r="AC12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD12" s="12">
+        <v>1</v>
       </c>
       <c r="AE12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>65</v>
       </c>
       <c r="AG12" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI12">
+        <v>66</v>
+      </c>
+      <c r="AH12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK12">
+      <c r="AI12" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ12">
         <v>5.5</v>
       </c>
+      <c r="AK12" t="s">
+        <v>55</v>
+      </c>
       <c r="AL12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C13" s="13">
         <v>45071</v>
@@ -3022,34 +2829,37 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+      <c r="O13" t="s">
+        <v>60</v>
+      </c>
+      <c r="P13" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J13" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" t="s">
-        <v>90</v>
-      </c>
-      <c r="M13" t="s">
-        <v>72</v>
-      </c>
-      <c r="N13" t="s">
-        <v>77</v>
-      </c>
-      <c r="O13" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" t="s">
-        <v>93</v>
-      </c>
       <c r="Q13" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R13" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S13" s="12">
         <v>1</v>
@@ -3058,13 +2868,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="V13" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="X13" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y13" s="12">
         <v>1</v>
@@ -3079,54 +2889,48 @@
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD13" s="12">
+        <v>1</v>
       </c>
       <c r="AE13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>65</v>
       </c>
       <c r="AG13" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK13">
+        <v>76</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ13">
         <v>5</v>
       </c>
+      <c r="AK13" t="s">
+        <v>55</v>
+      </c>
       <c r="AL13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C14" s="13">
         <v>45077</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F14" s="6">
         <v>10</v>
@@ -3134,34 +2938,36 @@
       <c r="G14" s="6">
         <v>5</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K14" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L14" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" t="s">
+        <v>60</v>
+      </c>
+      <c r="O14" t="s">
+        <v>60</v>
+      </c>
+      <c r="P14" t="s">
         <v>72</v>
       </c>
-      <c r="N14" t="s">
-        <v>77</v>
-      </c>
-      <c r="O14" t="s">
-        <v>77</v>
-      </c>
-      <c r="P14" t="s">
-        <v>93</v>
-      </c>
       <c r="Q14" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R14" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S14" s="12">
         <v>1</v>
@@ -3170,10 +2976,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X14" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="Y14" s="12">
         <v>1</v>
@@ -3188,54 +2994,48 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD14" s="12">
+        <v>1</v>
       </c>
       <c r="AE14" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>65</v>
       </c>
       <c r="AG14" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI14">
+        <v>66</v>
+      </c>
+      <c r="AH14">
         <v>8</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK14">
+      <c r="AI14" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ14">
         <v>6</v>
       </c>
+      <c r="AK14" t="s">
+        <v>55</v>
+      </c>
       <c r="AL14" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C15" s="13">
         <v>45077</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
@@ -3247,37 +3047,37 @@
         <v>3</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" t="s">
+        <v>57</v>
+      </c>
+      <c r="K15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" t="s">
+        <v>60</v>
+      </c>
+      <c r="O15" t="s">
+        <v>60</v>
+      </c>
+      <c r="P15" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" t="s">
-        <v>74</v>
-      </c>
-      <c r="K15" t="s">
-        <v>75</v>
-      </c>
-      <c r="L15" t="s">
-        <v>90</v>
-      </c>
-      <c r="M15" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15" t="s">
-        <v>77</v>
-      </c>
-      <c r="O15" t="s">
-        <v>77</v>
-      </c>
-      <c r="P15" t="s">
-        <v>107</v>
-      </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R15" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S15" s="12">
         <v>1</v>
@@ -3286,13 +3086,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W15" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="X15" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y15" s="12">
         <v>1</v>
@@ -3307,54 +3107,48 @@
         <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD15" s="12">
+        <v>1</v>
       </c>
       <c r="AE15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>65</v>
       </c>
       <c r="AG15" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK15">
+        <v>66</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ15">
         <v>5.5</v>
       </c>
+      <c r="AK15" t="s">
+        <v>55</v>
+      </c>
       <c r="AL15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C16" s="13">
         <v>45077</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="F16" s="6">
         <v>10</v>
@@ -3362,44 +3156,49 @@
       <c r="G16" s="6">
         <v>0.5</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K16" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L16" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" t="s">
+        <v>60</v>
+      </c>
+      <c r="O16" t="s">
+        <v>60</v>
+      </c>
+      <c r="P16" t="s">
         <v>72</v>
       </c>
-      <c r="O16" t="s">
-        <v>77</v>
-      </c>
-      <c r="P16" t="s">
-        <v>93</v>
-      </c>
       <c r="Q16" t="s">
+        <v>61</v>
+      </c>
+      <c r="R16" t="s">
+        <v>73</v>
+      </c>
+      <c r="S16" s="12">
+        <v>1</v>
+      </c>
+      <c r="T16" s="12">
+        <v>1</v>
+      </c>
+      <c r="U16" t="s">
+        <v>55</v>
+      </c>
+      <c r="X16" t="s">
         <v>79</v>
       </c>
-      <c r="R16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S16" s="12">
-        <v>1</v>
-      </c>
-      <c r="T16" s="12">
-        <v>1</v>
-      </c>
-      <c r="U16" t="s">
-        <v>72</v>
-      </c>
-      <c r="X16" t="s">
-        <v>100</v>
-      </c>
       <c r="Y16" s="12">
         <v>1</v>
       </c>
@@ -3413,42 +3212,36 @@
         <v>0</v>
       </c>
       <c r="AC16" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD16" s="12">
+        <v>1</v>
       </c>
       <c r="AE16" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>65</v>
       </c>
       <c r="AG16" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>77</v>
+        <v>66</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>55</v>
       </c>
       <c r="AL16" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM16" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C17" s="13">
         <v>45084</v>
@@ -3466,37 +3259,37 @@
         <v>3.5</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J17" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K17" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L17" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N17" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="O17" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P17" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="Q17" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R17" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S17" s="12">
         <v>1</v>
@@ -3505,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X17" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y17" s="12">
         <v>1</v>
@@ -3523,45 +3316,39 @@
         <v>1</v>
       </c>
       <c r="AC17" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD17" s="12">
+        <v>1</v>
       </c>
       <c r="AE17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>65</v>
       </c>
       <c r="AG17" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK17">
+        <v>66</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ17">
         <v>4</v>
       </c>
+      <c r="AK17" t="s">
+        <v>55</v>
+      </c>
       <c r="AL17" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C18" s="13">
         <v>45084</v>
@@ -3579,37 +3366,37 @@
         <v>5</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J18" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K18" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L18" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M18" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N18" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="O18" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P18" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="Q18" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R18" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S18" s="12">
         <v>1</v>
@@ -3618,10 +3405,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X18" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y18" s="12">
         <v>1</v>
@@ -3636,51 +3423,45 @@
         <v>1</v>
       </c>
       <c r="AC18" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD18" s="12">
+        <v>1</v>
       </c>
       <c r="AE18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>65</v>
       </c>
       <c r="AG18" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK18">
+        <v>66</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ18">
         <v>5</v>
       </c>
+      <c r="AK18" t="s">
+        <v>55</v>
+      </c>
       <c r="AL18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C19" s="13">
         <v>45085</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>12</v>
@@ -3692,37 +3473,37 @@
         <v>2</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" t="s">
+        <v>69</v>
+      </c>
+      <c r="M19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" t="s">
+        <v>60</v>
+      </c>
+      <c r="O19" t="s">
+        <v>60</v>
+      </c>
+      <c r="P19" t="s">
         <v>72</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" t="s">
-        <v>75</v>
-      </c>
-      <c r="L19" t="s">
-        <v>90</v>
-      </c>
-      <c r="M19" t="s">
-        <v>72</v>
-      </c>
-      <c r="N19" t="s">
-        <v>77</v>
-      </c>
-      <c r="O19" t="s">
-        <v>77</v>
-      </c>
-      <c r="P19" t="s">
-        <v>93</v>
-      </c>
       <c r="Q19" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R19" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S19" s="12">
         <v>1</v>
@@ -3731,13 +3512,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="W19" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="X19" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y19" s="12">
         <v>1</v>
@@ -3752,51 +3533,45 @@
         <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD19" s="12">
+        <v>1</v>
       </c>
       <c r="AE19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>65</v>
       </c>
       <c r="AG19" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK19">
+        <v>66</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ19">
         <v>2.5</v>
       </c>
+      <c r="AK19" t="s">
+        <v>55</v>
+      </c>
       <c r="AL19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C20" s="13">
         <v>45085</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>12</v>
@@ -3808,37 +3583,37 @@
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J20" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K20" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L20" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" t="s">
+        <v>60</v>
+      </c>
+      <c r="O20" t="s">
+        <v>60</v>
+      </c>
+      <c r="P20" t="s">
         <v>72</v>
       </c>
-      <c r="N20" t="s">
-        <v>77</v>
-      </c>
-      <c r="O20" t="s">
-        <v>77</v>
-      </c>
-      <c r="P20" t="s">
-        <v>93</v>
-      </c>
       <c r="Q20" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R20" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="S20" s="12">
         <v>0</v>
@@ -3847,10 +3622,10 @@
         <v>1</v>
       </c>
       <c r="U20" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X20" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y20" s="12">
         <v>1</v>
@@ -3865,54 +3640,48 @@
         <v>1</v>
       </c>
       <c r="AC20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD20" s="12">
+        <v>1</v>
       </c>
       <c r="AE20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>65</v>
       </c>
       <c r="AG20" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI20">
+        <v>66</v>
+      </c>
+      <c r="AH20">
         <v>2.4</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK20">
+      <c r="AI20" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ20">
         <v>9.5</v>
       </c>
+      <c r="AK20" t="s">
+        <v>55</v>
+      </c>
       <c r="AL20" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM20" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C21" s="13">
         <v>45085</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>12</v>
@@ -3924,37 +3693,37 @@
         <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" t="s">
+        <v>69</v>
+      </c>
+      <c r="M21" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" t="s">
+        <v>60</v>
+      </c>
+      <c r="O21" t="s">
+        <v>60</v>
+      </c>
+      <c r="P21" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" t="s">
-        <v>74</v>
-      </c>
-      <c r="K21" t="s">
-        <v>75</v>
-      </c>
-      <c r="L21" t="s">
-        <v>90</v>
-      </c>
-      <c r="M21" t="s">
-        <v>72</v>
-      </c>
-      <c r="N21" t="s">
-        <v>77</v>
-      </c>
-      <c r="O21" t="s">
-        <v>77</v>
-      </c>
-      <c r="P21" t="s">
-        <v>93</v>
-      </c>
       <c r="Q21" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R21" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S21" s="12">
         <v>1</v>
@@ -3963,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X21" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y21" s="12">
         <v>1</v>
@@ -3981,57 +3750,51 @@
         <v>1</v>
       </c>
       <c r="AC21" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD21" s="12">
+        <v>1</v>
       </c>
       <c r="AE21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF21" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>65</v>
       </c>
       <c r="AG21" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI21">
+        <v>66</v>
+      </c>
+      <c r="AH21">
         <v>2.4</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK21">
+      <c r="AI21" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ21">
         <v>5</v>
       </c>
+      <c r="AK21" t="s">
+        <v>55</v>
+      </c>
       <c r="AL21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F22" s="6">
         <v>200</v>
@@ -4039,34 +3802,36 @@
       <c r="G22" s="6">
         <v>0.25</v>
       </c>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="I22" s="2"/>
       <c r="J22" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K22" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L22" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M22" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N22" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="O22" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P22" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="Q22" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R22" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S22" s="12">
         <v>1</v>
@@ -4075,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X22" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="Y22" s="12">
         <v>1</v>
@@ -4093,54 +3858,48 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD22" s="12">
+        <v>1</v>
       </c>
       <c r="AE22" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF22" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>65</v>
       </c>
       <c r="AG22" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI22">
+        <v>66</v>
+      </c>
+      <c r="AH22">
         <v>5</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK22">
+      <c r="AI22" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ22">
         <v>5.5</v>
       </c>
+      <c r="AK22" t="s">
+        <v>55</v>
+      </c>
       <c r="AL22" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM22" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
@@ -4152,37 +3911,37 @@
         <v>0.25</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" t="s">
+        <v>57</v>
+      </c>
+      <c r="K23" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" t="s">
+        <v>69</v>
+      </c>
+      <c r="M23" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" t="s">
+        <v>60</v>
+      </c>
+      <c r="O23" t="s">
+        <v>60</v>
+      </c>
+      <c r="P23" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" t="s">
-        <v>74</v>
-      </c>
-      <c r="K23" t="s">
-        <v>75</v>
-      </c>
-      <c r="L23" t="s">
-        <v>90</v>
-      </c>
-      <c r="M23" t="s">
-        <v>72</v>
-      </c>
-      <c r="N23" t="s">
-        <v>77</v>
-      </c>
-      <c r="O23" t="s">
-        <v>77</v>
-      </c>
-      <c r="P23" t="s">
-        <v>93</v>
-      </c>
       <c r="Q23" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R23" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="S23" s="12">
         <v>1</v>
@@ -4191,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X23" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="Y23" s="12">
         <v>1</v>
@@ -4209,51 +3968,45 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="AD23" s="12">
+        <v>1</v>
       </c>
       <c r="AE23" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>65</v>
       </c>
       <c r="AG23" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>77</v>
+        <v>66</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>55</v>
       </c>
       <c r="AL23" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM23" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F24" s="6">
         <v>23</v>
@@ -4262,35 +4015,35 @@
         <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K24" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L24" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M24" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N24" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O24" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q24" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R24" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S24" s="12">
         <v>1</v>
@@ -4299,13 +4052,13 @@
         <v>1</v>
       </c>
       <c r="U24" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W24" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X24" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="Y24" s="12">
         <v>1</v>
@@ -4320,48 +4073,45 @@
         <v>0</v>
       </c>
       <c r="AC24" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD24" s="12">
+        <v>1</v>
       </c>
       <c r="AE24" s="12">
         <v>1</v>
       </c>
-      <c r="AF24" s="12">
-        <v>1</v>
+      <c r="AF24" t="s">
+        <v>65</v>
       </c>
       <c r="AG24" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>97</v>
+        <v>76</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>55</v>
       </c>
       <c r="AL24" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>290</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.35">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -4373,37 +4123,37 @@
         <v>3</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K25" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L25" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M25" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N25" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O25" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P25" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q25" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R25" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S25" s="12">
         <v>1</v>
@@ -4412,13 +4162,13 @@
         <v>1</v>
       </c>
       <c r="U25" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W25" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X25" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="Y25" s="12">
         <v>1</v>
@@ -4433,54 +4183,48 @@
         <v>1</v>
       </c>
       <c r="AC25" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD25" s="12">
+        <v>1</v>
       </c>
       <c r="AE25" s="12">
         <v>1</v>
       </c>
-      <c r="AF25" s="12">
-        <v>1</v>
+      <c r="AF25" t="s">
+        <v>65</v>
       </c>
       <c r="AG25" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK25">
+        <v>76</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ25">
         <v>2</v>
       </c>
+      <c r="AK25" t="s">
+        <v>55</v>
+      </c>
       <c r="AL25" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>291</v>
-      </c>
-      <c r="AO25" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -4492,37 +4236,37 @@
         <v>3</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J26" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K26" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L26" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M26" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N26" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O26" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P26" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q26" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R26" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S26" s="12">
         <v>1</v>
@@ -4531,13 +4275,13 @@
         <v>1</v>
       </c>
       <c r="U26" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W26" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X26" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="Y26" s="12">
         <v>1</v>
@@ -4552,54 +4296,48 @@
         <v>1</v>
       </c>
       <c r="AC26" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD26" s="12">
+        <v>1</v>
       </c>
       <c r="AE26" s="12">
         <v>1</v>
       </c>
-      <c r="AF26" s="12">
-        <v>1</v>
+      <c r="AF26" t="s">
+        <v>65</v>
       </c>
       <c r="AG26" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK26">
+        <v>76</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ26">
         <v>2</v>
       </c>
+      <c r="AK26" t="s">
+        <v>55</v>
+      </c>
       <c r="AL26" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM26" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>291</v>
-      </c>
-      <c r="AO26" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -4611,37 +4349,37 @@
         <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J27" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K27" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L27" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M27" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N27" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O27" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P27" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q27" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R27" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S27" s="12">
         <v>1</v>
@@ -4650,13 +4388,13 @@
         <v>1</v>
       </c>
       <c r="U27" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W27" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X27" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="Y27" s="12">
         <v>1</v>
@@ -4671,54 +4409,48 @@
         <v>1</v>
       </c>
       <c r="AC27" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD27" s="12">
+        <v>1</v>
       </c>
       <c r="AE27" s="12">
         <v>1</v>
       </c>
-      <c r="AF27" s="12">
-        <v>1</v>
+      <c r="AF27" t="s">
+        <v>65</v>
       </c>
       <c r="AG27" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK27">
+        <v>76</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ27">
         <v>2</v>
       </c>
+      <c r="AK27" t="s">
+        <v>55</v>
+      </c>
       <c r="AL27" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>291</v>
-      </c>
-      <c r="AO27" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -4730,37 +4462,37 @@
         <v>3</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K28" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L28" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M28" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N28" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O28" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P28" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q28" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R28" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S28" s="12">
         <v>1</v>
@@ -4769,13 +4501,13 @@
         <v>1</v>
       </c>
       <c r="U28" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W28" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X28" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="Y28" s="12">
         <v>1</v>
@@ -4790,54 +4522,48 @@
         <v>1</v>
       </c>
       <c r="AC28" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD28" s="12">
+        <v>1</v>
       </c>
       <c r="AE28" s="12">
         <v>1</v>
       </c>
-      <c r="AF28" s="12">
-        <v>1</v>
+      <c r="AF28" t="s">
+        <v>65</v>
       </c>
       <c r="AG28" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK28">
+        <v>76</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ28">
         <v>2</v>
       </c>
+      <c r="AK28" t="s">
+        <v>55</v>
+      </c>
       <c r="AL28" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>292</v>
-      </c>
-      <c r="AO28" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -4849,37 +4575,37 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J29" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K29" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L29" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M29" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="N29" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O29" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P29" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q29" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R29" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S29" s="12">
         <v>1</v>
@@ -4888,13 +4614,13 @@
         <v>1</v>
       </c>
       <c r="U29" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W29" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X29" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="Y29" s="12">
         <v>1</v>
@@ -4909,51 +4635,45 @@
         <v>1</v>
       </c>
       <c r="AC29" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD29" s="12">
+        <v>1</v>
       </c>
       <c r="AE29" s="12">
         <v>1</v>
       </c>
-      <c r="AF29" s="12">
-        <v>1</v>
+      <c r="AF29" t="s">
+        <v>65</v>
       </c>
       <c r="AG29" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK29">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ29">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>55</v>
       </c>
       <c r="AL29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM29" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO29" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
@@ -4965,37 +4685,37 @@
         <v>10</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J30" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K30" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L30" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M30" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N30" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O30" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P30" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q30" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R30" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S30" s="12">
         <v>1</v>
@@ -5004,13 +4724,13 @@
         <v>1</v>
       </c>
       <c r="U30" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="W30" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="X30" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="Y30" s="12">
         <v>1</v>
@@ -5025,51 +4745,45 @@
         <v>1</v>
       </c>
       <c r="AC30" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD30" s="12">
+        <v>1</v>
       </c>
       <c r="AE30" s="12">
         <v>1</v>
       </c>
-      <c r="AF30" s="12">
-        <v>1</v>
+      <c r="AF30" t="s">
+        <v>258</v>
       </c>
       <c r="AG30" t="s">
-        <v>288</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>289</v>
+        <v>66</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>259</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>55</v>
       </c>
       <c r="AL30" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM30" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>293</v>
-      </c>
-      <c r="AO30" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -5081,37 +4795,37 @@
         <v>10</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K31" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L31" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M31" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N31" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O31" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P31" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q31" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R31" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S31" s="12">
         <v>1</v>
@@ -5120,10 +4834,10 @@
         <v>1</v>
       </c>
       <c r="U31" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="X31" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y31" s="12">
         <v>1</v>
@@ -5138,54 +4852,48 @@
         <v>1</v>
       </c>
       <c r="AC31" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD31" s="12">
+        <v>1</v>
       </c>
       <c r="AE31" s="12">
         <v>1</v>
       </c>
-      <c r="AF31" s="12">
-        <v>1</v>
+      <c r="AF31" t="s">
+        <v>258</v>
       </c>
       <c r="AG31" t="s">
-        <v>288</v>
-      </c>
-      <c r="AH31" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>289</v>
+        <v>76</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>259</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>55</v>
       </c>
       <c r="AL31" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>294</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.35">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F32" s="6">
         <v>35</v>
@@ -5194,35 +4902,35 @@
         <v>6</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K32" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="L32" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="M32" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N32" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O32" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P32" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q32" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R32" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S32" s="12">
         <v>1</v>
@@ -5230,11 +4938,14 @@
       <c r="T32" s="12">
         <v>1</v>
       </c>
+      <c r="U32" t="s">
+        <v>55</v>
+      </c>
       <c r="W32" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X32" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="Y32" s="12">
         <v>1</v>
@@ -5249,48 +4960,45 @@
         <v>0</v>
       </c>
       <c r="AC32" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD32" s="12">
+        <v>1</v>
       </c>
       <c r="AE32" s="12">
         <v>1</v>
       </c>
-      <c r="AF32" s="12">
-        <v>1</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK32">
+      <c r="AF32" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ32">
         <v>5</v>
       </c>
+      <c r="AK32" t="s">
+        <v>55</v>
+      </c>
       <c r="AL32" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM32" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>295</v>
-      </c>
-      <c r="AO32" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
@@ -5302,37 +5010,37 @@
         <v>2</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K33" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L33" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M33" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N33" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O33" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P33" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q33" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R33" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S33" s="12">
         <v>1</v>
@@ -5341,13 +5049,13 @@
         <v>1</v>
       </c>
       <c r="U33" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W33" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X33" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="Y33" s="12">
         <v>0</v>
@@ -5362,54 +5070,48 @@
         <v>1</v>
       </c>
       <c r="AC33" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD33" s="12">
+        <v>1</v>
       </c>
       <c r="AE33" s="12">
         <v>1</v>
       </c>
-      <c r="AF33" s="12">
-        <v>1</v>
+      <c r="AF33" t="s">
+        <v>65</v>
       </c>
       <c r="AG33" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI33">
+        <v>76</v>
+      </c>
+      <c r="AH33">
         <v>20</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK33">
+      <c r="AI33" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ33">
         <v>2</v>
       </c>
+      <c r="AK33" t="s">
+        <v>55</v>
+      </c>
       <c r="AL33" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM33" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO33" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -5421,53 +5123,53 @@
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J34" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K34" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L34" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M34" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N34" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O34" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P34" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q34" t="s">
+        <v>61</v>
+      </c>
+      <c r="R34" t="s">
+        <v>73</v>
+      </c>
+      <c r="S34" s="12">
+        <v>1</v>
+      </c>
+      <c r="T34" s="12">
+        <v>1</v>
+      </c>
+      <c r="U34" t="s">
+        <v>55</v>
+      </c>
+      <c r="W34" t="s">
+        <v>252</v>
+      </c>
+      <c r="X34" t="s">
         <v>79</v>
       </c>
-      <c r="R34" t="s">
-        <v>94</v>
-      </c>
-      <c r="S34" s="12">
-        <v>1</v>
-      </c>
-      <c r="T34" s="12">
-        <v>1</v>
-      </c>
-      <c r="U34" t="s">
-        <v>72</v>
-      </c>
-      <c r="W34" t="s">
-        <v>280</v>
-      </c>
-      <c r="X34" t="s">
-        <v>100</v>
-      </c>
       <c r="Y34" s="12">
         <v>1</v>
       </c>
@@ -5481,57 +5183,51 @@
         <v>0</v>
       </c>
       <c r="AC34" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD34" s="12">
+        <v>1</v>
       </c>
       <c r="AE34" s="12">
         <v>1</v>
       </c>
-      <c r="AF34" s="12">
-        <v>1</v>
+      <c r="AF34" t="s">
+        <v>65</v>
       </c>
       <c r="AG34" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK34">
+        <v>76</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ34">
         <v>2</v>
       </c>
+      <c r="AK34" t="s">
+        <v>55</v>
+      </c>
       <c r="AL34" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM34" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>296</v>
-      </c>
-      <c r="AO34" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F35" s="6">
         <v>88</v>
@@ -5540,32 +5236,32 @@
         <v>0.25</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K35" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L35" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M35" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N35" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O35" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="Q35" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R35" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S35" s="12">
         <v>1</v>
@@ -5574,13 +5270,13 @@
         <v>1</v>
       </c>
       <c r="U35" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="W35" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X35" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="Y35" s="12">
         <v>1</v>
@@ -5595,54 +5291,48 @@
         <v>1</v>
       </c>
       <c r="AC35" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD35" s="12">
+        <v>1</v>
       </c>
       <c r="AE35" s="12">
         <v>1</v>
       </c>
-      <c r="AF35" s="12">
-        <v>1</v>
+      <c r="AF35" t="s">
+        <v>65</v>
       </c>
       <c r="AG35" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK35">
+        <v>66</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ35">
         <v>0.33</v>
       </c>
+      <c r="AK35" t="s">
+        <v>55</v>
+      </c>
       <c r="AL35" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM35" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>297</v>
-      </c>
-      <c r="AO35" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -5654,114 +5344,108 @@
         <v>3</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J36" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K36" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" t="s">
+        <v>69</v>
+      </c>
+      <c r="M36" t="s">
+        <v>55</v>
+      </c>
+      <c r="N36" t="s">
+        <v>55</v>
+      </c>
+      <c r="O36" t="s">
+        <v>60</v>
+      </c>
+      <c r="P36" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>250</v>
+      </c>
+      <c r="R36" t="s">
+        <v>73</v>
+      </c>
+      <c r="S36" s="12">
+        <v>1</v>
+      </c>
+      <c r="T36" s="12">
+        <v>1</v>
+      </c>
+      <c r="U36" t="s">
+        <v>55</v>
+      </c>
+      <c r="W36" t="s">
+        <v>252</v>
+      </c>
+      <c r="X36" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y36" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="s">
         <v>75</v>
       </c>
-      <c r="L36" t="s">
-        <v>90</v>
-      </c>
-      <c r="M36" t="s">
-        <v>72</v>
-      </c>
-      <c r="N36" t="s">
-        <v>72</v>
-      </c>
-      <c r="O36" t="s">
-        <v>77</v>
-      </c>
-      <c r="P36" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>278</v>
-      </c>
-      <c r="R36" t="s">
-        <v>94</v>
-      </c>
-      <c r="S36" s="12">
-        <v>1</v>
-      </c>
-      <c r="T36" s="12">
-        <v>1</v>
-      </c>
-      <c r="U36" t="s">
-        <v>72</v>
-      </c>
-      <c r="W36" t="s">
-        <v>280</v>
-      </c>
-      <c r="X36" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y36" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>287</v>
-      </c>
-      <c r="AE36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="12">
-        <v>1</v>
-      </c>
       <c r="AG36" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK36">
+        <v>66</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ36">
         <v>6</v>
       </c>
+      <c r="AK36" t="s">
+        <v>55</v>
+      </c>
       <c r="AL36" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM36" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>298</v>
-      </c>
-      <c r="AO36" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -5773,37 +5457,37 @@
         <v>3</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J37" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K37" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L37" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M37" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="N37" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O37" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P37" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q37" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R37" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S37" s="12">
         <v>1</v>
@@ -5812,13 +5496,13 @@
         <v>1</v>
       </c>
       <c r="U37" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="W37" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X37" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="Y37" s="12">
         <v>1</v>
@@ -5833,51 +5517,45 @@
         <v>1</v>
       </c>
       <c r="AC37" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD37" s="12">
+        <v>1</v>
       </c>
       <c r="AE37" s="12">
         <v>1</v>
       </c>
-      <c r="AF37" s="12">
-        <v>1</v>
+      <c r="AF37" t="s">
+        <v>65</v>
       </c>
       <c r="AG37" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH37" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK37">
+        <v>66</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ37">
         <v>5</v>
       </c>
+      <c r="AK37" t="s">
+        <v>55</v>
+      </c>
       <c r="AL37" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM37" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO37" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -5889,37 +5567,37 @@
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J38" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K38" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L38" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M38" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N38" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O38" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P38" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q38" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="R38" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S38" s="12">
         <v>1</v>
@@ -5927,11 +5605,14 @@
       <c r="T38" s="12">
         <v>1</v>
       </c>
+      <c r="U38" t="s">
+        <v>55</v>
+      </c>
       <c r="W38" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X38" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="Y38" s="12">
         <v>1</v>
@@ -5946,51 +5627,48 @@
         <v>0</v>
       </c>
       <c r="AC38" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>287</v>
+        <v>60</v>
+      </c>
+      <c r="AD38" s="12">
+        <v>0</v>
       </c>
       <c r="AE38" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="12">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>65</v>
       </c>
       <c r="AG38" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>85</v>
+        <v>66</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>55</v>
       </c>
       <c r="AL38" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM38" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN38" t="s">
-        <v>299</v>
-      </c>
-      <c r="AO38" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F39" s="6">
         <v>10</v>
@@ -5999,35 +5677,35 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K39" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L39" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M39" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="N39" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O39" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P39" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q39" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R39" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S39" s="12">
         <v>1</v>
@@ -6035,11 +5713,14 @@
       <c r="T39" s="12">
         <v>1</v>
       </c>
+      <c r="U39" t="s">
+        <v>55</v>
+      </c>
       <c r="W39" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X39" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="Y39" s="12">
         <v>1</v>
@@ -6054,54 +5735,48 @@
         <v>0</v>
       </c>
       <c r="AC39" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD39" s="12">
+        <v>1</v>
       </c>
       <c r="AE39" s="12">
         <v>1</v>
       </c>
-      <c r="AF39" s="12">
-        <v>1</v>
+      <c r="AF39" t="s">
+        <v>65</v>
       </c>
       <c r="AG39" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK39">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ39">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>55</v>
       </c>
       <c r="AL39" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM39" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN39" t="s">
-        <v>300</v>
-      </c>
-      <c r="AO39" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -6113,34 +5788,34 @@
         <v>1</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J40" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K40" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L40" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M40" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N40" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O40" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="Q40" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="R40" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S40" s="12">
         <v>1</v>
@@ -6149,13 +5824,13 @@
         <v>1</v>
       </c>
       <c r="U40" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="W40" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X40" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="Y40" s="12">
         <v>1</v>
@@ -6170,57 +5845,51 @@
         <v>0</v>
       </c>
       <c r="AC40" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>286</v>
+        <v>60</v>
+      </c>
+      <c r="AD40" s="12">
+        <v>1</v>
       </c>
       <c r="AE40" s="12">
         <v>1</v>
       </c>
-      <c r="AF40" s="12">
-        <v>1</v>
+      <c r="AF40" t="s">
+        <v>65</v>
       </c>
       <c r="AG40" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH40" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK40">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ40">
+        <v>1</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>55</v>
       </c>
       <c r="AL40" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM40" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s">
-        <v>298</v>
-      </c>
-      <c r="AO40" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F41" s="6">
         <v>52</v>
@@ -6229,35 +5898,35 @@
         <v>0.5</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K41" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L41" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M41" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N41" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O41" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q41" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="R41" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S41" s="12">
         <v>1</v>
@@ -6266,13 +5935,13 @@
         <v>1</v>
       </c>
       <c r="U41" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="W41" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="X41" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="Y41" s="12">
         <v>1</v>
@@ -6287,54 +5956,48 @@
         <v>0</v>
       </c>
       <c r="AC41" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>287</v>
+        <v>60</v>
+      </c>
+      <c r="AD41" s="12">
+        <v>0</v>
       </c>
       <c r="AE41" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="12">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>65</v>
       </c>
       <c r="AG41" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK41">
+        <v>66</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ41">
         <v>0.5</v>
       </c>
+      <c r="AK41" t="s">
+        <v>55</v>
+      </c>
       <c r="AL41" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM41" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s">
-        <v>301</v>
-      </c>
-      <c r="AO41" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="42" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -6346,37 +6009,37 @@
         <v>0.25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K42" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L42" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M42" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N42" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="O42" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="Q42" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="R42" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="S42" s="12">
         <v>1</v>
@@ -6384,8 +6047,11 @@
       <c r="T42" s="12">
         <v>1</v>
       </c>
+      <c r="U42" t="s">
+        <v>55</v>
+      </c>
       <c r="X42" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="Y42" s="12">
         <v>1</v>
@@ -6400,40 +6066,34 @@
         <v>0</v>
       </c>
       <c r="AC42" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>287</v>
+        <v>60</v>
+      </c>
+      <c r="AD42" s="12">
+        <v>0</v>
       </c>
       <c r="AE42" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="12">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>65</v>
       </c>
       <c r="AG42" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH42" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK42">
+        <v>66</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ42">
         <v>0.33</v>
       </c>
+      <c r="AK42" t="s">
+        <v>55</v>
+      </c>
       <c r="AL42" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="AM42" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s">
-        <v>302</v>
-      </c>
-      <c r="AO42" t="s">
-        <v>321</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -6461,34 +6121,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -6621,10 +6281,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="13">
         <v>45035</v>
@@ -6653,10 +6313,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="13">
         <v>45035</v>
@@ -6685,10 +6345,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="13">
         <v>45042</v>
@@ -6717,10 +6377,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" s="13">
         <v>45042</v>
@@ -6749,10 +6409,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C10" s="13">
         <v>45055</v>
@@ -6781,10 +6441,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C11" s="13">
         <v>45055</v>
@@ -6813,10 +6473,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C12" s="13">
         <v>45071</v>
@@ -6845,10 +6505,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C13" s="13">
         <v>45071</v>
@@ -6877,10 +6537,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C14" s="13">
         <v>45077</v>
@@ -6909,10 +6569,10 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C15" s="13">
         <v>45077</v>
@@ -6941,10 +6601,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C16" s="13">
         <v>45077</v>
@@ -6973,10 +6633,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C17" s="13">
         <v>45084</v>
@@ -7005,10 +6665,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C18" s="13">
         <v>45084</v>
@@ -7037,10 +6697,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C19" s="13">
         <v>45085</v>
@@ -7070,10 +6730,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C20" s="13">
         <v>45085</v>
@@ -7103,10 +6763,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C21" s="13">
         <v>45085</v>
@@ -7135,10 +6795,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -7167,10 +6827,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
@@ -7199,10 +6859,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -7231,10 +6891,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -7263,10 +6923,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -7295,10 +6955,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -7327,10 +6987,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -7359,10 +7019,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -7391,10 +7051,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -7423,10 +7083,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -7455,10 +7115,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -7487,10 +7147,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -7519,10 +7179,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -7551,10 +7211,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -7583,10 +7243,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -7615,10 +7275,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -7647,10 +7307,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -7679,10 +7339,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -7711,10 +7371,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -7743,10 +7403,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -7775,10 +7435,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -7826,25 +7486,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -7941,10 +7601,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="13">
         <v>45035</v>
@@ -7964,10 +7624,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="13">
         <v>45035</v>
@@ -7988,10 +7648,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="13">
         <v>45042</v>
@@ -8011,10 +7671,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" s="13">
         <v>45042</v>
@@ -8034,10 +7694,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C10" s="13">
         <v>45055</v>
@@ -8057,10 +7717,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C11" s="13">
         <v>45055</v>
@@ -8080,10 +7740,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C12" s="13">
         <v>45071</v>
@@ -8103,10 +7763,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C13" s="13">
         <v>45071</v>
@@ -8126,10 +7786,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C14" s="13">
         <v>45077</v>
@@ -8149,10 +7809,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C15" s="13">
         <v>45077</v>
@@ -8172,10 +7832,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C16" s="13">
         <v>45077</v>
@@ -8195,10 +7855,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C17" s="13">
         <v>45084</v>
@@ -8218,10 +7878,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C18" s="13">
         <v>45084</v>
@@ -8241,10 +7901,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C19" s="13">
         <v>45085</v>
@@ -8264,10 +7924,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C20" s="13">
         <v>45085</v>
@@ -8287,10 +7947,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C21" s="13">
         <v>45085</v>
@@ -8310,10 +7970,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -8333,10 +7993,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
@@ -8356,10 +8016,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -8379,10 +8039,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -8402,10 +8062,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -8425,10 +8085,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -8448,10 +8108,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -8471,10 +8131,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -8494,10 +8154,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -8517,10 +8177,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -8540,10 +8200,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -8563,10 +8223,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -8586,10 +8246,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -8609,10 +8269,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -8632,10 +8292,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -8655,10 +8315,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -8678,10 +8338,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -8701,10 +8361,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -8724,10 +8384,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -8747,10 +8407,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -8770,10 +8430,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -9454,91 +9114,91 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="AC1" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="V1" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
@@ -9606,7 +9266,7 @@
         <v>13.599999999999994</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="W2" s="22">
         <v>0.20867383512542267</v>
@@ -9695,7 +9355,7 @@
         <v>11.899999999999995</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="W3" s="22">
         <v>0.22000000000019782</v>
@@ -9784,7 +9444,7 @@
         <v>66.100000000000009</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="W4" s="22">
         <v>0.66333333333309008</v>
@@ -10407,7 +10067,7 @@
         <v>125.4</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="W11" s="22">
         <v>0.99032258064503076</v>
@@ -10496,7 +10156,7 @@
         <v>78.2</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="W12" s="22">
         <v>0.50000000000009537</v>
@@ -10587,7 +10247,7 @@
         <v>180</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="W13" s="22">
         <v>3.1046953405016224</v>
@@ -10613,10 +10273,10 @@
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14" s="13">
         <v>45035</v>
@@ -10676,7 +10336,7 @@
         <v>460.00000000000006</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="W14" s="22">
         <v>2.723333333333263</v>
@@ -10702,10 +10362,10 @@
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C15" s="13">
         <v>45035</v>
@@ -10767,7 +10427,7 @@
         <v>457</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="W15" s="22">
         <v>3.7199999999998568</v>
@@ -10793,10 +10453,10 @@
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C16" s="13">
         <v>45035</v>
@@ -10856,7 +10516,7 @@
         <v>457.5</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="W16" s="22">
         <v>1.25161290322564</v>
@@ -10882,10 +10542,10 @@
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C17" s="13">
         <v>45035</v>
@@ -10971,10 +10631,10 @@
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C18" s="13">
         <v>45035</v>
@@ -11060,10 +10720,10 @@
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C19" s="13">
         <v>45035</v>
@@ -11149,10 +10809,10 @@
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C20" s="13">
         <v>45042</v>
@@ -11238,10 +10898,10 @@
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C21" s="13">
         <v>45042</v>
@@ -11327,10 +10987,10 @@
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C22" s="13">
         <v>45042</v>
@@ -11416,10 +11076,10 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C23" s="13">
         <v>45042</v>
@@ -11505,10 +11165,10 @@
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C24" s="13">
         <v>45042</v>
@@ -11594,10 +11254,10 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C25" s="13">
         <v>45042</v>
@@ -11683,10 +11343,10 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C26" s="13">
         <v>45055</v>
@@ -11773,10 +11433,10 @@
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C27" s="13">
         <v>45055</v>
@@ -11863,10 +11523,10 @@
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C28" s="13">
         <v>45055</v>
@@ -11952,10 +11612,10 @@
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C29" s="13">
         <v>45055</v>
@@ -12015,7 +11675,7 @@
         <v>924</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="W29" s="22">
         <v>17.812903225806423</v>
@@ -12041,10 +11701,10 @@
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C30" s="13">
         <v>45055</v>
@@ -12104,7 +11764,7 @@
         <v>400</v>
       </c>
       <c r="V30" s="5" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="W30" s="22">
         <v>1.4549999999997472</v>
@@ -12130,10 +11790,10 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C31" s="13">
         <v>45055</v>
@@ -12193,7 +11853,7 @@
         <v>877</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="W31" s="22">
         <v>27.430000000000138</v>
@@ -12219,10 +11879,10 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C32" s="13">
         <v>45071</v>
@@ -12308,10 +11968,10 @@
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C33" s="13">
         <v>45071</v>
@@ -12397,10 +12057,10 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C34" s="13">
         <v>45071</v>
@@ -12486,10 +12146,10 @@
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C35" s="13">
         <v>45071</v>
@@ -12575,10 +12235,10 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C36" s="13">
         <v>45077</v>
@@ -12638,7 +12298,7 @@
         <v>187.99999999999997</v>
       </c>
       <c r="V36" s="5" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="W36" s="22">
         <v>1.1333333333335343</v>
@@ -12664,10 +12324,10 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C37" s="13">
         <v>45077</v>
@@ -12727,7 +12387,7 @@
         <v>171.00000000000009</v>
       </c>
       <c r="V37" s="5" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="W37" s="22">
         <v>1.0933333333336275</v>
@@ -12753,10 +12413,10 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C38" s="13">
         <v>45077</v>
@@ -12816,7 +12476,7 @@
         <v>314.99999999999994</v>
       </c>
       <c r="V38" s="5" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="W38" s="22">
         <v>1.4544444444442524</v>
@@ -12842,10 +12502,10 @@
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C39" s="13">
         <v>45077</v>
@@ -12905,7 +12565,7 @@
         <v>913.99999999999989</v>
       </c>
       <c r="V39" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="W39" s="22">
         <v>6.2937499999997648</v>
@@ -12931,10 +12591,10 @@
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C40" s="13">
         <v>45077</v>
@@ -12994,7 +12654,7 @@
         <v>671.99999999999989</v>
       </c>
       <c r="V40" s="5" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="W40" s="22">
         <v>2.1166666666663523</v>
@@ -13020,10 +12680,10 @@
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C41" s="13">
         <v>45077</v>
@@ -13083,7 +12743,7 @@
         <v>862.33</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="W41" s="22">
         <v>2.4999999999999369</v>
@@ -13109,10 +12769,10 @@
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C42" s="13">
         <v>45077</v>
@@ -13198,10 +12858,10 @@
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C43" s="13">
         <v>45077</v>
@@ -13261,7 +12921,7 @@
         <v>169.00000000000003</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="W43" s="22">
         <v>0.56333333333308622</v>
@@ -13287,10 +12947,10 @@
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C44" s="13">
         <v>45077</v>
@@ -13350,7 +13010,7 @@
         <v>445.00000000000011</v>
       </c>
       <c r="V44" s="5" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="W44" s="22">
         <v>1.2199999999997619</v>
@@ -13376,10 +13036,10 @@
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C45" s="13">
         <v>45084</v>
@@ -13439,7 +13099,7 @@
         <v>632.99999999999989</v>
       </c>
       <c r="V45" s="5" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="W45" s="22">
         <v>1.2000000000000455</v>
@@ -13465,10 +13125,10 @@
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C46" s="13">
         <v>45084</v>
@@ -13528,7 +13188,7 @@
         <v>603.99999999999989</v>
       </c>
       <c r="V46" s="5" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="W46" s="22">
         <v>0.79666666666658636</v>
@@ -13554,10 +13214,10 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C47" s="13">
         <v>45084</v>
@@ -13617,7 +13277,7 @@
         <v>309.00000000000006</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="W47" s="22">
         <v>0.81333333333333258</v>
@@ -13643,10 +13303,10 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C48" s="13">
         <v>45084</v>
@@ -13706,7 +13366,7 @@
         <v>1748</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="W48" s="22">
         <v>4.956666666666365</v>
@@ -13732,10 +13392,10 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C49" s="13">
         <v>45084</v>
@@ -13821,10 +13481,10 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C50" s="13">
         <v>45084</v>
@@ -13884,7 +13544,7 @@
         <v>1755.9999999999998</v>
       </c>
       <c r="V50" s="5" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="W50" s="22">
         <v>9.8999999999999009</v>
@@ -13910,10 +13570,10 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C51" s="13">
         <v>45085</v>
@@ -13973,7 +13633,7 @@
         <v>781</v>
       </c>
       <c r="V51" s="5" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="W51" s="22">
         <v>1.9193548387096737</v>
@@ -13999,10 +13659,10 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C52" s="13">
         <v>45085</v>
@@ -14062,7 +13722,7 @@
         <v>756.99999999999989</v>
       </c>
       <c r="V52" s="5" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="W52" s="22">
         <v>1.8777777777777436</v>
@@ -14088,10 +13748,10 @@
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C53" s="13">
         <v>45085</v>
@@ -14151,7 +13811,7 @@
         <v>874</v>
       </c>
       <c r="V53" s="5" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="W53" s="22">
         <v>3.9393939393938018</v>
@@ -14177,10 +13837,10 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C54" s="13">
         <v>45085</v>
@@ -14240,7 +13900,7 @@
         <v>1754.67</v>
       </c>
       <c r="V54" s="5" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="W54" s="22">
         <v>14.73666666666702</v>
@@ -14266,10 +13926,10 @@
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C55" s="13">
         <v>45085</v>
@@ -14329,7 +13989,7 @@
         <v>1766</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="W55" s="22">
         <v>4.1111111111110032</v>
@@ -14355,10 +14015,10 @@
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C56" s="13">
         <v>45085</v>
@@ -14444,10 +14104,10 @@
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C57" s="13">
         <v>45085</v>
@@ -14533,10 +14193,10 @@
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C58" s="13">
         <v>45098</v>
@@ -14596,7 +14256,7 @@
         <v>902.99999999999989</v>
       </c>
       <c r="V58" s="5" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="W58" s="22">
         <v>2.23111111111128</v>
@@ -14622,10 +14282,10 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C59" s="13">
         <v>45098</v>
@@ -14686,7 +14346,7 @@
         <v>718.33</v>
       </c>
       <c r="V59" s="5" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="W59" s="22">
         <v>1.832258064516443</v>
@@ -14712,10 +14372,10 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C60" s="13">
         <v>45098</v>
@@ -14775,7 +14435,7 @@
         <v>650</v>
       </c>
       <c r="V60" s="5" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="W60" s="22">
         <v>1.5031249999997165</v>
@@ -14801,10 +14461,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C61" s="13">
         <v>45098</v>
@@ -14864,7 +14524,7 @@
         <v>413.99999999999994</v>
       </c>
       <c r="V61" s="5" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="W61" s="22">
         <v>0.97509632616516206</v>
@@ -14890,10 +14550,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C62" s="13">
         <v>45098</v>
@@ -14954,7 +14614,7 @@
         <v>367.99999999999994</v>
       </c>
       <c r="V62" s="5" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="W62" s="22">
         <v>0.93333333333352664</v>
@@ -14980,10 +14640,10 @@
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C63" s="13">
         <v>45098</v>
@@ -15069,10 +14729,10 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C64" s="13">
         <v>45306</v>
@@ -15130,7 +14790,7 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="23" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="W64" s="22">
         <v>2.51612903225816</v>
@@ -15156,10 +14816,10 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C65" s="13">
         <v>45306</v>
@@ -15217,7 +14877,7 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="23" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="W65" s="22">
         <v>19.096774193548345</v>
@@ -15243,10 +14903,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C66" s="13">
         <v>45306</v>
@@ -15330,10 +14990,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C67" s="13">
         <v>45307</v>
@@ -15391,7 +15051,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="23" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="W67" s="22">
         <v>0.55000000000025773</v>
@@ -15417,10 +15077,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C68" s="13">
         <v>45307</v>
@@ -15480,7 +15140,7 @@
         <v>436</v>
       </c>
       <c r="V68" s="23" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="W68" s="22">
         <v>0.52459999999999996</v>
@@ -15506,10 +15166,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="C69" s="13">
         <v>45307</v>
@@ -15569,7 +15229,7 @@
         <v>495</v>
       </c>
       <c r="V69" s="23" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="W69" s="22">
         <v>0.50000000000009537</v>
@@ -15595,10 +15255,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="C70" s="13">
         <v>45307</v>
@@ -15656,7 +15316,7 @@
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="23" t="s">
-        <v>329</v>
+        <v>280</v>
       </c>
       <c r="W70" s="22">
         <v>0.67096774193575381</v>
@@ -15682,10 +15342,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="C71" s="13">
         <v>45307</v>
@@ -15743,7 +15403,7 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="23" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="W71" s="22">
         <v>0.643750000000054</v>
@@ -15769,10 +15429,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="C72" s="13">
         <v>45307</v>
@@ -15830,7 +15490,7 @@
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="23" t="s">
-        <v>331</v>
+        <v>282</v>
       </c>
       <c r="W72" s="22">
         <v>110.50000000000011</v>
@@ -15856,10 +15516,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C73" s="13">
         <v>45307</v>
@@ -15917,7 +15577,7 @@
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="23" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="W73" s="22">
         <v>0.64193548387096155</v>
@@ -15943,10 +15603,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C74" s="13">
         <v>45307</v>
@@ -16004,7 +15664,7 @@
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="23" t="s">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="W74" s="22">
         <v>79.343333333333277</v>
@@ -16030,10 +15690,10 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C75" s="13">
         <v>45307</v>
@@ -16093,7 +15753,7 @@
         <v>5439.9999999999991</v>
       </c>
       <c r="V75" s="23" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="W75" s="22">
         <v>216.45199134199115</v>
@@ -16119,10 +15779,10 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C76" s="13">
         <v>45307</v>
@@ -16180,7 +15840,7 @@
         <v>1016</v>
       </c>
       <c r="V76" s="23" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="W76" s="22">
         <v>0.60303030303029714</v>
@@ -16206,10 +15866,10 @@
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C77" s="13">
         <v>45307</v>
@@ -16269,7 +15929,7 @@
         <v>2375</v>
       </c>
       <c r="V77" s="23" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="W77" s="22">
         <v>48.758620689655217</v>
@@ -16295,10 +15955,10 @@
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C78" s="13">
         <v>45307</v>
@@ -16358,7 +16018,7 @@
         <v>685</v>
       </c>
       <c r="V78" s="23" t="s">
-        <v>337</v>
+        <v>288</v>
       </c>
       <c r="W78" s="22">
         <v>136.87692307692299</v>
@@ -16384,10 +16044,10 @@
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C79" s="13">
         <v>45313</v>
@@ -16447,7 +16107,7 @@
         <v>296.00000000000006</v>
       </c>
       <c r="V79" s="23" t="s">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="W79" s="22">
         <v>1.1862068965516548</v>
@@ -16473,10 +16133,10 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C80" s="13">
         <v>45313</v>
@@ -16536,7 +16196,7 @@
         <v>260.00000000000006</v>
       </c>
       <c r="V80" s="23" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="W80" s="22">
         <v>1.2645161290320615</v>
@@ -16562,10 +16222,10 @@
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C81" s="13">
         <v>45313</v>
@@ -16625,7 +16285,7 @@
         <v>2103.3333333333335</v>
       </c>
       <c r="V81" s="23" t="s">
-        <v>340</v>
+        <v>291</v>
       </c>
       <c r="W81" s="22">
         <v>4.5483870967743663</v>
@@ -16651,10 +16311,10 @@
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="C82" s="13">
         <v>45314</v>
@@ -16714,7 +16374,7 @@
         <v>236.00000000000003</v>
       </c>
       <c r="V82" s="23" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="W82" s="22">
         <v>0.70909090909097905</v>
@@ -16740,10 +16400,10 @@
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="C83" s="13">
         <v>45314</v>
@@ -16803,7 +16463,7 @@
         <v>294.00000000000006</v>
       </c>
       <c r="V83" s="23" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="W83" s="22">
         <v>0.71999999999997988</v>
@@ -16829,10 +16489,10 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="C84" s="13">
         <v>45314</v>
@@ -16892,7 +16552,7 @@
         <v>4746.666666666667</v>
       </c>
       <c r="V84" s="23" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="W84" s="22">
         <v>37.889841269841206</v>
@@ -16918,10 +16578,10 @@
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C85" s="13">
         <v>45320</v>
@@ -16981,7 +16641,7 @@
         <v>108.99999999999999</v>
       </c>
       <c r="V85" s="23" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="W85" s="22">
         <v>0.87419354838700769</v>
@@ -17007,10 +16667,10 @@
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C86" s="13">
         <v>45320</v>
@@ -17070,7 +16730,7 @@
         <v>795.00000000000034</v>
       </c>
       <c r="V86" s="23" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="W86" s="22">
         <v>10.465624999999923</v>
@@ -17096,10 +16756,10 @@
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C87" s="13">
         <v>45320</v>
@@ -17130,10 +16790,10 @@
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C88" s="13">
         <v>45320</v>
@@ -17193,7 +16853,7 @@
         <v>83</v>
       </c>
       <c r="V88" s="23" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="W88" s="22">
         <v>0.6062500000001414</v>
@@ -17219,10 +16879,10 @@
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C89" s="13">
         <v>45320</v>
@@ -17282,7 +16942,7 @@
         <v>2429.9999999999995</v>
       </c>
       <c r="V89" s="23" t="s">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="W89" s="22">
         <v>110.45000000000016</v>
@@ -17308,10 +16968,10 @@
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="C90" s="13">
         <v>45320</v>
@@ -17342,10 +17002,10 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C91" s="13">
         <v>45321</v>
@@ -17405,7 +17065,7 @@
         <v>340.00000000000006</v>
       </c>
       <c r="V91" s="23" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="W91" s="22">
         <v>0.75937499999989555</v>
@@ -17431,10 +17091,10 @@
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C92" s="13">
         <v>45321</v>
@@ -17494,7 +17154,7 @@
         <v>255.99999999999994</v>
       </c>
       <c r="V92" s="23" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="W92" s="22">
         <v>0.75333333333347241</v>
@@ -17520,10 +17180,10 @@
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C93" s="13">
         <v>45321</v>
@@ -17583,7 +17243,7 @@
         <v>3620</v>
       </c>
       <c r="V93" s="23" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="W93" s="22">
         <v>27.085714285714094</v>
@@ -17609,10 +17269,10 @@
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C94" s="13">
         <v>45321</v>
@@ -17672,7 +17332,7 @@
         <v>671</v>
       </c>
       <c r="V94" s="23" t="s">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="W94" s="22">
         <v>2.4827586206895043</v>
@@ -17698,10 +17358,10 @@
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C95" s="13">
         <v>45321</v>
@@ -17761,7 +17421,7 @@
         <v>597</v>
       </c>
       <c r="V95" s="23" t="s">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="W95" s="22">
         <v>1.0322580645162445</v>
@@ -17787,10 +17447,10 @@
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C96" s="13">
         <v>45321</v>
@@ -17850,7 +17510,7 @@
         <v>6336.666666666667</v>
       </c>
       <c r="V96" s="23" t="s">
-        <v>353</v>
+        <v>304</v>
       </c>
       <c r="W96" s="22">
         <v>13.079063146997981</v>
@@ -17876,10 +17536,10 @@
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C97" s="13">
         <v>45321</v>
@@ -17939,7 +17599,7 @@
         <v>417</v>
       </c>
       <c r="V97" s="23" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="W97" s="22">
         <v>1.403333333333497</v>
@@ -17965,10 +17625,10 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C98" s="13">
         <v>45321</v>
@@ -18028,7 +17688,7 @@
         <v>238.99999999999997</v>
       </c>
       <c r="V98" s="23" t="s">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="W98" s="22">
         <v>1.0333333333332935</v>
@@ -18054,10 +17714,10 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="C99" s="13">
         <v>45321</v>
@@ -18143,10 +17803,10 @@
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="C100" s="13">
         <v>45327</v>
@@ -18206,7 +17866,7 @@
         <v>2530</v>
       </c>
       <c r="V100" s="23" t="s">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="W100" s="22">
         <v>42.168965517241475</v>
@@ -18232,10 +17892,10 @@
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="C101" s="13">
         <v>45327</v>
@@ -18293,7 +17953,7 @@
         <v>7460</v>
       </c>
       <c r="V101" s="23" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="W101" s="22">
         <v>29.444444444444507</v>
@@ -18319,10 +17979,10 @@
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="C102" s="13">
         <v>45327</v>
@@ -18353,10 +18013,10 @@
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C103" s="13">
         <v>45328</v>
@@ -18416,7 +18076,7 @@
         <v>1325</v>
       </c>
       <c r="V103" s="23" t="s">
-        <v>358</v>
+        <v>309</v>
       </c>
       <c r="W103" s="22">
         <v>7.5764705882354004</v>
@@ -18442,10 +18102,10 @@
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C104" s="13">
         <v>45328</v>
@@ -18505,7 +18165,7 @@
         <v>960.00000000000034</v>
       </c>
       <c r="V104" s="23" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="W104" s="22">
         <v>1.0531250000000991</v>
@@ -18531,10 +18191,10 @@
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="C105" s="13">
         <v>45328</v>
@@ -18594,7 +18254,7 @@
         <v>5140.0000000000009</v>
       </c>
       <c r="V105" s="23" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="W105" s="22">
         <v>138.51052631578958</v>
@@ -18620,10 +18280,10 @@
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="C106" s="13">
         <v>45328</v>
@@ -18683,7 +18343,7 @@
         <v>2189.9999999999995</v>
       </c>
       <c r="V106" s="23" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="W106" s="22">
         <v>36.022727272727131</v>
@@ -18709,10 +18369,10 @@
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="C107" s="13">
         <v>45328</v>
@@ -18772,7 +18432,7 @@
         <v>7280</v>
       </c>
       <c r="V107" s="23" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="W107" s="22">
         <v>126.63333333333307</v>
@@ -18798,10 +18458,10 @@
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="C108" s="13">
         <v>45328</v>
@@ -18832,10 +18492,10 @@
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C109" s="13">
         <v>45334</v>
@@ -18895,7 +18555,7 @@
         <v>95.499999999999957</v>
       </c>
       <c r="V109" s="23" t="s">
-        <v>362</v>
+        <v>313</v>
       </c>
       <c r="W109" s="22">
         <v>0.59687500000005222</v>
@@ -18921,10 +18581,10 @@
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C110" s="13">
         <v>45334</v>
@@ -18984,7 +18644,7 @@
         <v>64.5</v>
       </c>
       <c r="V110" s="23" t="s">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="W110" s="22">
         <v>0.53225806451614921</v>
@@ -19010,10 +18670,10 @@
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C111" s="13">
         <v>45334</v>
@@ -19073,7 +18733,7 @@
         <v>1359.9999999999998</v>
       </c>
       <c r="V111" s="23" t="s">
-        <v>364</v>
+        <v>315</v>
       </c>
       <c r="W111" s="22">
         <v>25.639999999999926</v>
@@ -19099,10 +18759,10 @@
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C112" s="13">
         <v>45334</v>
@@ -19162,7 +18822,7 @@
         <v>139</v>
       </c>
       <c r="V112" s="23" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="W112" s="22">
         <v>1.0555555555554639</v>
@@ -19188,10 +18848,10 @@
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C113" s="13">
         <v>45334</v>
@@ -19251,7 +18911,7 @@
         <v>147.5</v>
       </c>
       <c r="V113" s="23" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="W113" s="22">
         <v>0.95000000000000639</v>
@@ -19277,10 +18937,10 @@
     </row>
     <row r="114" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C114" s="13">
         <v>45334</v>
@@ -19340,7 +19000,7 @@
         <v>124.00000000000001</v>
       </c>
       <c r="V114" s="23" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="W114" s="22">
         <v>0.82999999999984198</v>
@@ -19366,10 +19026,10 @@
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C115" s="13">
         <v>45335</v>
@@ -19429,7 +19089,7 @@
         <v>2770</v>
       </c>
       <c r="V115" s="23" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="W115" s="22">
         <v>8.7866666666665569</v>
@@ -19455,10 +19115,10 @@
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C116" s="13">
         <v>45335</v>
@@ -19518,7 +19178,7 @@
         <v>2929.9999999999995</v>
       </c>
       <c r="V116" s="23" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
       <c r="W116" s="22">
         <v>6.4066666666666565</v>
@@ -19544,10 +19204,10 @@
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C117" s="13">
         <v>45335</v>
@@ -19607,7 +19267,7 @@
         <v>2719.9999999999995</v>
       </c>
       <c r="V117" s="23" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="W117" s="22">
         <v>14.151808278867122</v>
@@ -19633,10 +19293,10 @@
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C118" s="13">
         <v>45335</v>
@@ -19722,10 +19382,10 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C119" s="13">
         <v>45335</v>
@@ -19785,7 +19445,7 @@
         <v>305.99999999999994</v>
       </c>
       <c r="V119" s="23" t="s">
-        <v>371</v>
+        <v>322</v>
       </c>
       <c r="W119" s="22">
         <v>2.8219999999999619</v>
@@ -19811,10 +19471,10 @@
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="C120" s="13">
         <v>45335</v>
@@ -19874,7 +19534,7 @@
         <v>1980.0000000000005</v>
       </c>
       <c r="V120" s="23" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="W120" s="22">
         <v>95.649999999999835</v>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\Sampling &amp; Field &amp; Lab\Raw Data\0 - raw_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D9FD2E-CF55-46A2-ABC9-188AF558752A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="661"/>
+    <workbookView xWindow="12800" yWindow="0" windowWidth="12800" windowHeight="13800" tabRatio="661" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="gas" sheetId="28" r:id="rId3"/>
     <sheet name="parameters" sheetId="15" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1015,7 +1016,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -1147,7 +1148,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="fmtMidLeft" xfId="1"/>
+    <cellStyle name="fmtMidLeft" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1465,7 +1466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AM42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6103,7 +6104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7472,8 +7473,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G111"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J111"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" bestFit="1" customWidth="1"/>
@@ -7484,7 +7485,7 @@
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>132</v>
       </c>
@@ -7506,8 +7507,10 @@
       <c r="G1" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
@@ -7521,7 +7524,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="5">
-        <v>2.636158905904523</v>
+        <v>27.256032960311835</v>
       </c>
       <c r="F2" s="10">
         <v>0</v>
@@ -7529,8 +7532,10 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -7544,16 +7549,18 @@
         <v>3</v>
       </c>
       <c r="E3" s="5">
-        <v>0.60373304087214053</v>
+        <v>31.683908747629939</v>
       </c>
       <c r="F3" s="10">
-        <v>0</v>
+        <v>87.434598130127654</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -7567,16 +7574,18 @@
         <v>2</v>
       </c>
       <c r="E4" s="5">
-        <v>1.6219944898894096</v>
+        <v>7.0569646960259611</v>
       </c>
       <c r="F4" s="10">
-        <v>0</v>
+        <v>63.143274473722634</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -7590,16 +7599,18 @@
         <v>3</v>
       </c>
       <c r="E5" s="5">
-        <v>1.3010745781164941</v>
+        <v>40.083047620107997</v>
       </c>
       <c r="F5" s="10">
-        <v>0</v>
+        <v>19.32545041520487</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -7613,16 +7624,16 @@
         <v>2</v>
       </c>
       <c r="E6" s="5">
-        <v>6.2442928261726101</v>
+        <v>85.619676672652588</v>
       </c>
       <c r="F6" s="10">
-        <v>49.42965571262723</v>
+        <v>161.51600270489382</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -7637,7 +7648,7 @@
         <v>410</v>
       </c>
       <c r="E7" s="5">
-        <v>6.9874856720334708E-2</v>
+        <v>0.41804215414344859</v>
       </c>
       <c r="F7" s="10">
         <v>0</v>
@@ -7646,7 +7657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -7660,7 +7671,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="5">
-        <v>1.7547574474127787</v>
+        <v>41.581268461004157</v>
       </c>
       <c r="F8" s="10">
         <v>0</v>
@@ -7669,7 +7680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -7683,16 +7694,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="5">
-        <v>6.9684218922271048</v>
+        <v>116.9319533376742</v>
       </c>
       <c r="F9" s="10">
-        <v>0</v>
+        <v>179.60486212833976</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -7715,7 +7726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -7729,16 +7740,16 @@
         <v>368</v>
       </c>
       <c r="E11" s="5">
-        <v>6.3242229995352298E-2</v>
+        <v>1.1288055659963265</v>
       </c>
       <c r="F11" s="10">
-        <v>0</v>
+        <v>0.39877288001502859</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -7752,16 +7763,16 @@
         <v>4</v>
       </c>
       <c r="E12" s="5">
-        <v>3.7113810141010423E-2</v>
+        <v>0.16777941727158485</v>
       </c>
       <c r="F12" s="10">
-        <v>0</v>
+        <v>3.4966994406334519</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -7775,16 +7786,16 @@
         <v>2</v>
       </c>
       <c r="E13" s="5">
-        <v>3.0477408485254385</v>
+        <v>14.571948977041183</v>
       </c>
       <c r="F13" s="10">
-        <v>2.203290852651111</v>
+        <v>19.803629333789317</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
@@ -7798,7 +7809,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="5">
-        <v>3.8736863075649837E-2</v>
+        <v>3.4719943236557458</v>
       </c>
       <c r="F14" s="10">
         <v>0</v>
@@ -7807,7 +7818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
@@ -7821,16 +7832,16 @@
         <v>2</v>
       </c>
       <c r="E15" s="5">
-        <v>14.241294116190522</v>
+        <v>153.2423560757739</v>
       </c>
       <c r="F15" s="10">
-        <v>0</v>
+        <v>176.11862559465976</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>35</v>
       </c>
@@ -7867,10 +7878,10 @@
         <v>3</v>
       </c>
       <c r="E17" s="5">
-        <v>3.6979108812784931</v>
+        <v>28.485341453873755</v>
       </c>
       <c r="F17" s="10">
-        <v>15.913642332138245</v>
+        <v>81.11974136168314</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -7890,7 +7901,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="5">
-        <v>4.5469290015537265</v>
+        <v>30.760164271592441</v>
       </c>
       <c r="F18" s="10">
         <v>0</v>
@@ -7913,7 +7924,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="5">
-        <v>10.370416059605184</v>
+        <v>15.209500495155361</v>
       </c>
       <c r="F19" s="10">
         <v>0</v>
@@ -7936,10 +7947,10 @@
         <v>3</v>
       </c>
       <c r="E20" s="5">
-        <v>0.97299809427969042</v>
+        <v>36.117419601049299</v>
       </c>
       <c r="F20" s="10">
-        <v>6.8247044192230932</v>
+        <v>59.718406767352484</v>
       </c>
       <c r="G20" s="2">
         <v>0</v>
@@ -7959,7 +7970,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="5">
-        <v>1.9281240383078269</v>
+        <v>13.691699720391201</v>
       </c>
       <c r="F21" s="10">
         <v>0</v>
@@ -7982,10 +7993,10 @@
         <v>200</v>
       </c>
       <c r="E22" s="5">
-        <v>0.16598108903827372</v>
+        <v>0.78425223654444509</v>
       </c>
       <c r="F22" s="10">
-        <v>0</v>
+        <v>1.3278801150469495</v>
       </c>
       <c r="G22" s="2">
         <v>0</v>
@@ -8028,10 +8039,10 @@
         <v>23</v>
       </c>
       <c r="E24" s="5">
-        <v>4.46</v>
+        <v>40.760529746994699</v>
       </c>
       <c r="F24" s="10">
-        <v>0</v>
+        <v>77.837928292732087</v>
       </c>
       <c r="G24" s="2">
         <v>0</v>
@@ -8051,10 +8062,10 @@
         <v>4</v>
       </c>
       <c r="E25" s="5">
-        <v>2.15</v>
+        <v>13.78189684420064</v>
       </c>
       <c r="F25" s="10">
-        <v>0</v>
+        <v>489.5511674618088</v>
       </c>
       <c r="G25" s="2">
         <v>0</v>
@@ -8073,11 +8084,11 @@
       <c r="D26" s="14">
         <v>5</v>
       </c>
-      <c r="E26" s="5">
-        <v>4.28</v>
+      <c r="E26">
+        <v>13.922565398619984</v>
       </c>
       <c r="F26" s="10">
-        <v>0</v>
+        <v>142.94185913569089</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
@@ -8097,7 +8108,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="5">
-        <v>10.96</v>
+        <v>37.863042537419226</v>
       </c>
       <c r="F27" s="10">
         <v>0</v>
@@ -8120,7 +8131,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="5">
-        <v>4.6900000000000004</v>
+        <v>21.609484786801232</v>
       </c>
       <c r="F28" s="10">
         <v>0</v>
@@ -8143,10 +8154,10 @@
         <v>9</v>
       </c>
       <c r="E29" s="5">
-        <v>2.1</v>
+        <v>16.940467516231084</v>
       </c>
       <c r="F29" s="10">
-        <v>0</v>
+        <v>16.250904483447439</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
@@ -8166,10 +8177,10 @@
         <v>15</v>
       </c>
       <c r="E30" s="5">
-        <v>1.87</v>
+        <v>6.9014015313100829</v>
       </c>
       <c r="F30" s="10">
-        <v>0</v>
+        <v>23.360308160919679</v>
       </c>
       <c r="G30" s="2">
         <v>0</v>
@@ -8189,7 +8200,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="5">
-        <v>0.46</v>
+        <v>0.68228053039211889</v>
       </c>
       <c r="F31" s="10">
         <v>0</v>
@@ -8212,10 +8223,10 @@
         <v>35</v>
       </c>
       <c r="E32" s="5">
-        <v>0.2</v>
+        <v>0.76502851822708029</v>
       </c>
       <c r="F32" s="10">
-        <v>0</v>
+        <v>7.739177459094555</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
@@ -8235,10 +8246,10 @@
         <v>30</v>
       </c>
       <c r="E33" s="5">
-        <v>3.4</v>
+        <v>18.99466229724479</v>
       </c>
       <c r="F33" s="10">
-        <v>32.200000000000003</v>
+        <v>160.38552456591518</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
@@ -8258,10 +8269,10 @@
         <v>30</v>
       </c>
       <c r="E34" s="5">
-        <v>1.19</v>
+        <v>10.905486816804119</v>
       </c>
       <c r="F34" s="10">
-        <v>1.1000000000000001</v>
+        <v>31.764058108059167</v>
       </c>
       <c r="G34" s="2">
         <v>0</v>
@@ -8281,10 +8292,10 @@
         <v>88</v>
       </c>
       <c r="E35" s="5">
-        <v>7.98</v>
+        <v>25.183914185723339</v>
       </c>
       <c r="F35" s="10">
-        <v>0.9</v>
+        <v>39.861061346201026</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
@@ -8304,10 +8315,10 @@
         <v>35</v>
       </c>
       <c r="E36" s="5">
-        <v>1.44</v>
+        <v>12.560183791534289</v>
       </c>
       <c r="F36" s="10">
-        <v>0</v>
+        <v>33.035650424532093</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
@@ -8327,10 +8338,10 @@
         <v>43</v>
       </c>
       <c r="E37" s="5">
-        <v>0.9</v>
+        <v>3.2521696824356239</v>
       </c>
       <c r="F37" s="10">
-        <v>0</v>
+        <v>15.046435130031679</v>
       </c>
       <c r="G37" s="2">
         <v>0</v>
@@ -8350,10 +8361,10 @@
         <v>29</v>
       </c>
       <c r="E38" s="5">
-        <v>1.45</v>
+        <v>5.2923871983452093</v>
       </c>
       <c r="F38" s="10">
-        <v>1</v>
+        <v>9.689658198069047</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
@@ -8376,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="10">
-        <v>1.6</v>
+        <v>19.447947290655982</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
@@ -8396,10 +8407,10 @@
         <v>16</v>
       </c>
       <c r="E40" s="5">
-        <v>3.04</v>
+        <v>41.48733670085722</v>
       </c>
       <c r="F40" s="10">
-        <v>1.8</v>
+        <v>71.687198413046801</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
@@ -8419,10 +8430,10 @@
         <v>52</v>
       </c>
       <c r="E41" s="5">
-        <v>1.41</v>
+        <v>4.6043646132977205</v>
       </c>
       <c r="F41" s="10">
-        <v>1.1000000000000001</v>
+        <v>8.8582875515555664</v>
       </c>
       <c r="G41" s="2">
         <v>0</v>
@@ -8442,10 +8453,10 @@
         <v>14</v>
       </c>
       <c r="E42" s="5">
-        <v>0.49</v>
+        <v>3.5666395482277267</v>
       </c>
       <c r="F42" s="10">
-        <v>0</v>
+        <v>25.965908032387219</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -9079,7 +9090,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AC122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D9FD2E-CF55-46A2-ABC9-188AF558752A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972CAC14-0649-48FC-B178-913DAE4B76E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="0" windowWidth="12800" windowHeight="13800" tabRatio="661" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="gas" sheetId="28" r:id="rId3"/>
     <sheet name="parameters" sheetId="15" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1082,7 +1082,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1146,6 +1146,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="fmtMidLeft" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -6707,16 +6708,16 @@
         <v>45085</v>
       </c>
       <c r="D19" s="5">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="E19" s="5">
-        <v>0</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="F19" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" s="5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="H19" s="5">
         <f>2700/1000</f>
@@ -6740,16 +6741,16 @@
         <v>45085</v>
       </c>
       <c r="D20" s="5">
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E20" s="5">
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F20" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" s="5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="H20" s="5">
         <f>2700/1000</f>
@@ -7474,7 +7475,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" bestFit="1" customWidth="1"/>
@@ -7483,9 +7484,10 @@
     <col min="4" max="4" width="6.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>132</v>
       </c>
@@ -7509,8 +7511,10 @@
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K1" s="1"/>
+      <c r="M1" s="25"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
@@ -7532,10 +7536,8 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -7557,10 +7559,8 @@
       <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -7582,10 +7582,8 @@
       <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -7607,10 +7605,8 @@
       <c r="G5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -7633,7 +7629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -7657,7 +7653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -7680,7 +7676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -7693,7 +7689,7 @@
       <c r="D9" s="6">
         <v>2</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="23">
         <v>116.9319533376742</v>
       </c>
       <c r="F9" s="10">
@@ -7703,7 +7699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -7726,7 +7722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -7749,7 +7745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -7772,7 +7768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -7795,7 +7791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
@@ -7818,7 +7814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
@@ -7831,7 +7827,7 @@
       <c r="D15" s="6">
         <v>2</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="23">
         <v>153.2423560757739</v>
       </c>
       <c r="F15" s="10">
@@ -7841,7 +7837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>35</v>
       </c>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972CAC14-0649-48FC-B178-913DAE4B76E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050F1F03-3E5E-47F4-9D7B-1109B8272685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="322">
   <si>
     <t>pH</t>
   </si>
@@ -155,9 +155,6 @@
     <t xml:space="preserve">Pender Island </t>
   </si>
   <si>
-    <t>Office building</t>
-  </si>
-  <si>
     <t>16-DC-07062023</t>
   </si>
   <si>
@@ -459,9 +456,6 @@
   </si>
   <si>
     <t xml:space="preserve">Commercial  </t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>rent_or_own</t>
@@ -1512,121 +1506,121 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.35">
@@ -1652,38 +1646,38 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" t="s">
         <v>56</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>57</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>58</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" t="s">
         <v>59</v>
       </c>
-      <c r="M2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" t="s">
         <v>60</v>
       </c>
-      <c r="O2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>61</v>
       </c>
-      <c r="R2" t="s">
-        <v>62</v>
-      </c>
       <c r="S2" s="12">
         <v>1</v>
       </c>
@@ -1691,52 +1685,52 @@
         <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y2" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD2" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="s">
         <v>64</v>
       </c>
-      <c r="Y2" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD2" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>65</v>
       </c>
-      <c r="AG2" t="s">
-        <v>66</v>
-      </c>
       <c r="AI2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ2">
         <v>15</v>
       </c>
       <c r="AK2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.35">
@@ -1762,88 +1756,88 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" t="s">
         <v>56</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>57</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>58</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" t="s">
         <v>59</v>
       </c>
-      <c r="M3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" t="s">
         <v>60</v>
       </c>
-      <c r="O3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P3" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>61</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" s="12">
+        <v>1</v>
+      </c>
+      <c r="T3" s="12">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W3" t="s">
         <v>62</v>
       </c>
-      <c r="S3" s="12">
-        <v>1</v>
-      </c>
-      <c r="T3" s="12">
-        <v>0</v>
-      </c>
-      <c r="U3" t="s">
-        <v>55</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>63</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="s">
         <v>64</v>
       </c>
-      <c r="Y3" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>65</v>
       </c>
-      <c r="AG3" t="s">
-        <v>66</v>
-      </c>
       <c r="AI3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.35">
@@ -1869,65 +1863,65 @@
         <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" t="s">
+        <v>59</v>
+      </c>
+      <c r="P4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="R4" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="12">
+        <v>1</v>
+      </c>
+      <c r="T4" s="12">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y4" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="s">
         <v>59</v>
       </c>
-      <c r="M4" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4" t="s">
-        <v>60</v>
-      </c>
-      <c r="O4" t="s">
-        <v>60</v>
-      </c>
-      <c r="P4" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R4" t="s">
-        <v>62</v>
-      </c>
-      <c r="S4" s="12">
-        <v>1</v>
-      </c>
-      <c r="T4" s="12">
-        <v>0</v>
-      </c>
-      <c r="U4" t="s">
-        <v>55</v>
-      </c>
-      <c r="X4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y4" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>60</v>
-      </c>
       <c r="AD4" s="12">
         <v>1</v>
       </c>
@@ -1935,22 +1929,22 @@
         <v>0</v>
       </c>
       <c r="AF4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG4" t="s">
         <v>65</v>
       </c>
-      <c r="AG4" t="s">
-        <v>66</v>
-      </c>
       <c r="AI4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ4">
         <v>5</v>
       </c>
       <c r="AK4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.35">
@@ -1976,50 +1970,50 @@
         <v>6</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" t="s">
+        <v>59</v>
+      </c>
+      <c r="P5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" t="s">
-        <v>69</v>
-      </c>
-      <c r="M5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" t="s">
-        <v>60</v>
-      </c>
-      <c r="O5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" s="12">
+        <v>1</v>
+      </c>
+      <c r="T5" s="12">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" t="s">
         <v>70</v>
       </c>
-      <c r="Q5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R5" t="s">
-        <v>62</v>
-      </c>
-      <c r="S5" s="12">
-        <v>1</v>
-      </c>
-      <c r="T5" s="12">
-        <v>0</v>
-      </c>
-      <c r="U5" t="s">
-        <v>55</v>
-      </c>
-      <c r="X5" t="s">
-        <v>71</v>
-      </c>
       <c r="Y5" s="12">
         <v>1</v>
       </c>
@@ -2033,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD5" s="12">
         <v>1</v>
@@ -2042,22 +2036,22 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG5" t="s">
         <v>65</v>
       </c>
-      <c r="AG5" t="s">
-        <v>66</v>
-      </c>
       <c r="AI5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ5">
         <v>6</v>
       </c>
       <c r="AK5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.35">
@@ -2071,7 +2065,7 @@
         <v>45035</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -2083,38 +2077,38 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" t="s">
         <v>56</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>57</v>
       </c>
-      <c r="K6" t="s">
-        <v>58</v>
-      </c>
       <c r="L6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" t="s">
         <v>60</v>
       </c>
-      <c r="O6" t="s">
-        <v>60</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
         <v>72</v>
       </c>
-      <c r="Q6" t="s">
-        <v>61</v>
-      </c>
-      <c r="R6" t="s">
-        <v>73</v>
-      </c>
       <c r="S6" s="12">
         <v>1</v>
       </c>
@@ -2122,49 +2116,49 @@
         <v>1</v>
       </c>
       <c r="U6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y6" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD6" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="s">
         <v>64</v>
       </c>
-      <c r="Y6" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
+      <c r="AG6" t="s">
         <v>65</v>
       </c>
-      <c r="AG6" t="s">
-        <v>66</v>
-      </c>
       <c r="AI6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ6">
         <v>5</v>
       </c>
       <c r="AK6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.35">
@@ -2178,10 +2172,10 @@
         <v>45035</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F7" s="6">
         <f>410</f>
@@ -2192,48 +2186,48 @@
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
         <v>57</v>
       </c>
-      <c r="K7" t="s">
-        <v>58</v>
-      </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q7" t="s">
         <v>60</v>
       </c>
-      <c r="O7" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
+        <v>61</v>
+      </c>
+      <c r="S7" s="12">
+        <v>1</v>
+      </c>
+      <c r="T7" s="12">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>54</v>
+      </c>
+      <c r="X7" t="s">
         <v>78</v>
       </c>
-      <c r="Q7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R7" t="s">
-        <v>62</v>
-      </c>
-      <c r="S7" s="12">
-        <v>1</v>
-      </c>
-      <c r="T7" s="12">
-        <v>0</v>
-      </c>
-      <c r="U7" t="s">
-        <v>55</v>
-      </c>
-      <c r="X7" t="s">
-        <v>79</v>
-      </c>
       <c r="Y7" s="12">
         <v>1</v>
       </c>
@@ -2247,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD7" s="12">
         <v>1</v>
@@ -2256,22 +2250,22 @@
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ7">
         <v>0.5</v>
       </c>
       <c r="AK7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.35">
@@ -2297,38 +2291,38 @@
         <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" t="s">
         <v>56</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>57</v>
       </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P8" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q8" t="s">
         <v>60</v>
       </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P8" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>61</v>
       </c>
-      <c r="R8" t="s">
-        <v>62</v>
-      </c>
       <c r="S8" s="12">
         <v>1</v>
       </c>
@@ -2336,52 +2330,52 @@
         <v>0</v>
       </c>
       <c r="U8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y8" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD8" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="s">
         <v>64</v>
       </c>
-      <c r="Y8" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AG8" t="s">
         <v>65</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>66</v>
       </c>
       <c r="AH8">
         <v>4.5</v>
       </c>
       <c r="AI8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ8">
         <v>10</v>
       </c>
       <c r="AK8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.35">
@@ -2407,85 +2401,85 @@
         <v>8</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" t="s">
         <v>56</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>57</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>58</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" t="s">
         <v>59</v>
       </c>
-      <c r="M9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
+        <v>59</v>
+      </c>
+      <c r="P9" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q9" t="s">
         <v>60</v>
       </c>
-      <c r="O9" t="s">
-        <v>60</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="R9" t="s">
+        <v>61</v>
+      </c>
+      <c r="S9" s="12">
+        <v>1</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>54</v>
+      </c>
+      <c r="X9" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y9" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD9" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="s">
         <v>74</v>
       </c>
-      <c r="Q9" t="s">
-        <v>61</v>
-      </c>
-      <c r="R9" t="s">
-        <v>62</v>
-      </c>
-      <c r="S9" s="12">
-        <v>1</v>
-      </c>
-      <c r="T9" s="12">
-        <v>0</v>
-      </c>
-      <c r="U9" t="s">
-        <v>55</v>
-      </c>
-      <c r="X9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y9" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="s">
+      <c r="AG9" t="s">
         <v>75</v>
       </c>
-      <c r="AG9" t="s">
-        <v>76</v>
-      </c>
       <c r="AI9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.35">
@@ -2511,36 +2505,36 @@
         <v>2.5</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P10" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q10" t="s">
         <v>60</v>
       </c>
-      <c r="O10" t="s">
-        <v>60</v>
-      </c>
-      <c r="P10" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>61</v>
       </c>
-      <c r="R10" t="s">
-        <v>62</v>
-      </c>
       <c r="S10" s="12">
         <v>1</v>
       </c>
@@ -2548,46 +2542,46 @@
         <v>0</v>
       </c>
       <c r="U10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y10" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD10" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="s">
         <v>64</v>
       </c>
-      <c r="Y10" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>65</v>
-      </c>
       <c r="AG10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.35">
@@ -2613,36 +2607,36 @@
         <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N11" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" t="s">
         <v>60</v>
       </c>
-      <c r="O11" t="s">
-        <v>60</v>
-      </c>
-      <c r="P11" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>61</v>
       </c>
-      <c r="R11" t="s">
-        <v>62</v>
-      </c>
       <c r="S11" s="12">
         <v>1</v>
       </c>
@@ -2650,46 +2644,46 @@
         <v>0</v>
       </c>
       <c r="U11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X11" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y11" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD11" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="s">
         <v>64</v>
       </c>
-      <c r="Y11" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>65</v>
-      </c>
       <c r="AG11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.35">
@@ -2715,38 +2709,38 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" t="s">
         <v>56</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>57</v>
       </c>
-      <c r="K12" t="s">
-        <v>58</v>
-      </c>
       <c r="L12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N12" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" t="s">
+        <v>59</v>
+      </c>
+      <c r="P12" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q12" t="s">
         <v>60</v>
       </c>
-      <c r="O12" t="s">
-        <v>60</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="R12" t="s">
         <v>72</v>
       </c>
-      <c r="Q12" t="s">
-        <v>61</v>
-      </c>
-      <c r="R12" t="s">
-        <v>73</v>
-      </c>
       <c r="S12" s="12">
         <v>1</v>
       </c>
@@ -2754,58 +2748,58 @@
         <v>1</v>
       </c>
       <c r="U12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V12" t="s">
+        <v>83</v>
+      </c>
+      <c r="W12" t="s">
         <v>84</v>
       </c>
-      <c r="W12" t="s">
-        <v>85</v>
-      </c>
       <c r="X12" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD12" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="s">
         <v>64</v>
       </c>
-      <c r="Y12" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="s">
+      <c r="AG12" t="s">
         <v>65</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>66</v>
       </c>
       <c r="AH12">
         <v>2.2000000000000002</v>
       </c>
       <c r="AI12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ12">
         <v>5.5</v>
       </c>
       <c r="AK12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.35">
@@ -2831,38 +2825,38 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" t="s">
         <v>56</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>57</v>
       </c>
-      <c r="K13" t="s">
-        <v>58</v>
-      </c>
       <c r="L13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N13" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" t="s">
+        <v>59</v>
+      </c>
+      <c r="P13" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q13" t="s">
         <v>60</v>
       </c>
-      <c r="O13" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>61</v>
       </c>
-      <c r="R13" t="s">
-        <v>62</v>
-      </c>
       <c r="S13" s="12">
         <v>1</v>
       </c>
@@ -2870,52 +2864,52 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s">
         <v>82</v>
       </c>
-      <c r="V13" t="s">
-        <v>83</v>
-      </c>
       <c r="X13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD13" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="s">
         <v>64</v>
       </c>
-      <c r="Y13" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>65</v>
-      </c>
       <c r="AG13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ13">
         <v>5</v>
       </c>
       <c r="AK13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.35">
@@ -2932,7 +2926,7 @@
         <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="F14" s="6">
         <v>10</v>
@@ -2941,36 +2935,36 @@
         <v>5</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" t="s">
         <v>57</v>
       </c>
-      <c r="K14" t="s">
-        <v>58</v>
-      </c>
       <c r="L14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N14" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" t="s">
+        <v>59</v>
+      </c>
+      <c r="P14" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" t="s">
         <v>60</v>
       </c>
-      <c r="O14" t="s">
-        <v>60</v>
-      </c>
-      <c r="P14" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>61</v>
       </c>
-      <c r="R14" t="s">
-        <v>62</v>
-      </c>
       <c r="S14" s="12">
         <v>1</v>
       </c>
@@ -2978,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y14" s="12">
         <v>1</v>
@@ -2996,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD14" s="12">
         <v>1</v>
@@ -3005,25 +2999,25 @@
         <v>0</v>
       </c>
       <c r="AF14" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG14" t="s">
         <v>65</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>66</v>
       </c>
       <c r="AH14">
         <v>8</v>
       </c>
       <c r="AI14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ14">
         <v>6</v>
       </c>
       <c r="AK14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.35">
@@ -3049,38 +3043,38 @@
         <v>3</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" t="s">
+        <v>59</v>
+      </c>
+      <c r="O15" t="s">
+        <v>59</v>
+      </c>
+      <c r="P15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q15" t="s">
         <v>60</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" t="s">
-        <v>69</v>
-      </c>
-      <c r="M15" t="s">
-        <v>55</v>
-      </c>
-      <c r="N15" t="s">
-        <v>60</v>
-      </c>
-      <c r="O15" t="s">
-        <v>60</v>
-      </c>
-      <c r="P15" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>61</v>
       </c>
-      <c r="R15" t="s">
-        <v>62</v>
-      </c>
       <c r="S15" s="12">
         <v>1</v>
       </c>
@@ -3088,52 +3082,52 @@
         <v>0</v>
       </c>
       <c r="U15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="X15" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y15" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="s">
         <v>64</v>
       </c>
-      <c r="Y15" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD15" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE15" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="s">
+      <c r="AG15" t="s">
         <v>65</v>
       </c>
-      <c r="AG15" t="s">
-        <v>66</v>
-      </c>
       <c r="AI15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ15">
         <v>5.5</v>
       </c>
       <c r="AK15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.35">
@@ -3150,7 +3144,7 @@
         <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F16" s="6">
         <v>10</v>
@@ -3159,36 +3153,36 @@
         <v>0.5</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" t="s">
         <v>57</v>
       </c>
-      <c r="K16" t="s">
-        <v>58</v>
-      </c>
       <c r="L16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N16" t="s">
+        <v>59</v>
+      </c>
+      <c r="O16" t="s">
+        <v>59</v>
+      </c>
+      <c r="P16" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q16" t="s">
         <v>60</v>
       </c>
-      <c r="O16" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="R16" t="s">
         <v>72</v>
       </c>
-      <c r="Q16" t="s">
-        <v>61</v>
-      </c>
-      <c r="R16" t="s">
-        <v>73</v>
-      </c>
       <c r="S16" s="12">
         <v>1</v>
       </c>
@@ -3196,10 +3190,10 @@
         <v>1</v>
       </c>
       <c r="U16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y16" s="12">
         <v>1</v>
@@ -3214,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD16" s="12">
         <v>1</v>
@@ -3223,27 +3217,27 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG16" t="s">
         <v>65</v>
       </c>
-      <c r="AG16" t="s">
-        <v>66</v>
-      </c>
       <c r="AI16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C17" s="13">
         <v>45084</v>
@@ -3261,38 +3255,38 @@
         <v>3.5</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" t="s">
         <v>56</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>57</v>
       </c>
-      <c r="K17" t="s">
-        <v>58</v>
-      </c>
       <c r="L17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N17" t="s">
+        <v>59</v>
+      </c>
+      <c r="O17" t="s">
+        <v>59</v>
+      </c>
+      <c r="P17" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q17" t="s">
         <v>60</v>
       </c>
-      <c r="O17" t="s">
-        <v>60</v>
-      </c>
-      <c r="P17" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>61</v>
       </c>
-      <c r="R17" t="s">
-        <v>62</v>
-      </c>
       <c r="S17" s="12">
         <v>1</v>
       </c>
@@ -3300,57 +3294,57 @@
         <v>0</v>
       </c>
       <c r="U17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="s">
         <v>64</v>
       </c>
-      <c r="Y17" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD17" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="s">
+      <c r="AG17" t="s">
         <v>65</v>
       </c>
-      <c r="AG17" t="s">
-        <v>66</v>
-      </c>
       <c r="AI17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ17">
         <v>4</v>
       </c>
       <c r="AK17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="13">
         <v>45084</v>
@@ -3368,38 +3362,38 @@
         <v>5</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" t="s">
         <v>56</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>57</v>
       </c>
-      <c r="K18" t="s">
-        <v>58</v>
-      </c>
       <c r="L18" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O18" t="s">
+        <v>59</v>
+      </c>
+      <c r="P18" t="s">
         <v>69</v>
       </c>
-      <c r="M18" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="Q18" t="s">
         <v>60</v>
       </c>
-      <c r="O18" t="s">
-        <v>60</v>
-      </c>
-      <c r="P18" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>61</v>
       </c>
-      <c r="R18" t="s">
-        <v>62</v>
-      </c>
       <c r="S18" s="12">
         <v>1</v>
       </c>
@@ -3407,57 +3401,57 @@
         <v>0</v>
       </c>
       <c r="U18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X18" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="s">
         <v>64</v>
       </c>
-      <c r="Y18" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD18" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE18" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="s">
+      <c r="AG18" t="s">
         <v>65</v>
       </c>
-      <c r="AG18" t="s">
-        <v>66</v>
-      </c>
       <c r="AI18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ18">
         <v>5</v>
       </c>
       <c r="AK18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="13">
         <v>45085</v>
@@ -3475,38 +3469,38 @@
         <v>2</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" t="s">
         <v>56</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>57</v>
       </c>
-      <c r="K19" t="s">
-        <v>58</v>
-      </c>
       <c r="L19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N19" t="s">
+        <v>59</v>
+      </c>
+      <c r="O19" t="s">
+        <v>59</v>
+      </c>
+      <c r="P19" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q19" t="s">
         <v>60</v>
       </c>
-      <c r="O19" t="s">
-        <v>60</v>
-      </c>
-      <c r="P19" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>61</v>
       </c>
-      <c r="R19" t="s">
-        <v>62</v>
-      </c>
       <c r="S19" s="12">
         <v>1</v>
       </c>
@@ -3514,60 +3508,60 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="W19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="X19" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y19" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="s">
         <v>64</v>
       </c>
-      <c r="Y19" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE19" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="s">
+      <c r="AG19" t="s">
         <v>65</v>
       </c>
-      <c r="AG19" t="s">
-        <v>66</v>
-      </c>
       <c r="AI19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ19">
         <v>2.5</v>
       </c>
       <c r="AK19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="13">
         <v>45085</v>
@@ -3585,38 +3579,38 @@
         <v>3</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J20" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" t="s">
+        <v>59</v>
+      </c>
+      <c r="P20" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q20" t="s">
         <v>60</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="R20" t="s">
         <v>90</v>
       </c>
-      <c r="J20" t="s">
-        <v>57</v>
-      </c>
-      <c r="K20" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" t="s">
-        <v>69</v>
-      </c>
-      <c r="M20" t="s">
-        <v>55</v>
-      </c>
-      <c r="N20" t="s">
-        <v>60</v>
-      </c>
-      <c r="O20" t="s">
-        <v>60</v>
-      </c>
-      <c r="P20" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>61</v>
-      </c>
-      <c r="R20" t="s">
-        <v>91</v>
-      </c>
       <c r="S20" s="12">
         <v>0</v>
       </c>
@@ -3624,60 +3618,60 @@
         <v>1</v>
       </c>
       <c r="U20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X20" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y20" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="s">
         <v>64</v>
       </c>
-      <c r="Y20" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE20" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="s">
+      <c r="AG20" t="s">
         <v>65</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>66</v>
       </c>
       <c r="AH20">
         <v>2.4</v>
       </c>
       <c r="AI20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ20">
         <v>9.5</v>
       </c>
       <c r="AK20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="13">
         <v>45085</v>
@@ -3695,38 +3689,38 @@
         <v>3</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" t="s">
         <v>56</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>57</v>
       </c>
-      <c r="K21" t="s">
-        <v>58</v>
-      </c>
       <c r="L21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N21" t="s">
+        <v>59</v>
+      </c>
+      <c r="O21" t="s">
+        <v>59</v>
+      </c>
+      <c r="P21" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q21" t="s">
         <v>60</v>
       </c>
-      <c r="O21" t="s">
-        <v>60</v>
-      </c>
-      <c r="P21" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>61</v>
       </c>
-      <c r="R21" t="s">
-        <v>62</v>
-      </c>
       <c r="S21" s="12">
         <v>1</v>
       </c>
@@ -3734,60 +3728,60 @@
         <v>0</v>
       </c>
       <c r="U21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X21" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y21" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD21" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="s">
         <v>64</v>
       </c>
-      <c r="Y21" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE21" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="s">
+      <c r="AG21" t="s">
         <v>65</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>66</v>
       </c>
       <c r="AH21">
         <v>2.4</v>
       </c>
       <c r="AI21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ21">
         <v>5</v>
       </c>
       <c r="AK21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -3796,7 +3790,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F22" s="6">
         <v>200</v>
@@ -3805,36 +3799,36 @@
         <v>0.25</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" t="s">
         <v>57</v>
       </c>
-      <c r="K22" t="s">
-        <v>58</v>
-      </c>
       <c r="L22" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" t="s">
+        <v>59</v>
+      </c>
+      <c r="O22" t="s">
+        <v>59</v>
+      </c>
+      <c r="P22" t="s">
         <v>69</v>
       </c>
-      <c r="M22" t="s">
-        <v>55</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="Q22" t="s">
         <v>60</v>
       </c>
-      <c r="O22" t="s">
-        <v>60</v>
-      </c>
-      <c r="P22" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>61</v>
       </c>
-      <c r="R22" t="s">
-        <v>62</v>
-      </c>
       <c r="S22" s="12">
         <v>1</v>
       </c>
@@ -3842,10 +3836,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y22" s="12">
         <v>1</v>
@@ -3860,7 +3854,7 @@
         <v>1</v>
       </c>
       <c r="AC22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD22" s="12">
         <v>1</v>
@@ -3869,39 +3863,39 @@
         <v>0</v>
       </c>
       <c r="AF22" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG22" t="s">
         <v>65</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>66</v>
       </c>
       <c r="AH22">
         <v>5</v>
       </c>
       <c r="AI22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ22">
         <v>5.5</v>
       </c>
       <c r="AK22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
@@ -3913,38 +3907,38 @@
         <v>0.25</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" t="s">
         <v>56</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>57</v>
       </c>
-      <c r="K23" t="s">
-        <v>58</v>
-      </c>
       <c r="L23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N23" t="s">
+        <v>59</v>
+      </c>
+      <c r="O23" t="s">
+        <v>59</v>
+      </c>
+      <c r="P23" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q23" t="s">
         <v>60</v>
       </c>
-      <c r="O23" t="s">
-        <v>60</v>
-      </c>
-      <c r="P23" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>61</v>
       </c>
-      <c r="R23" t="s">
-        <v>62</v>
-      </c>
       <c r="S23" s="12">
         <v>1</v>
       </c>
@@ -3952,10 +3946,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y23" s="12">
         <v>1</v>
@@ -3970,7 +3964,7 @@
         <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD23" s="12">
         <v>1</v>
@@ -3979,36 +3973,36 @@
         <v>0</v>
       </c>
       <c r="AF23" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG23" t="s">
         <v>65</v>
       </c>
-      <c r="AG23" t="s">
-        <v>66</v>
-      </c>
       <c r="AI23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F24" s="6">
         <v>23</v>
@@ -4017,35 +4011,35 @@
         <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24" t="s">
         <v>57</v>
       </c>
-      <c r="K24" t="s">
-        <v>58</v>
-      </c>
       <c r="L24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O24" t="s">
+        <v>59</v>
+      </c>
+      <c r="P24" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q24" t="s">
         <v>60</v>
       </c>
-      <c r="P24" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>61</v>
-      </c>
       <c r="R24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S24" s="12">
         <v>1</v>
@@ -4054,14 +4048,14 @@
         <v>1</v>
       </c>
       <c r="U24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W24" t="s">
+        <v>250</v>
+      </c>
+      <c r="X24" t="s">
         <v>252</v>
       </c>
-      <c r="X24" t="s">
-        <v>254</v>
-      </c>
       <c r="Y24" s="12">
         <v>1</v>
       </c>
@@ -4075,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD24" s="12">
         <v>1</v>
@@ -4084,36 +4078,36 @@
         <v>1</v>
       </c>
       <c r="AF24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AK24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -4125,37 +4119,37 @@
         <v>3</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J25" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" t="s">
+        <v>54</v>
+      </c>
+      <c r="O25" t="s">
+        <v>59</v>
+      </c>
+      <c r="P25" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q25" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J25" t="s">
-        <v>57</v>
-      </c>
-      <c r="K25" t="s">
-        <v>58</v>
-      </c>
-      <c r="L25" t="s">
-        <v>69</v>
-      </c>
-      <c r="M25" t="s">
-        <v>55</v>
-      </c>
-      <c r="N25" t="s">
-        <v>55</v>
-      </c>
-      <c r="O25" t="s">
-        <v>60</v>
-      </c>
-      <c r="P25" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>61</v>
-      </c>
       <c r="R25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S25" s="12">
         <v>1</v>
@@ -4164,13 +4158,13 @@
         <v>1</v>
       </c>
       <c r="U25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W25" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X25" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Y25" s="12">
         <v>1</v>
@@ -4185,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="AC25" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD25" s="12">
         <v>1</v>
@@ -4194,39 +4188,39 @@
         <v>1</v>
       </c>
       <c r="AF25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ25">
         <v>2</v>
       </c>
       <c r="AK25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -4238,37 +4232,37 @@
         <v>3</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" t="s">
+        <v>54</v>
+      </c>
+      <c r="O26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P26" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q26" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J26" t="s">
-        <v>57</v>
-      </c>
-      <c r="K26" t="s">
-        <v>58</v>
-      </c>
-      <c r="L26" t="s">
-        <v>69</v>
-      </c>
-      <c r="M26" t="s">
-        <v>55</v>
-      </c>
-      <c r="N26" t="s">
-        <v>55</v>
-      </c>
-      <c r="O26" t="s">
-        <v>60</v>
-      </c>
-      <c r="P26" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>61</v>
-      </c>
       <c r="R26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S26" s="12">
         <v>1</v>
@@ -4277,13 +4271,13 @@
         <v>1</v>
       </c>
       <c r="U26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y26" s="12">
         <v>1</v>
@@ -4298,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="AC26" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD26" s="12">
         <v>1</v>
@@ -4307,39 +4301,39 @@
         <v>1</v>
       </c>
       <c r="AF26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ26">
         <v>2</v>
       </c>
       <c r="AK26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -4351,37 +4345,37 @@
         <v>3</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" t="s">
+        <v>68</v>
+      </c>
+      <c r="M27" t="s">
+        <v>54</v>
+      </c>
+      <c r="N27" t="s">
+        <v>54</v>
+      </c>
+      <c r="O27" t="s">
+        <v>59</v>
+      </c>
+      <c r="P27" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q27" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J27" t="s">
-        <v>57</v>
-      </c>
-      <c r="K27" t="s">
-        <v>58</v>
-      </c>
-      <c r="L27" t="s">
-        <v>69</v>
-      </c>
-      <c r="M27" t="s">
-        <v>55</v>
-      </c>
-      <c r="N27" t="s">
-        <v>55</v>
-      </c>
-      <c r="O27" t="s">
-        <v>60</v>
-      </c>
-      <c r="P27" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>61</v>
-      </c>
       <c r="R27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S27" s="12">
         <v>1</v>
@@ -4390,13 +4384,13 @@
         <v>1</v>
       </c>
       <c r="U27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y27" s="12">
         <v>1</v>
@@ -4411,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="AC27" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD27" s="12">
         <v>1</v>
@@ -4420,39 +4414,39 @@
         <v>1</v>
       </c>
       <c r="AF27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ27">
         <v>2</v>
       </c>
       <c r="AK27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -4464,37 +4458,37 @@
         <v>3</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" t="s">
+        <v>54</v>
+      </c>
+      <c r="O28" t="s">
+        <v>59</v>
+      </c>
+      <c r="P28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q28" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J28" t="s">
-        <v>57</v>
-      </c>
-      <c r="K28" t="s">
-        <v>58</v>
-      </c>
-      <c r="L28" t="s">
-        <v>69</v>
-      </c>
-      <c r="M28" t="s">
-        <v>55</v>
-      </c>
-      <c r="N28" t="s">
-        <v>55</v>
-      </c>
-      <c r="O28" t="s">
-        <v>60</v>
-      </c>
-      <c r="P28" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>61</v>
-      </c>
       <c r="R28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S28" s="12">
         <v>1</v>
@@ -4503,13 +4497,13 @@
         <v>1</v>
       </c>
       <c r="U28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y28" s="12">
         <v>1</v>
@@ -4524,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="AC28" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD28" s="12">
         <v>1</v>
@@ -4533,39 +4527,39 @@
         <v>1</v>
       </c>
       <c r="AF28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ28">
         <v>2</v>
       </c>
       <c r="AK28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM28" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -4577,37 +4571,37 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" t="s">
+        <v>68</v>
+      </c>
+      <c r="M29" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" t="s">
+        <v>54</v>
+      </c>
+      <c r="O29" t="s">
+        <v>59</v>
+      </c>
+      <c r="P29" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q29" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J29" t="s">
-        <v>57</v>
-      </c>
-      <c r="K29" t="s">
-        <v>58</v>
-      </c>
-      <c r="L29" t="s">
-        <v>69</v>
-      </c>
-      <c r="M29" t="s">
-        <v>60</v>
-      </c>
-      <c r="N29" t="s">
-        <v>55</v>
-      </c>
-      <c r="O29" t="s">
-        <v>60</v>
-      </c>
-      <c r="P29" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>61</v>
-      </c>
       <c r="R29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S29" s="12">
         <v>1</v>
@@ -4616,13 +4610,13 @@
         <v>1</v>
       </c>
       <c r="U29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W29" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X29" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Y29" s="12">
         <v>1</v>
@@ -4637,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="AC29" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD29" s="12">
         <v>1</v>
@@ -4646,36 +4640,36 @@
         <v>1</v>
       </c>
       <c r="AF29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ29">
         <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
@@ -4687,37 +4681,37 @@
         <v>10</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" t="s">
+        <v>54</v>
+      </c>
+      <c r="O30" t="s">
+        <v>59</v>
+      </c>
+      <c r="P30" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q30" t="s">
         <v>60</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J30" t="s">
-        <v>57</v>
-      </c>
-      <c r="K30" t="s">
-        <v>58</v>
-      </c>
-      <c r="L30" t="s">
-        <v>69</v>
-      </c>
-      <c r="M30" t="s">
-        <v>55</v>
-      </c>
-      <c r="N30" t="s">
-        <v>55</v>
-      </c>
-      <c r="O30" t="s">
-        <v>60</v>
-      </c>
-      <c r="P30" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>61</v>
-      </c>
       <c r="R30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S30" s="12">
         <v>1</v>
@@ -4726,66 +4720,66 @@
         <v>1</v>
       </c>
       <c r="U30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W30" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="X30" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y30" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD30" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="s">
         <v>256</v>
       </c>
-      <c r="Y30" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD30" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE30" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>258</v>
-      </c>
       <c r="AG30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AI30" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AK30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -4797,37 +4791,37 @@
         <v>10</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" t="s">
+        <v>68</v>
+      </c>
+      <c r="M31" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" t="s">
+        <v>54</v>
+      </c>
+      <c r="O31" t="s">
+        <v>59</v>
+      </c>
+      <c r="P31" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q31" t="s">
         <v>60</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J31" t="s">
-        <v>57</v>
-      </c>
-      <c r="K31" t="s">
-        <v>58</v>
-      </c>
-      <c r="L31" t="s">
-        <v>69</v>
-      </c>
-      <c r="M31" t="s">
-        <v>55</v>
-      </c>
-      <c r="N31" t="s">
-        <v>55</v>
-      </c>
-      <c r="O31" t="s">
-        <v>60</v>
-      </c>
-      <c r="P31" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>61</v>
-      </c>
       <c r="R31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S31" s="12">
         <v>1</v>
@@ -4836,10 +4830,10 @@
         <v>1</v>
       </c>
       <c r="U31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y31" s="12">
         <v>1</v>
@@ -4854,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="AC31" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD31" s="12">
         <v>1</v>
@@ -4863,39 +4857,39 @@
         <v>1</v>
       </c>
       <c r="AF31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AK31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM31" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F32" s="6">
         <v>35</v>
@@ -4904,35 +4898,35 @@
         <v>6</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K32" t="s">
+        <v>245</v>
+      </c>
+      <c r="L32" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" t="s">
+        <v>54</v>
+      </c>
+      <c r="O32" t="s">
+        <v>59</v>
+      </c>
+      <c r="P32" t="s">
         <v>247</v>
       </c>
-      <c r="L32" t="s">
-        <v>248</v>
-      </c>
-      <c r="M32" t="s">
-        <v>55</v>
-      </c>
-      <c r="N32" t="s">
-        <v>55</v>
-      </c>
-      <c r="O32" t="s">
+      <c r="Q32" t="s">
         <v>60</v>
       </c>
-      <c r="P32" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>61</v>
-      </c>
       <c r="R32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S32" s="12">
         <v>1</v>
@@ -4941,13 +4935,13 @@
         <v>1</v>
       </c>
       <c r="U32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W32" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y32" s="12">
         <v>1</v>
@@ -4962,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD32" s="12">
         <v>1</v>
@@ -4971,36 +4965,36 @@
         <v>1</v>
       </c>
       <c r="AF32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AI32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ32">
         <v>5</v>
       </c>
       <c r="AK32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM32" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
@@ -5012,37 +5006,37 @@
         <v>2</v>
       </c>
       <c r="H33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" t="s">
+        <v>56</v>
+      </c>
+      <c r="K33" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" t="s">
+        <v>68</v>
+      </c>
+      <c r="M33" t="s">
+        <v>54</v>
+      </c>
+      <c r="N33" t="s">
+        <v>54</v>
+      </c>
+      <c r="O33" t="s">
+        <v>59</v>
+      </c>
+      <c r="P33" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q33" t="s">
         <v>60</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J33" t="s">
-        <v>57</v>
-      </c>
-      <c r="K33" t="s">
-        <v>58</v>
-      </c>
-      <c r="L33" t="s">
-        <v>69</v>
-      </c>
-      <c r="M33" t="s">
-        <v>55</v>
-      </c>
-      <c r="N33" t="s">
-        <v>55</v>
-      </c>
-      <c r="O33" t="s">
-        <v>60</v>
-      </c>
-      <c r="P33" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>61</v>
-      </c>
       <c r="R33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S33" s="12">
         <v>1</v>
@@ -5051,13 +5045,13 @@
         <v>1</v>
       </c>
       <c r="U33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W33" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X33" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Y33" s="12">
         <v>0</v>
@@ -5072,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="AC33" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD33" s="12">
         <v>1</v>
@@ -5081,39 +5075,39 @@
         <v>1</v>
       </c>
       <c r="AF33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH33">
         <v>20</v>
       </c>
       <c r="AI33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ33">
         <v>2</v>
       </c>
       <c r="AK33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -5125,37 +5119,37 @@
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K34" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" t="s">
+        <v>68</v>
+      </c>
+      <c r="M34" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" t="s">
+        <v>54</v>
+      </c>
+      <c r="O34" t="s">
+        <v>59</v>
+      </c>
+      <c r="P34" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q34" t="s">
         <v>60</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J34" t="s">
-        <v>57</v>
-      </c>
-      <c r="K34" t="s">
-        <v>58</v>
-      </c>
-      <c r="L34" t="s">
-        <v>69</v>
-      </c>
-      <c r="M34" t="s">
-        <v>55</v>
-      </c>
-      <c r="N34" t="s">
-        <v>55</v>
-      </c>
-      <c r="O34" t="s">
-        <v>60</v>
-      </c>
-      <c r="P34" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>61</v>
-      </c>
       <c r="R34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S34" s="12">
         <v>1</v>
@@ -5164,13 +5158,13 @@
         <v>1</v>
       </c>
       <c r="U34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W34" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y34" s="12">
         <v>1</v>
@@ -5185,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="AC34" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD34" s="12">
         <v>1</v>
@@ -5194,42 +5188,42 @@
         <v>1</v>
       </c>
       <c r="AF34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AG34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ34">
         <v>2</v>
       </c>
       <c r="AK34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM34" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" s="6">
         <v>88</v>
@@ -5238,32 +5232,32 @@
         <v>0.25</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" t="s">
+        <v>56</v>
+      </c>
+      <c r="K35" t="s">
         <v>57</v>
       </c>
-      <c r="K35" t="s">
-        <v>58</v>
-      </c>
       <c r="L35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S35" s="12">
         <v>1</v>
@@ -5272,13 +5266,13 @@
         <v>1</v>
       </c>
       <c r="U35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W35" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X35" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Y35" s="12">
         <v>1</v>
@@ -5293,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="AC35" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD35" s="12">
         <v>1</v>
@@ -5302,39 +5296,39 @@
         <v>1</v>
       </c>
       <c r="AF35" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG35" t="s">
         <v>65</v>
       </c>
-      <c r="AG35" t="s">
-        <v>66</v>
-      </c>
       <c r="AI35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ35">
         <v>0.33</v>
       </c>
       <c r="AK35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM35" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -5346,52 +5340,52 @@
         <v>3</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J36" t="s">
+        <v>56</v>
+      </c>
+      <c r="K36" t="s">
         <v>57</v>
       </c>
-      <c r="K36" t="s">
-        <v>58</v>
-      </c>
       <c r="L36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P36" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q36" t="s">
+        <v>248</v>
+      </c>
+      <c r="R36" t="s">
+        <v>72</v>
+      </c>
+      <c r="S36" s="12">
+        <v>1</v>
+      </c>
+      <c r="T36" s="12">
+        <v>1</v>
+      </c>
+      <c r="U36" t="s">
+        <v>54</v>
+      </c>
+      <c r="W36" t="s">
         <v>250</v>
       </c>
-      <c r="R36" t="s">
-        <v>73</v>
-      </c>
-      <c r="S36" s="12">
-        <v>1</v>
-      </c>
-      <c r="T36" s="12">
-        <v>1</v>
-      </c>
-      <c r="U36" t="s">
-        <v>55</v>
-      </c>
-      <c r="W36" t="s">
-        <v>252</v>
-      </c>
       <c r="X36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y36" s="12">
         <v>1</v>
@@ -5406,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="AC36" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD36" s="12">
         <v>0</v>
@@ -5415,39 +5409,39 @@
         <v>1</v>
       </c>
       <c r="AF36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AI36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ36">
         <v>6</v>
       </c>
       <c r="AK36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -5459,37 +5453,37 @@
         <v>3</v>
       </c>
       <c r="H37" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J37" t="s">
+        <v>56</v>
+      </c>
+      <c r="K37" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37" t="s">
+        <v>59</v>
+      </c>
+      <c r="N37" t="s">
+        <v>54</v>
+      </c>
+      <c r="O37" t="s">
+        <v>59</v>
+      </c>
+      <c r="P37" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q37" t="s">
         <v>60</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J37" t="s">
-        <v>57</v>
-      </c>
-      <c r="K37" t="s">
-        <v>58</v>
-      </c>
-      <c r="L37" t="s">
-        <v>69</v>
-      </c>
-      <c r="M37" t="s">
-        <v>60</v>
-      </c>
-      <c r="N37" t="s">
-        <v>55</v>
-      </c>
-      <c r="O37" t="s">
-        <v>60</v>
-      </c>
-      <c r="P37" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>61</v>
-      </c>
       <c r="R37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S37" s="12">
         <v>1</v>
@@ -5498,66 +5492,66 @@
         <v>1</v>
       </c>
       <c r="U37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W37" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X37" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y37" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AE37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="s">
         <v>64</v>
       </c>
-      <c r="Y37" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AE37" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF37" t="s">
+      <c r="AG37" t="s">
         <v>65</v>
       </c>
-      <c r="AG37" t="s">
-        <v>66</v>
-      </c>
       <c r="AI37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ37">
         <v>5</v>
       </c>
       <c r="AK37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -5569,52 +5563,52 @@
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s">
+        <v>56</v>
+      </c>
+      <c r="K38" t="s">
         <v>57</v>
       </c>
-      <c r="K38" t="s">
-        <v>58</v>
-      </c>
       <c r="L38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q38" t="s">
+        <v>248</v>
+      </c>
+      <c r="R38" t="s">
+        <v>72</v>
+      </c>
+      <c r="S38" s="12">
+        <v>1</v>
+      </c>
+      <c r="T38" s="12">
+        <v>1</v>
+      </c>
+      <c r="U38" t="s">
+        <v>54</v>
+      </c>
+      <c r="W38" t="s">
         <v>250</v>
       </c>
-      <c r="R38" t="s">
-        <v>73</v>
-      </c>
-      <c r="S38" s="12">
-        <v>1</v>
-      </c>
-      <c r="T38" s="12">
-        <v>1</v>
-      </c>
-      <c r="U38" t="s">
-        <v>55</v>
-      </c>
-      <c r="W38" t="s">
-        <v>252</v>
-      </c>
       <c r="X38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y38" s="12">
         <v>1</v>
@@ -5629,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="AC38" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD38" s="12">
         <v>0</v>
@@ -5638,39 +5632,39 @@
         <v>1</v>
       </c>
       <c r="AF38" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG38" t="s">
         <v>65</v>
       </c>
-      <c r="AG38" t="s">
-        <v>66</v>
-      </c>
       <c r="AI38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AK38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM38" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" s="6">
         <v>10</v>
@@ -5679,35 +5673,35 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" t="s">
+        <v>56</v>
+      </c>
+      <c r="K39" t="s">
         <v>57</v>
       </c>
-      <c r="K39" t="s">
-        <v>58</v>
-      </c>
       <c r="L39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M39" t="s">
+        <v>59</v>
+      </c>
+      <c r="N39" t="s">
+        <v>54</v>
+      </c>
+      <c r="O39" t="s">
+        <v>59</v>
+      </c>
+      <c r="P39" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q39" t="s">
         <v>60</v>
       </c>
-      <c r="N39" t="s">
-        <v>55</v>
-      </c>
-      <c r="O39" t="s">
-        <v>60</v>
-      </c>
-      <c r="P39" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>61</v>
-      </c>
       <c r="R39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S39" s="12">
         <v>1</v>
@@ -5716,13 +5710,13 @@
         <v>1</v>
       </c>
       <c r="U39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y39" s="12">
         <v>1</v>
@@ -5737,7 +5731,7 @@
         <v>0</v>
       </c>
       <c r="AC39" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD39" s="12">
         <v>1</v>
@@ -5746,39 +5740,39 @@
         <v>1</v>
       </c>
       <c r="AF39" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG39" t="s">
         <v>65</v>
       </c>
-      <c r="AG39" t="s">
-        <v>66</v>
-      </c>
       <c r="AI39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ39">
         <v>1</v>
       </c>
       <c r="AK39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM39" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -5790,34 +5784,34 @@
         <v>1</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J40" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" t="s">
         <v>57</v>
       </c>
-      <c r="K40" t="s">
-        <v>58</v>
-      </c>
       <c r="L40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q40" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S40" s="12">
         <v>1</v>
@@ -5826,13 +5820,13 @@
         <v>1</v>
       </c>
       <c r="U40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W40" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="X40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y40" s="12">
         <v>1</v>
@@ -5847,7 +5841,7 @@
         <v>0</v>
       </c>
       <c r="AC40" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD40" s="12">
         <v>1</v>
@@ -5856,42 +5850,42 @@
         <v>1</v>
       </c>
       <c r="AF40" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG40" t="s">
         <v>65</v>
       </c>
-      <c r="AG40" t="s">
-        <v>66</v>
-      </c>
       <c r="AI40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ40">
         <v>1</v>
       </c>
       <c r="AK40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM40" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F41" s="6">
         <v>52</v>
@@ -5900,50 +5894,50 @@
         <v>0.5</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" t="s">
+        <v>56</v>
+      </c>
+      <c r="K41" t="s">
         <v>57</v>
       </c>
-      <c r="K41" t="s">
-        <v>58</v>
-      </c>
       <c r="L41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q41" t="s">
+        <v>248</v>
+      </c>
+      <c r="R41" t="s">
+        <v>72</v>
+      </c>
+      <c r="S41" s="12">
+        <v>1</v>
+      </c>
+      <c r="T41" s="12">
+        <v>1</v>
+      </c>
+      <c r="U41" t="s">
+        <v>59</v>
+      </c>
+      <c r="W41" t="s">
         <v>250</v>
       </c>
-      <c r="R41" t="s">
-        <v>73</v>
-      </c>
-      <c r="S41" s="12">
-        <v>1</v>
-      </c>
-      <c r="T41" s="12">
-        <v>1</v>
-      </c>
-      <c r="U41" t="s">
-        <v>60</v>
-      </c>
-      <c r="W41" t="s">
-        <v>252</v>
-      </c>
       <c r="X41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y41" s="12">
         <v>1</v>
@@ -5958,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="AC41" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD41" s="12">
         <v>0</v>
@@ -5967,39 +5961,39 @@
         <v>1</v>
       </c>
       <c r="AF41" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG41" t="s">
         <v>65</v>
       </c>
-      <c r="AG41" t="s">
-        <v>66</v>
-      </c>
       <c r="AI41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ41">
         <v>0.5</v>
       </c>
       <c r="AK41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM41" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -6011,37 +6005,37 @@
         <v>0.25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J42" t="s">
+        <v>56</v>
+      </c>
+      <c r="K42" t="s">
         <v>57</v>
       </c>
-      <c r="K42" t="s">
-        <v>58</v>
-      </c>
       <c r="L42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q42" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S42" s="12">
         <v>1</v>
@@ -6050,10 +6044,10 @@
         <v>1</v>
       </c>
       <c r="U42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y42" s="12">
         <v>1</v>
@@ -6068,7 +6062,7 @@
         <v>0</v>
       </c>
       <c r="AC42" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AD42" s="12">
         <v>0</v>
@@ -6077,25 +6071,25 @@
         <v>1</v>
       </c>
       <c r="AF42" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG42" t="s">
         <v>65</v>
       </c>
-      <c r="AG42" t="s">
-        <v>66</v>
-      </c>
       <c r="AI42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AJ42">
         <v>0.33</v>
       </c>
       <c r="AK42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AL42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AM42" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -6123,34 +6117,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>175</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -6635,10 +6629,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C17" s="13">
         <v>45084</v>
@@ -6667,10 +6661,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="13">
         <v>45084</v>
@@ -6699,10 +6693,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="13">
         <v>45085</v>
@@ -6732,10 +6726,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="13">
         <v>45085</v>
@@ -6765,10 +6759,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="13">
         <v>45085</v>
@@ -6797,10 +6791,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -6829,10 +6823,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
@@ -6861,10 +6855,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -6893,10 +6887,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -6925,10 +6919,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -6957,10 +6951,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -6989,10 +6983,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -7021,10 +7015,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -7053,10 +7047,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -7085,10 +7079,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -7117,10 +7111,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -7149,10 +7143,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -7181,10 +7175,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -7213,10 +7207,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -7245,10 +7239,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -7277,10 +7271,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -7309,10 +7303,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -7341,10 +7335,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -7373,10 +7367,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -7405,10 +7399,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -7437,10 +7431,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -7489,25 +7483,25 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>134</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -7862,10 +7856,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C17" s="13">
         <v>45084</v>
@@ -7885,10 +7879,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="13">
         <v>45084</v>
@@ -7908,10 +7902,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="13">
         <v>45085</v>
@@ -7931,10 +7925,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="13">
         <v>45085</v>
@@ -7954,10 +7948,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="13">
         <v>45085</v>
@@ -7977,10 +7971,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="13">
         <v>45098</v>
@@ -8000,10 +7994,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="13">
         <v>45098</v>
@@ -8023,10 +8017,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -8046,10 +8040,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -8069,10 +8063,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -8092,10 +8086,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -8115,10 +8109,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -8138,10 +8132,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -8161,10 +8155,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -8184,10 +8178,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -8207,10 +8201,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -8230,10 +8224,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -8253,10 +8247,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -8276,10 +8270,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -8299,10 +8293,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -8322,10 +8316,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -8345,10 +8339,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -8368,10 +8362,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -8391,10 +8385,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -8414,10 +8408,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -8437,10 +8431,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -9121,91 +9115,91 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>134</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="N1" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="O1" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="P1" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q1" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="M1" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="P1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="W1" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="Z1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="AA1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="X1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
@@ -9273,7 +9267,7 @@
         <v>13.599999999999994</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W2" s="22">
         <v>0.20867383512542267</v>
@@ -9362,7 +9356,7 @@
         <v>11.899999999999995</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W3" s="22">
         <v>0.22000000000019782</v>
@@ -9451,7 +9445,7 @@
         <v>66.100000000000009</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W4" s="22">
         <v>0.66333333333309008</v>
@@ -10074,7 +10068,7 @@
         <v>125.4</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W11" s="22">
         <v>0.99032258064503076</v>
@@ -10163,7 +10157,7 @@
         <v>78.2</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W12" s="22">
         <v>0.50000000000009537</v>
@@ -10254,7 +10248,7 @@
         <v>180</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="W13" s="22">
         <v>3.1046953405016224</v>
@@ -10343,7 +10337,7 @@
         <v>460.00000000000006</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W14" s="22">
         <v>2.723333333333263</v>
@@ -10434,7 +10428,7 @@
         <v>457</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="W15" s="22">
         <v>3.7199999999998568</v>
@@ -10523,7 +10517,7 @@
         <v>457.5</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="W16" s="22">
         <v>1.25161290322564</v>
@@ -11682,7 +11676,7 @@
         <v>924</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W29" s="22">
         <v>17.812903225806423</v>
@@ -11771,7 +11765,7 @@
         <v>400</v>
       </c>
       <c r="V30" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W30" s="22">
         <v>1.4549999999997472</v>
@@ -11860,7 +11854,7 @@
         <v>877</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="W31" s="22">
         <v>27.430000000000138</v>
@@ -12305,7 +12299,7 @@
         <v>187.99999999999997</v>
       </c>
       <c r="V36" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W36" s="22">
         <v>1.1333333333335343</v>
@@ -12394,7 +12388,7 @@
         <v>171.00000000000009</v>
       </c>
       <c r="V37" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W37" s="22">
         <v>1.0933333333336275</v>
@@ -12483,7 +12477,7 @@
         <v>314.99999999999994</v>
       </c>
       <c r="V38" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W38" s="22">
         <v>1.4544444444442524</v>
@@ -12572,7 +12566,7 @@
         <v>913.99999999999989</v>
       </c>
       <c r="V39" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="W39" s="22">
         <v>6.2937499999997648</v>
@@ -12661,7 +12655,7 @@
         <v>671.99999999999989</v>
       </c>
       <c r="V40" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="W40" s="22">
         <v>2.1166666666663523</v>
@@ -12750,7 +12744,7 @@
         <v>862.33</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="W41" s="22">
         <v>2.4999999999999369</v>
@@ -12928,7 +12922,7 @@
         <v>169.00000000000003</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W43" s="22">
         <v>0.56333333333308622</v>
@@ -13017,7 +13011,7 @@
         <v>445.00000000000011</v>
       </c>
       <c r="V44" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W44" s="22">
         <v>1.2199999999997619</v>
@@ -13043,10 +13037,10 @@
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C45" s="13">
         <v>45084</v>
@@ -13106,7 +13100,7 @@
         <v>632.99999999999989</v>
       </c>
       <c r="V45" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W45" s="22">
         <v>1.2000000000000455</v>
@@ -13132,10 +13126,10 @@
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C46" s="13">
         <v>45084</v>
@@ -13195,7 +13189,7 @@
         <v>603.99999999999989</v>
       </c>
       <c r="V46" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W46" s="22">
         <v>0.79666666666658636</v>
@@ -13221,10 +13215,10 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="C47" s="13">
         <v>45084</v>
@@ -13284,7 +13278,7 @@
         <v>309.00000000000006</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W47" s="22">
         <v>0.81333333333333258</v>
@@ -13310,10 +13304,10 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="13">
         <v>45084</v>
@@ -13373,7 +13367,7 @@
         <v>1748</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W48" s="22">
         <v>4.956666666666365</v>
@@ -13399,10 +13393,10 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C49" s="13">
         <v>45084</v>
@@ -13488,10 +13482,10 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C50" s="13">
         <v>45084</v>
@@ -13551,7 +13545,7 @@
         <v>1755.9999999999998</v>
       </c>
       <c r="V50" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W50" s="22">
         <v>9.8999999999999009</v>
@@ -13577,10 +13571,10 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" s="13">
         <v>45085</v>
@@ -13640,7 +13634,7 @@
         <v>781</v>
       </c>
       <c r="V51" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W51" s="22">
         <v>1.9193548387096737</v>
@@ -13666,10 +13660,10 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="13">
         <v>45085</v>
@@ -13729,7 +13723,7 @@
         <v>756.99999999999989</v>
       </c>
       <c r="V52" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W52" s="22">
         <v>1.8777777777777436</v>
@@ -13755,10 +13749,10 @@
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C53" s="13">
         <v>45085</v>
@@ -13818,7 +13812,7 @@
         <v>874</v>
       </c>
       <c r="V53" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="W53" s="22">
         <v>3.9393939393938018</v>
@@ -13844,10 +13838,10 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C54" s="13">
         <v>45085</v>
@@ -13907,7 +13901,7 @@
         <v>1754.67</v>
       </c>
       <c r="V54" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W54" s="22">
         <v>14.73666666666702</v>
@@ -13933,10 +13927,10 @@
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C55" s="13">
         <v>45085</v>
@@ -13996,7 +13990,7 @@
         <v>1766</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="W55" s="22">
         <v>4.1111111111110032</v>
@@ -14022,10 +14016,10 @@
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C56" s="13">
         <v>45085</v>
@@ -14111,10 +14105,10 @@
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C57" s="13">
         <v>45085</v>
@@ -14200,10 +14194,10 @@
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C58" s="13">
         <v>45098</v>
@@ -14263,7 +14257,7 @@
         <v>902.99999999999989</v>
       </c>
       <c r="V58" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W58" s="22">
         <v>2.23111111111128</v>
@@ -14289,10 +14283,10 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C59" s="13">
         <v>45098</v>
@@ -14353,7 +14347,7 @@
         <v>718.33</v>
       </c>
       <c r="V59" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W59" s="22">
         <v>1.832258064516443</v>
@@ -14379,10 +14373,10 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C60" s="13">
         <v>45098</v>
@@ -14442,7 +14436,7 @@
         <v>650</v>
       </c>
       <c r="V60" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="W60" s="22">
         <v>1.5031249999997165</v>
@@ -14468,10 +14462,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C61" s="13">
         <v>45098</v>
@@ -14531,7 +14525,7 @@
         <v>413.99999999999994</v>
       </c>
       <c r="V61" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W61" s="22">
         <v>0.97509632616516206</v>
@@ -14557,10 +14551,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C62" s="13">
         <v>45098</v>
@@ -14621,7 +14615,7 @@
         <v>367.99999999999994</v>
       </c>
       <c r="V62" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W62" s="22">
         <v>0.93333333333352664</v>
@@ -14647,10 +14641,10 @@
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C63" s="13">
         <v>45098</v>
@@ -14736,10 +14730,10 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C64" s="13">
         <v>45306</v>
@@ -14797,7 +14791,7 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="W64" s="22">
         <v>2.51612903225816</v>
@@ -14823,10 +14817,10 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C65" s="13">
         <v>45306</v>
@@ -14884,7 +14878,7 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="W65" s="22">
         <v>19.096774193548345</v>
@@ -14910,10 +14904,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C66" s="13">
         <v>45306</v>
@@ -14997,10 +14991,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C67" s="13">
         <v>45307</v>
@@ -15058,7 +15052,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="W67" s="22">
         <v>0.55000000000025773</v>
@@ -15084,10 +15078,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C68" s="13">
         <v>45307</v>
@@ -15147,7 +15141,7 @@
         <v>436</v>
       </c>
       <c r="V68" s="23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="W68" s="22">
         <v>0.52459999999999996</v>
@@ -15173,10 +15167,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C69" s="13">
         <v>45307</v>
@@ -15236,7 +15230,7 @@
         <v>495</v>
       </c>
       <c r="V69" s="23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="W69" s="22">
         <v>0.50000000000009537</v>
@@ -15262,10 +15256,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C70" s="13">
         <v>45307</v>
@@ -15323,7 +15317,7 @@
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="W70" s="22">
         <v>0.67096774193575381</v>
@@ -15349,10 +15343,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C71" s="13">
         <v>45307</v>
@@ -15410,7 +15404,7 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="W71" s="22">
         <v>0.643750000000054</v>
@@ -15436,10 +15430,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C72" s="13">
         <v>45307</v>
@@ -15497,7 +15491,7 @@
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W72" s="22">
         <v>110.50000000000011</v>
@@ -15523,10 +15517,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C73" s="13">
         <v>45307</v>
@@ -15584,7 +15578,7 @@
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="W73" s="22">
         <v>0.64193548387096155</v>
@@ -15610,10 +15604,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C74" s="13">
         <v>45307</v>
@@ -15671,7 +15665,7 @@
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="23" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="W74" s="22">
         <v>79.343333333333277</v>
@@ -15697,10 +15691,10 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C75" s="13">
         <v>45307</v>
@@ -15760,7 +15754,7 @@
         <v>5439.9999999999991</v>
       </c>
       <c r="V75" s="23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="W75" s="22">
         <v>216.45199134199115</v>
@@ -15786,10 +15780,10 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C76" s="13">
         <v>45307</v>
@@ -15847,7 +15841,7 @@
         <v>1016</v>
       </c>
       <c r="V76" s="23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="W76" s="22">
         <v>0.60303030303029714</v>
@@ -15873,10 +15867,10 @@
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C77" s="13">
         <v>45307</v>
@@ -15936,7 +15930,7 @@
         <v>2375</v>
       </c>
       <c r="V77" s="23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="W77" s="22">
         <v>48.758620689655217</v>
@@ -15962,10 +15956,10 @@
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C78" s="13">
         <v>45307</v>
@@ -16025,7 +16019,7 @@
         <v>685</v>
       </c>
       <c r="V78" s="23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="W78" s="22">
         <v>136.87692307692299</v>
@@ -16051,10 +16045,10 @@
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C79" s="13">
         <v>45313</v>
@@ -16114,7 +16108,7 @@
         <v>296.00000000000006</v>
       </c>
       <c r="V79" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="W79" s="22">
         <v>1.1862068965516548</v>
@@ -16140,10 +16134,10 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C80" s="13">
         <v>45313</v>
@@ -16203,7 +16197,7 @@
         <v>260.00000000000006</v>
       </c>
       <c r="V80" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="W80" s="22">
         <v>1.2645161290320615</v>
@@ -16229,10 +16223,10 @@
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C81" s="13">
         <v>45313</v>
@@ -16292,7 +16286,7 @@
         <v>2103.3333333333335</v>
       </c>
       <c r="V81" s="23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="W81" s="22">
         <v>4.5483870967743663</v>
@@ -16318,10 +16312,10 @@
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C82" s="13">
         <v>45314</v>
@@ -16381,7 +16375,7 @@
         <v>236.00000000000003</v>
       </c>
       <c r="V82" s="23" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="W82" s="22">
         <v>0.70909090909097905</v>
@@ -16407,10 +16401,10 @@
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C83" s="13">
         <v>45314</v>
@@ -16470,7 +16464,7 @@
         <v>294.00000000000006</v>
       </c>
       <c r="V83" s="23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="W83" s="22">
         <v>0.71999999999997988</v>
@@ -16496,10 +16490,10 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C84" s="13">
         <v>45314</v>
@@ -16559,7 +16553,7 @@
         <v>4746.666666666667</v>
       </c>
       <c r="V84" s="23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="W84" s="22">
         <v>37.889841269841206</v>
@@ -16585,10 +16579,10 @@
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C85" s="13">
         <v>45320</v>
@@ -16648,7 +16642,7 @@
         <v>108.99999999999999</v>
       </c>
       <c r="V85" s="23" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="W85" s="22">
         <v>0.87419354838700769</v>
@@ -16674,10 +16668,10 @@
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C86" s="13">
         <v>45320</v>
@@ -16737,7 +16731,7 @@
         <v>795.00000000000034</v>
       </c>
       <c r="V86" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="W86" s="22">
         <v>10.465624999999923</v>
@@ -16763,10 +16757,10 @@
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C87" s="13">
         <v>45320</v>
@@ -16797,10 +16791,10 @@
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C88" s="13">
         <v>45320</v>
@@ -16860,7 +16854,7 @@
         <v>83</v>
       </c>
       <c r="V88" s="23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="W88" s="22">
         <v>0.6062500000001414</v>
@@ -16886,10 +16880,10 @@
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C89" s="13">
         <v>45320</v>
@@ -16949,7 +16943,7 @@
         <v>2429.9999999999995</v>
       </c>
       <c r="V89" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="W89" s="22">
         <v>110.45000000000016</v>
@@ -16975,10 +16969,10 @@
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C90" s="13">
         <v>45320</v>
@@ -17009,10 +17003,10 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C91" s="13">
         <v>45321</v>
@@ -17072,7 +17066,7 @@
         <v>340.00000000000006</v>
       </c>
       <c r="V91" s="23" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="W91" s="22">
         <v>0.75937499999989555</v>
@@ -17098,10 +17092,10 @@
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C92" s="13">
         <v>45321</v>
@@ -17161,7 +17155,7 @@
         <v>255.99999999999994</v>
       </c>
       <c r="V92" s="23" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="W92" s="22">
         <v>0.75333333333347241</v>
@@ -17187,10 +17181,10 @@
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C93" s="13">
         <v>45321</v>
@@ -17250,7 +17244,7 @@
         <v>3620</v>
       </c>
       <c r="V93" s="23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="W93" s="22">
         <v>27.085714285714094</v>
@@ -17276,10 +17270,10 @@
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C94" s="13">
         <v>45321</v>
@@ -17339,7 +17333,7 @@
         <v>671</v>
       </c>
       <c r="V94" s="23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="W94" s="22">
         <v>2.4827586206895043</v>
@@ -17365,10 +17359,10 @@
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C95" s="13">
         <v>45321</v>
@@ -17428,7 +17422,7 @@
         <v>597</v>
       </c>
       <c r="V95" s="23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="W95" s="22">
         <v>1.0322580645162445</v>
@@ -17454,10 +17448,10 @@
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C96" s="13">
         <v>45321</v>
@@ -17517,7 +17511,7 @@
         <v>6336.666666666667</v>
       </c>
       <c r="V96" s="23" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="W96" s="22">
         <v>13.079063146997981</v>
@@ -17543,10 +17537,10 @@
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C97" s="13">
         <v>45321</v>
@@ -17606,7 +17600,7 @@
         <v>417</v>
       </c>
       <c r="V97" s="23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="W97" s="22">
         <v>1.403333333333497</v>
@@ -17632,10 +17626,10 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C98" s="13">
         <v>45321</v>
@@ -17695,7 +17689,7 @@
         <v>238.99999999999997</v>
       </c>
       <c r="V98" s="23" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="W98" s="22">
         <v>1.0333333333332935</v>
@@ -17721,10 +17715,10 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C99" s="13">
         <v>45321</v>
@@ -17810,10 +17804,10 @@
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C100" s="13">
         <v>45327</v>
@@ -17873,7 +17867,7 @@
         <v>2530</v>
       </c>
       <c r="V100" s="23" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="W100" s="22">
         <v>42.168965517241475</v>
@@ -17899,10 +17893,10 @@
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C101" s="13">
         <v>45327</v>
@@ -17960,7 +17954,7 @@
         <v>7460</v>
       </c>
       <c r="V101" s="23" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="W101" s="22">
         <v>29.444444444444507</v>
@@ -17986,10 +17980,10 @@
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C102" s="13">
         <v>45327</v>
@@ -18020,10 +18014,10 @@
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C103" s="13">
         <v>45328</v>
@@ -18083,7 +18077,7 @@
         <v>1325</v>
       </c>
       <c r="V103" s="23" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="W103" s="22">
         <v>7.5764705882354004</v>
@@ -18109,10 +18103,10 @@
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C104" s="13">
         <v>45328</v>
@@ -18172,7 +18166,7 @@
         <v>960.00000000000034</v>
       </c>
       <c r="V104" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W104" s="22">
         <v>1.0531250000000991</v>
@@ -18198,10 +18192,10 @@
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C105" s="13">
         <v>45328</v>
@@ -18261,7 +18255,7 @@
         <v>5140.0000000000009</v>
       </c>
       <c r="V105" s="23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="W105" s="22">
         <v>138.51052631578958</v>
@@ -18287,10 +18281,10 @@
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C106" s="13">
         <v>45328</v>
@@ -18350,7 +18344,7 @@
         <v>2189.9999999999995</v>
       </c>
       <c r="V106" s="23" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="W106" s="22">
         <v>36.022727272727131</v>
@@ -18376,10 +18370,10 @@
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C107" s="13">
         <v>45328</v>
@@ -18439,7 +18433,7 @@
         <v>7280</v>
       </c>
       <c r="V107" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="W107" s="22">
         <v>126.63333333333307</v>
@@ -18465,10 +18459,10 @@
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C108" s="13">
         <v>45328</v>
@@ -18499,10 +18493,10 @@
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C109" s="13">
         <v>45334</v>
@@ -18562,7 +18556,7 @@
         <v>95.499999999999957</v>
       </c>
       <c r="V109" s="23" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="W109" s="22">
         <v>0.59687500000005222</v>
@@ -18588,10 +18582,10 @@
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C110" s="13">
         <v>45334</v>
@@ -18651,7 +18645,7 @@
         <v>64.5</v>
       </c>
       <c r="V110" s="23" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="W110" s="22">
         <v>0.53225806451614921</v>
@@ -18677,10 +18671,10 @@
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C111" s="13">
         <v>45334</v>
@@ -18740,7 +18734,7 @@
         <v>1359.9999999999998</v>
       </c>
       <c r="V111" s="23" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="W111" s="22">
         <v>25.639999999999926</v>
@@ -18766,10 +18760,10 @@
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C112" s="13">
         <v>45334</v>
@@ -18829,7 +18823,7 @@
         <v>139</v>
       </c>
       <c r="V112" s="23" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="W112" s="22">
         <v>1.0555555555554639</v>
@@ -18855,10 +18849,10 @@
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C113" s="13">
         <v>45334</v>
@@ -18918,7 +18912,7 @@
         <v>147.5</v>
       </c>
       <c r="V113" s="23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="W113" s="22">
         <v>0.95000000000000639</v>
@@ -18944,10 +18938,10 @@
     </row>
     <row r="114" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C114" s="13">
         <v>45334</v>
@@ -19007,7 +19001,7 @@
         <v>124.00000000000001</v>
       </c>
       <c r="V114" s="23" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="W114" s="22">
         <v>0.82999999999984198</v>
@@ -19033,10 +19027,10 @@
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C115" s="13">
         <v>45335</v>
@@ -19096,7 +19090,7 @@
         <v>2770</v>
       </c>
       <c r="V115" s="23" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="W115" s="22">
         <v>8.7866666666665569</v>
@@ -19122,10 +19116,10 @@
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C116" s="13">
         <v>45335</v>
@@ -19185,7 +19179,7 @@
         <v>2929.9999999999995</v>
       </c>
       <c r="V116" s="23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="W116" s="22">
         <v>6.4066666666666565</v>
@@ -19211,10 +19205,10 @@
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C117" s="13">
         <v>45335</v>
@@ -19274,7 +19268,7 @@
         <v>2719.9999999999995</v>
       </c>
       <c r="V117" s="23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="W117" s="22">
         <v>14.151808278867122</v>
@@ -19300,10 +19294,10 @@
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C118" s="13">
         <v>45335</v>
@@ -19389,10 +19383,10 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C119" s="13">
         <v>45335</v>
@@ -19452,7 +19446,7 @@
         <v>305.99999999999994</v>
       </c>
       <c r="V119" s="23" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="W119" s="22">
         <v>2.8219999999999619</v>
@@ -19478,10 +19472,10 @@
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C120" s="13">
         <v>45335</v>
@@ -19541,7 +19535,7 @@
         <v>1980.0000000000005</v>
       </c>
       <c r="V120" s="23" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="W120" s="22">
         <v>95.649999999999835</v>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050F1F03-3E5E-47F4-9D7B-1109B8272685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3B4D21-6D20-4424-9357-BF2913D3CFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="320">
   <si>
     <t>pH</t>
   </si>
@@ -695,9 +695,6 @@
     <t>18-KK-13022024</t>
   </si>
   <si>
-    <t>19-KK13022024</t>
-  </si>
-  <si>
     <t>11a</t>
   </si>
   <si>
@@ -854,12 +851,6 @@
     <t>Plastic and feminine products</t>
   </si>
   <si>
-    <t>18-KK130202024</t>
-  </si>
-  <si>
-    <t>19-K-13022024</t>
-  </si>
-  <si>
     <t>228</t>
   </si>
   <si>
@@ -1005,6 +996,9 @@
   </si>
   <si>
     <t>13937</t>
+  </si>
+  <si>
+    <t>19-KK-13022024</t>
   </si>
 </sst>
 </file>
@@ -3993,13 +3987,13 @@
         <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>138</v>
@@ -4033,7 +4027,7 @@
         <v>59</v>
       </c>
       <c r="P24" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q24" t="s">
         <v>60</v>
@@ -4051,10 +4045,10 @@
         <v>54</v>
       </c>
       <c r="W24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X24" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Y24" s="12">
         <v>1</v>
@@ -4093,7 +4087,7 @@
         <v>59</v>
       </c>
       <c r="AM24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.35">
@@ -4101,13 +4095,13 @@
         <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -4143,7 +4137,7 @@
         <v>59</v>
       </c>
       <c r="P25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q25" t="s">
         <v>60</v>
@@ -4161,10 +4155,10 @@
         <v>54</v>
       </c>
       <c r="W25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X25" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y25" s="12">
         <v>1</v>
@@ -4206,7 +4200,7 @@
         <v>59</v>
       </c>
       <c r="AM25" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.35">
@@ -4214,13 +4208,13 @@
         <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -4256,7 +4250,7 @@
         <v>59</v>
       </c>
       <c r="P26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q26" t="s">
         <v>60</v>
@@ -4274,7 +4268,7 @@
         <v>54</v>
       </c>
       <c r="W26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X26" t="s">
         <v>91</v>
@@ -4319,7 +4313,7 @@
         <v>59</v>
       </c>
       <c r="AM26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.35">
@@ -4327,13 +4321,13 @@
         <v>203</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -4369,7 +4363,7 @@
         <v>59</v>
       </c>
       <c r="P27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q27" t="s">
         <v>60</v>
@@ -4387,7 +4381,7 @@
         <v>54</v>
       </c>
       <c r="W27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X27" t="s">
         <v>91</v>
@@ -4432,7 +4426,7 @@
         <v>59</v>
       </c>
       <c r="AM27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.35">
@@ -4440,13 +4434,13 @@
         <v>204</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -4482,7 +4476,7 @@
         <v>59</v>
       </c>
       <c r="P28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q28" t="s">
         <v>60</v>
@@ -4500,7 +4494,7 @@
         <v>54</v>
       </c>
       <c r="W28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X28" t="s">
         <v>91</v>
@@ -4545,7 +4539,7 @@
         <v>59</v>
       </c>
       <c r="AM28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.35">
@@ -4553,13 +4547,13 @@
         <v>205</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -4595,7 +4589,7 @@
         <v>59</v>
       </c>
       <c r="P29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q29" t="s">
         <v>60</v>
@@ -4613,10 +4607,10 @@
         <v>54</v>
       </c>
       <c r="W29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y29" s="12">
         <v>1</v>
@@ -4663,13 +4657,13 @@
         <v>206</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
@@ -4705,7 +4699,7 @@
         <v>59</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q30" t="s">
         <v>60</v>
@@ -4723,10 +4717,10 @@
         <v>59</v>
       </c>
       <c r="W30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y30" s="12">
         <v>1</v>
@@ -4750,13 +4744,13 @@
         <v>1</v>
       </c>
       <c r="AF30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s">
         <v>65</v>
       </c>
       <c r="AI30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AK30" t="s">
         <v>54</v>
@@ -4765,7 +4759,7 @@
         <v>59</v>
       </c>
       <c r="AM30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.35">
@@ -4773,13 +4767,13 @@
         <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -4815,7 +4809,7 @@
         <v>59</v>
       </c>
       <c r="P31" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q31" t="s">
         <v>60</v>
@@ -4857,13 +4851,13 @@
         <v>1</v>
       </c>
       <c r="AF31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s">
         <v>75</v>
       </c>
       <c r="AI31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AK31" t="s">
         <v>54</v>
@@ -4872,7 +4866,7 @@
         <v>59</v>
       </c>
       <c r="AM31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.35">
@@ -4880,13 +4874,13 @@
         <v>208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>138</v>
@@ -4905,10 +4899,10 @@
         <v>56</v>
       </c>
       <c r="K32" t="s">
+        <v>244</v>
+      </c>
+      <c r="L32" t="s">
         <v>245</v>
-      </c>
-      <c r="L32" t="s">
-        <v>246</v>
       </c>
       <c r="M32" t="s">
         <v>54</v>
@@ -4920,7 +4914,7 @@
         <v>59</v>
       </c>
       <c r="P32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q32" t="s">
         <v>60</v>
@@ -4938,7 +4932,7 @@
         <v>54</v>
       </c>
       <c r="W32" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X32" t="s">
         <v>70</v>
@@ -4980,7 +4974,7 @@
         <v>59</v>
       </c>
       <c r="AM32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.35">
@@ -4988,13 +4982,13 @@
         <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
@@ -5030,7 +5024,7 @@
         <v>59</v>
       </c>
       <c r="P33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q33" t="s">
         <v>60</v>
@@ -5048,10 +5042,10 @@
         <v>54</v>
       </c>
       <c r="W33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Y33" s="12">
         <v>0</v>
@@ -5101,13 +5095,13 @@
         <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -5143,7 +5137,7 @@
         <v>59</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q34" t="s">
         <v>60</v>
@@ -5161,7 +5155,7 @@
         <v>54</v>
       </c>
       <c r="W34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X34" t="s">
         <v>78</v>
@@ -5206,7 +5200,7 @@
         <v>59</v>
       </c>
       <c r="AM34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.35">
@@ -5214,13 +5208,13 @@
         <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>138</v>
@@ -5269,10 +5263,10 @@
         <v>54</v>
       </c>
       <c r="W35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y35" s="12">
         <v>1</v>
@@ -5314,7 +5308,7 @@
         <v>59</v>
       </c>
       <c r="AM35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.35">
@@ -5322,13 +5316,13 @@
         <v>212</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -5364,10 +5358,10 @@
         <v>59</v>
       </c>
       <c r="P36" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q36" t="s">
         <v>247</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>248</v>
       </c>
       <c r="R36" t="s">
         <v>72</v>
@@ -5382,7 +5376,7 @@
         <v>54</v>
       </c>
       <c r="W36" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X36" t="s">
         <v>78</v>
@@ -5427,7 +5421,7 @@
         <v>59</v>
       </c>
       <c r="AM36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.35">
@@ -5435,13 +5429,13 @@
         <v>213</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -5477,7 +5471,7 @@
         <v>59</v>
       </c>
       <c r="P37" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q37" t="s">
         <v>60</v>
@@ -5495,7 +5489,7 @@
         <v>59</v>
       </c>
       <c r="W37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X37" t="s">
         <v>63</v>
@@ -5545,13 +5539,13 @@
         <v>214</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -5587,10 +5581,10 @@
         <v>59</v>
       </c>
       <c r="P38" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q38" t="s">
         <v>247</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>248</v>
       </c>
       <c r="R38" t="s">
         <v>72</v>
@@ -5605,7 +5599,7 @@
         <v>54</v>
       </c>
       <c r="W38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X38" t="s">
         <v>70</v>
@@ -5647,7 +5641,7 @@
         <v>59</v>
       </c>
       <c r="AM38" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.35">
@@ -5655,13 +5649,13 @@
         <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>138</v>
@@ -5695,7 +5689,7 @@
         <v>59</v>
       </c>
       <c r="P39" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q39" t="s">
         <v>60</v>
@@ -5713,7 +5707,7 @@
         <v>54</v>
       </c>
       <c r="W39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X39" t="s">
         <v>70</v>
@@ -5758,7 +5752,7 @@
         <v>59</v>
       </c>
       <c r="AM39" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.35">
@@ -5766,13 +5760,13 @@
         <v>216</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -5808,7 +5802,7 @@
         <v>54</v>
       </c>
       <c r="Q40" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R40" t="s">
         <v>72</v>
@@ -5823,7 +5817,7 @@
         <v>59</v>
       </c>
       <c r="W40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X40" t="s">
         <v>78</v>
@@ -5868,7 +5862,7 @@
         <v>59</v>
       </c>
       <c r="AM40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.35">
@@ -5876,13 +5870,13 @@
         <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>138</v>
@@ -5916,10 +5910,10 @@
         <v>59</v>
       </c>
       <c r="P41" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q41" t="s">
         <v>247</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>248</v>
       </c>
       <c r="R41" t="s">
         <v>72</v>
@@ -5934,7 +5928,7 @@
         <v>59</v>
       </c>
       <c r="W41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X41" t="s">
         <v>78</v>
@@ -5979,21 +5973,21 @@
         <v>59</v>
       </c>
       <c r="AM41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>218</v>
+        <v>319</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -6029,10 +6023,10 @@
         <v>59</v>
       </c>
       <c r="P42" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q42" t="s">
         <v>247</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>248</v>
       </c>
       <c r="R42" t="s">
         <v>72</v>
@@ -6089,7 +6083,7 @@
         <v>59</v>
       </c>
       <c r="AM42" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -6858,7 +6852,7 @@
         <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -6890,7 +6884,7 @@
         <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -6922,7 +6916,7 @@
         <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -6954,7 +6948,7 @@
         <v>203</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -6986,7 +6980,7 @@
         <v>204</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -7018,7 +7012,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -7050,7 +7044,7 @@
         <v>206</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -7082,7 +7076,7 @@
         <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -7114,7 +7108,7 @@
         <v>208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -7146,7 +7140,7 @@
         <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -7178,7 +7172,7 @@
         <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -7210,7 +7204,7 @@
         <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -7242,7 +7236,7 @@
         <v>212</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -7274,7 +7268,7 @@
         <v>213</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -7306,7 +7300,7 @@
         <v>214</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -7338,7 +7332,7 @@
         <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -7370,7 +7364,7 @@
         <v>216</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -7402,7 +7396,7 @@
         <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -7431,10 +7425,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>218</v>
+        <v>319</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -8020,7 +8014,7 @@
         <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -8043,7 +8037,7 @@
         <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -8066,7 +8060,7 @@
         <v>202</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -8089,7 +8083,7 @@
         <v>203</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -8112,7 +8106,7 @@
         <v>204</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -8135,7 +8129,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -8158,7 +8152,7 @@
         <v>206</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -8181,7 +8175,7 @@
         <v>207</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -8204,7 +8198,7 @@
         <v>208</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -8227,7 +8221,7 @@
         <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -8250,7 +8244,7 @@
         <v>210</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -8273,7 +8267,7 @@
         <v>211</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -8296,7 +8290,7 @@
         <v>212</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -8319,7 +8313,7 @@
         <v>213</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -8342,7 +8336,7 @@
         <v>214</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -8365,7 +8359,7 @@
         <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -8388,7 +8382,7 @@
         <v>216</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -8411,7 +8405,7 @@
         <v>217</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -8431,10 +8425,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>218</v>
+        <v>319</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -14733,7 +14727,7 @@
         <v>200</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C64" s="13">
         <v>45306</v>
@@ -14791,7 +14785,7 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="23" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="W64" s="22">
         <v>2.51612903225816</v>
@@ -14820,7 +14814,7 @@
         <v>200</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C65" s="13">
         <v>45306</v>
@@ -14878,7 +14872,7 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="23" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="W65" s="22">
         <v>19.096774193548345</v>
@@ -14907,7 +14901,7 @@
         <v>200</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C66" s="13">
         <v>45306</v>
@@ -14994,7 +14988,7 @@
         <v>201</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C67" s="13">
         <v>45307</v>
@@ -15052,7 +15046,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="W67" s="22">
         <v>0.55000000000025773</v>
@@ -15081,7 +15075,7 @@
         <v>201</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C68" s="13">
         <v>45307</v>
@@ -15141,7 +15135,7 @@
         <v>436</v>
       </c>
       <c r="V68" s="23" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="W68" s="22">
         <v>0.52459999999999996</v>
@@ -15170,7 +15164,7 @@
         <v>201</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C69" s="13">
         <v>45307</v>
@@ -15230,7 +15224,7 @@
         <v>495</v>
       </c>
       <c r="V69" s="23" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="W69" s="22">
         <v>0.50000000000009537</v>
@@ -15259,7 +15253,7 @@
         <v>202</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C70" s="13">
         <v>45307</v>
@@ -15317,7 +15311,7 @@
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="23" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="W70" s="22">
         <v>0.67096774193575381</v>
@@ -15346,7 +15340,7 @@
         <v>202</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C71" s="13">
         <v>45307</v>
@@ -15404,7 +15398,7 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="23" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="W71" s="22">
         <v>0.643750000000054</v>
@@ -15433,7 +15427,7 @@
         <v>202</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="13">
         <v>45307</v>
@@ -15491,7 +15485,7 @@
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="23" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="W72" s="22">
         <v>110.50000000000011</v>
@@ -15520,7 +15514,7 @@
         <v>203</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C73" s="13">
         <v>45307</v>
@@ -15578,7 +15572,7 @@
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="23" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="W73" s="22">
         <v>0.64193548387096155</v>
@@ -15607,7 +15601,7 @@
         <v>203</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C74" s="13">
         <v>45307</v>
@@ -15665,7 +15659,7 @@
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="23" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="W74" s="22">
         <v>79.343333333333277</v>
@@ -15694,7 +15688,7 @@
         <v>203</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C75" s="13">
         <v>45307</v>
@@ -15754,7 +15748,7 @@
         <v>5439.9999999999991</v>
       </c>
       <c r="V75" s="23" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="W75" s="22">
         <v>216.45199134199115</v>
@@ -15783,7 +15777,7 @@
         <v>204</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C76" s="13">
         <v>45307</v>
@@ -15841,7 +15835,7 @@
         <v>1016</v>
       </c>
       <c r="V76" s="23" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="W76" s="22">
         <v>0.60303030303029714</v>
@@ -15870,7 +15864,7 @@
         <v>204</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C77" s="13">
         <v>45307</v>
@@ -15930,7 +15924,7 @@
         <v>2375</v>
       </c>
       <c r="V77" s="23" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="W77" s="22">
         <v>48.758620689655217</v>
@@ -15959,7 +15953,7 @@
         <v>204</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C78" s="13">
         <v>45307</v>
@@ -16019,7 +16013,7 @@
         <v>685</v>
       </c>
       <c r="V78" s="23" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="W78" s="22">
         <v>136.87692307692299</v>
@@ -16048,7 +16042,7 @@
         <v>205</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C79" s="13">
         <v>45313</v>
@@ -16108,7 +16102,7 @@
         <v>296.00000000000006</v>
       </c>
       <c r="V79" s="23" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="W79" s="22">
         <v>1.1862068965516548</v>
@@ -16137,7 +16131,7 @@
         <v>205</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C80" s="13">
         <v>45313</v>
@@ -16197,7 +16191,7 @@
         <v>260.00000000000006</v>
       </c>
       <c r="V80" s="23" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W80" s="22">
         <v>1.2645161290320615</v>
@@ -16226,7 +16220,7 @@
         <v>205</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C81" s="13">
         <v>45313</v>
@@ -16286,7 +16280,7 @@
         <v>2103.3333333333335</v>
       </c>
       <c r="V81" s="23" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W81" s="22">
         <v>4.5483870967743663</v>
@@ -16315,7 +16309,7 @@
         <v>206</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C82" s="13">
         <v>45314</v>
@@ -16375,7 +16369,7 @@
         <v>236.00000000000003</v>
       </c>
       <c r="V82" s="23" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="W82" s="22">
         <v>0.70909090909097905</v>
@@ -16404,7 +16398,7 @@
         <v>206</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C83" s="13">
         <v>45314</v>
@@ -16464,7 +16458,7 @@
         <v>294.00000000000006</v>
       </c>
       <c r="V83" s="23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="W83" s="22">
         <v>0.71999999999997988</v>
@@ -16493,7 +16487,7 @@
         <v>206</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C84" s="13">
         <v>45314</v>
@@ -16553,7 +16547,7 @@
         <v>4746.666666666667</v>
       </c>
       <c r="V84" s="23" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="W84" s="22">
         <v>37.889841269841206</v>
@@ -16582,7 +16576,7 @@
         <v>207</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C85" s="13">
         <v>45320</v>
@@ -16642,7 +16636,7 @@
         <v>108.99999999999999</v>
       </c>
       <c r="V85" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="W85" s="22">
         <v>0.87419354838700769</v>
@@ -16671,7 +16665,7 @@
         <v>207</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C86" s="13">
         <v>45320</v>
@@ -16731,7 +16725,7 @@
         <v>795.00000000000034</v>
       </c>
       <c r="V86" s="23" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="W86" s="22">
         <v>10.465624999999923</v>
@@ -16760,7 +16754,7 @@
         <v>207</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C87" s="13">
         <v>45320</v>
@@ -16794,7 +16788,7 @@
         <v>208</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C88" s="13">
         <v>45320</v>
@@ -16854,7 +16848,7 @@
         <v>83</v>
       </c>
       <c r="V88" s="23" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="W88" s="22">
         <v>0.6062500000001414</v>
@@ -16883,7 +16877,7 @@
         <v>208</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C89" s="13">
         <v>45320</v>
@@ -16943,7 +16937,7 @@
         <v>2429.9999999999995</v>
       </c>
       <c r="V89" s="23" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="W89" s="22">
         <v>110.45000000000016</v>
@@ -16972,7 +16966,7 @@
         <v>208</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C90" s="13">
         <v>45320</v>
@@ -17006,7 +17000,7 @@
         <v>209</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C91" s="13">
         <v>45321</v>
@@ -17066,7 +17060,7 @@
         <v>340.00000000000006</v>
       </c>
       <c r="V91" s="23" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="W91" s="22">
         <v>0.75937499999989555</v>
@@ -17095,7 +17089,7 @@
         <v>209</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C92" s="13">
         <v>45321</v>
@@ -17155,7 +17149,7 @@
         <v>255.99999999999994</v>
       </c>
       <c r="V92" s="23" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="W92" s="22">
         <v>0.75333333333347241</v>
@@ -17184,7 +17178,7 @@
         <v>209</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C93" s="13">
         <v>45321</v>
@@ -17244,7 +17238,7 @@
         <v>3620</v>
       </c>
       <c r="V93" s="23" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="W93" s="22">
         <v>27.085714285714094</v>
@@ -17273,7 +17267,7 @@
         <v>210</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C94" s="13">
         <v>45321</v>
@@ -17333,7 +17327,7 @@
         <v>671</v>
       </c>
       <c r="V94" s="23" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="W94" s="22">
         <v>2.4827586206895043</v>
@@ -17362,7 +17356,7 @@
         <v>210</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C95" s="13">
         <v>45321</v>
@@ -17422,7 +17416,7 @@
         <v>597</v>
       </c>
       <c r="V95" s="23" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="W95" s="22">
         <v>1.0322580645162445</v>
@@ -17451,7 +17445,7 @@
         <v>210</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C96" s="13">
         <v>45321</v>
@@ -17511,7 +17505,7 @@
         <v>6336.666666666667</v>
       </c>
       <c r="V96" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="W96" s="22">
         <v>13.079063146997981</v>
@@ -17540,7 +17534,7 @@
         <v>211</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C97" s="13">
         <v>45321</v>
@@ -17600,7 +17594,7 @@
         <v>417</v>
       </c>
       <c r="V97" s="23" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="W97" s="22">
         <v>1.403333333333497</v>
@@ -17629,7 +17623,7 @@
         <v>211</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C98" s="13">
         <v>45321</v>
@@ -17689,7 +17683,7 @@
         <v>238.99999999999997</v>
       </c>
       <c r="V98" s="23" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="W98" s="22">
         <v>1.0333333333332935</v>
@@ -17718,7 +17712,7 @@
         <v>211</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C99" s="13">
         <v>45321</v>
@@ -17807,7 +17801,7 @@
         <v>212</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C100" s="13">
         <v>45327</v>
@@ -17867,7 +17861,7 @@
         <v>2530</v>
       </c>
       <c r="V100" s="23" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="W100" s="22">
         <v>42.168965517241475</v>
@@ -17896,7 +17890,7 @@
         <v>212</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C101" s="13">
         <v>45327</v>
@@ -17954,7 +17948,7 @@
         <v>7460</v>
       </c>
       <c r="V101" s="23" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="W101" s="22">
         <v>29.444444444444507</v>
@@ -17983,7 +17977,7 @@
         <v>212</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C102" s="13">
         <v>45327</v>
@@ -18017,7 +18011,7 @@
         <v>213</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C103" s="13">
         <v>45328</v>
@@ -18077,7 +18071,7 @@
         <v>1325</v>
       </c>
       <c r="V103" s="23" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="W103" s="22">
         <v>7.5764705882354004</v>
@@ -18106,7 +18100,7 @@
         <v>213</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C104" s="13">
         <v>45328</v>
@@ -18195,7 +18189,7 @@
         <v>213</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C105" s="13">
         <v>45328</v>
@@ -18255,7 +18249,7 @@
         <v>5140.0000000000009</v>
       </c>
       <c r="V105" s="23" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="W105" s="22">
         <v>138.51052631578958</v>
@@ -18284,7 +18278,7 @@
         <v>214</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C106" s="13">
         <v>45328</v>
@@ -18344,7 +18338,7 @@
         <v>2189.9999999999995</v>
       </c>
       <c r="V106" s="23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="W106" s="22">
         <v>36.022727272727131</v>
@@ -18373,7 +18367,7 @@
         <v>214</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C107" s="13">
         <v>45328</v>
@@ -18433,7 +18427,7 @@
         <v>7280</v>
       </c>
       <c r="V107" s="23" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="W107" s="22">
         <v>126.63333333333307</v>
@@ -18462,7 +18456,7 @@
         <v>214</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C108" s="13">
         <v>45328</v>
@@ -18496,7 +18490,7 @@
         <v>215</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C109" s="13">
         <v>45334</v>
@@ -18556,7 +18550,7 @@
         <v>95.499999999999957</v>
       </c>
       <c r="V109" s="23" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="W109" s="22">
         <v>0.59687500000005222</v>
@@ -18585,7 +18579,7 @@
         <v>215</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C110" s="13">
         <v>45334</v>
@@ -18645,7 +18639,7 @@
         <v>64.5</v>
       </c>
       <c r="V110" s="23" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="W110" s="22">
         <v>0.53225806451614921</v>
@@ -18674,7 +18668,7 @@
         <v>215</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C111" s="13">
         <v>45334</v>
@@ -18734,7 +18728,7 @@
         <v>1359.9999999999998</v>
       </c>
       <c r="V111" s="23" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="W111" s="22">
         <v>25.639999999999926</v>
@@ -18763,7 +18757,7 @@
         <v>216</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C112" s="13">
         <v>45334</v>
@@ -18823,7 +18817,7 @@
         <v>139</v>
       </c>
       <c r="V112" s="23" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="W112" s="22">
         <v>1.0555555555554639</v>
@@ -18852,7 +18846,7 @@
         <v>216</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C113" s="13">
         <v>45334</v>
@@ -18912,7 +18906,7 @@
         <v>147.5</v>
       </c>
       <c r="V113" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="W113" s="22">
         <v>0.95000000000000639</v>
@@ -18941,7 +18935,7 @@
         <v>216</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C114" s="13">
         <v>45334</v>
@@ -19001,7 +18995,7 @@
         <v>124.00000000000001</v>
       </c>
       <c r="V114" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="W114" s="22">
         <v>0.82999999999984198</v>
@@ -19027,10 +19021,10 @@
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C115" s="13">
         <v>45335</v>
@@ -19090,7 +19084,7 @@
         <v>2770</v>
       </c>
       <c r="V115" s="23" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="W115" s="22">
         <v>8.7866666666665569</v>
@@ -19116,10 +19110,10 @@
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C116" s="13">
         <v>45335</v>
@@ -19179,7 +19173,7 @@
         <v>2929.9999999999995</v>
       </c>
       <c r="V116" s="23" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="W116" s="22">
         <v>6.4066666666666565</v>
@@ -19205,10 +19199,10 @@
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C117" s="13">
         <v>45335</v>
@@ -19268,7 +19262,7 @@
         <v>2719.9999999999995</v>
       </c>
       <c r="V117" s="23" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="W117" s="22">
         <v>14.151808278867122</v>
@@ -19294,10 +19288,10 @@
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C118" s="13">
         <v>45335</v>
@@ -19383,10 +19377,10 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C119" s="13">
         <v>45335</v>
@@ -19446,7 +19440,7 @@
         <v>305.99999999999994</v>
       </c>
       <c r="V119" s="23" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="W119" s="22">
         <v>2.8219999999999619</v>
@@ -19472,10 +19466,10 @@
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C120" s="13">
         <v>45335</v>
@@ -19535,7 +19529,7 @@
         <v>1980.0000000000005</v>
       </c>
       <c r="V120" s="23" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="W120" s="22">
         <v>95.649999999999835</v>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3B4D21-6D20-4424-9357-BF2913D3CFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D281B2C6-348B-4DF0-9783-FBBA759564C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -14744,9 +14744,7 @@
       <c r="G64" s="5">
         <v>0.29599999999999999</v>
       </c>
-      <c r="H64" s="5">
-        <v>2.93</v>
-      </c>
+      <c r="H64" s="5"/>
       <c r="I64" s="10">
         <v>-216</v>
       </c>
@@ -14831,9 +14829,7 @@
       <c r="G65" s="5">
         <v>6.2E-2</v>
       </c>
-      <c r="H65" s="5">
-        <v>2.88</v>
-      </c>
+      <c r="H65" s="5"/>
       <c r="I65" s="10">
         <v>-260</v>
       </c>
@@ -14918,9 +14914,7 @@
       <c r="G66" s="5">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="H66" s="5">
-        <v>3.9</v>
-      </c>
+      <c r="H66" s="5"/>
       <c r="I66" s="10">
         <v>-276</v>
       </c>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D281B2C6-348B-4DF0-9783-FBBA759564C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A440BE-2D82-4247-AC06-2955B25A0CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="gas" sheetId="28" r:id="rId3"/>
     <sheet name="parameters" sheetId="15" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4883,7 +4883,7 @@
         <v>240</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="F32" s="6">
         <v>35</v>
@@ -5217,7 +5217,7 @@
         <v>240</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="F35" s="6">
         <v>88</v>
@@ -5879,7 +5879,7 @@
         <v>240</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="F41" s="6">
         <v>52</v>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A440BE-2D82-4247-AC06-2955B25A0CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F71F86-8787-44E2-9F1D-6DAAC09123F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="gas" sheetId="28" r:id="rId3"/>
     <sheet name="parameters" sheetId="15" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="317">
   <si>
     <t>pH</t>
   </si>
@@ -242,9 +242,6 @@
     <t>Bleach, CLR</t>
   </si>
   <si>
-    <t>Kitchen Laundry Bathing Toilet</t>
-  </si>
-  <si>
     <t>Concrete</t>
   </si>
   <si>
@@ -797,13 +794,7 @@
     <t>Toilet Bathing Laundry</t>
   </si>
   <si>
-    <t>Kitchen Toilet Bathing Laundry</t>
-  </si>
-  <si>
     <t>Toilet Bathing Kitchen</t>
-  </si>
-  <si>
-    <t>Kitchen Bathing Laundry</t>
   </si>
   <si>
     <t>1 - 5 years old</t>
@@ -1500,121 +1491,121 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.35">
@@ -1664,7 +1655,7 @@
         <v>59</v>
       </c>
       <c r="P2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q2" t="s">
         <v>60</v>
@@ -1774,7 +1765,7 @@
         <v>59</v>
       </c>
       <c r="P3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q3" t="s">
         <v>60</v>
@@ -1881,7 +1872,7 @@
         <v>59</v>
       </c>
       <c r="P4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="s">
         <v>60</v>
@@ -1899,7 +1890,7 @@
         <v>54</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="Y4" s="12">
         <v>1</v>
@@ -1976,7 +1967,7 @@
         <v>57</v>
       </c>
       <c r="L5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M5" t="s">
         <v>54</v>
@@ -1988,7 +1979,7 @@
         <v>59</v>
       </c>
       <c r="P5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q5" t="s">
         <v>60</v>
@@ -2006,7 +1997,7 @@
         <v>54</v>
       </c>
       <c r="X5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y5" s="12">
         <v>1</v>
@@ -2083,7 +2074,7 @@
         <v>57</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M6" t="s">
         <v>54</v>
@@ -2095,13 +2086,13 @@
         <v>59</v>
       </c>
       <c r="P6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="s">
         <v>60</v>
       </c>
       <c r="R6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S6" s="12">
         <v>1</v>
@@ -2169,7 +2160,7 @@
         <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F7" s="6">
         <f>410</f>
@@ -2190,7 +2181,7 @@
         <v>57</v>
       </c>
       <c r="L7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M7" t="s">
         <v>54</v>
@@ -2202,7 +2193,7 @@
         <v>59</v>
       </c>
       <c r="P7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q7" t="s">
         <v>60</v>
@@ -2220,7 +2211,7 @@
         <v>54</v>
       </c>
       <c r="X7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y7" s="12">
         <v>1</v>
@@ -2247,7 +2238,7 @@
         <v>64</v>
       </c>
       <c r="AG7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI7" t="s">
         <v>59</v>
@@ -2297,7 +2288,7 @@
         <v>57</v>
       </c>
       <c r="L8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M8" t="s">
         <v>54</v>
@@ -2309,7 +2300,7 @@
         <v>59</v>
       </c>
       <c r="P8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q8" t="s">
         <v>60</v>
@@ -2419,7 +2410,7 @@
         <v>59</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q9" t="s">
         <v>60</v>
@@ -2461,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG9" t="s">
         <v>74</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>75</v>
       </c>
       <c r="AI9" t="s">
         <v>59</v>
@@ -2503,13 +2494,13 @@
       </c>
       <c r="I10" s="2"/>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
         <v>57</v>
       </c>
       <c r="L10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M10" t="s">
         <v>54</v>
@@ -2521,7 +2512,7 @@
         <v>59</v>
       </c>
       <c r="P10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q10" t="s">
         <v>60</v>
@@ -2566,7 +2557,7 @@
         <v>64</v>
       </c>
       <c r="AG10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI10" t="s">
         <v>59</v>
@@ -2605,13 +2596,13 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K11" t="s">
         <v>57</v>
       </c>
       <c r="L11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M11" t="s">
         <v>54</v>
@@ -2623,7 +2614,7 @@
         <v>59</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q11" t="s">
         <v>60</v>
@@ -2668,7 +2659,7 @@
         <v>64</v>
       </c>
       <c r="AG11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI11" t="s">
         <v>59</v>
@@ -2715,7 +2706,7 @@
         <v>57</v>
       </c>
       <c r="L12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M12" t="s">
         <v>54</v>
@@ -2727,13 +2718,13 @@
         <v>59</v>
       </c>
       <c r="P12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q12" t="s">
         <v>60</v>
       </c>
       <c r="R12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S12" s="12">
         <v>1</v>
@@ -2742,13 +2733,13 @@
         <v>1</v>
       </c>
       <c r="U12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V12" t="s">
+        <v>82</v>
+      </c>
+      <c r="W12" t="s">
         <v>83</v>
-      </c>
-      <c r="W12" t="s">
-        <v>84</v>
       </c>
       <c r="X12" t="s">
         <v>63</v>
@@ -2831,7 +2822,7 @@
         <v>57</v>
       </c>
       <c r="L13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M13" t="s">
         <v>54</v>
@@ -2843,7 +2834,7 @@
         <v>59</v>
       </c>
       <c r="P13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q13" t="s">
         <v>60</v>
@@ -2858,10 +2849,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
+        <v>80</v>
+      </c>
+      <c r="V13" t="s">
         <v>81</v>
-      </c>
-      <c r="V13" t="s">
-        <v>82</v>
       </c>
       <c r="X13" t="s">
         <v>63</v>
@@ -2891,7 +2882,7 @@
         <v>64</v>
       </c>
       <c r="AG13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI13" t="s">
         <v>59</v>
@@ -2920,7 +2911,7 @@
         <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F14" s="6">
         <v>10</v>
@@ -2939,7 +2930,7 @@
         <v>57</v>
       </c>
       <c r="L14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M14" t="s">
         <v>54</v>
@@ -2951,7 +2942,7 @@
         <v>59</v>
       </c>
       <c r="P14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q14" t="s">
         <v>60</v>
@@ -2969,7 +2960,7 @@
         <v>54</v>
       </c>
       <c r="X14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y14" s="12">
         <v>1</v>
@@ -3049,7 +3040,7 @@
         <v>57</v>
       </c>
       <c r="L15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M15" t="s">
         <v>54</v>
@@ -3061,7 +3052,7 @@
         <v>59</v>
       </c>
       <c r="P15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q15" t="s">
         <v>60</v>
@@ -3079,7 +3070,7 @@
         <v>54</v>
       </c>
       <c r="W15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X15" t="s">
         <v>63</v>
@@ -3138,7 +3129,7 @@
         <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F16" s="6">
         <v>10</v>
@@ -3157,7 +3148,7 @@
         <v>57</v>
       </c>
       <c r="L16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M16" t="s">
         <v>54</v>
@@ -3169,13 +3160,13 @@
         <v>59</v>
       </c>
       <c r="P16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" t="s">
         <v>60</v>
       </c>
       <c r="R16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S16" s="12">
         <v>1</v>
@@ -3187,7 +3178,7 @@
         <v>54</v>
       </c>
       <c r="X16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y16" s="12">
         <v>1</v>
@@ -3261,7 +3252,7 @@
         <v>57</v>
       </c>
       <c r="L17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M17" t="s">
         <v>54</v>
@@ -3273,7 +3264,7 @@
         <v>59</v>
       </c>
       <c r="P17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q17" t="s">
         <v>60</v>
@@ -3368,7 +3359,7 @@
         <v>57</v>
       </c>
       <c r="L18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M18" t="s">
         <v>54</v>
@@ -3380,7 +3371,7 @@
         <v>59</v>
       </c>
       <c r="P18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q18" t="s">
         <v>60</v>
@@ -3475,7 +3466,7 @@
         <v>57</v>
       </c>
       <c r="L19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M19" t="s">
         <v>54</v>
@@ -3487,7 +3478,7 @@
         <v>59</v>
       </c>
       <c r="P19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q19" t="s">
         <v>60</v>
@@ -3502,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="W19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="X19" t="s">
         <v>63</v>
@@ -3576,7 +3567,7 @@
         <v>59</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s">
         <v>56</v>
@@ -3585,7 +3576,7 @@
         <v>57</v>
       </c>
       <c r="L20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M20" t="s">
         <v>54</v>
@@ -3597,13 +3588,13 @@
         <v>59</v>
       </c>
       <c r="P20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q20" t="s">
         <v>60</v>
       </c>
       <c r="R20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S20" s="12">
         <v>0</v>
@@ -3695,7 +3686,7 @@
         <v>57</v>
       </c>
       <c r="L21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M21" t="s">
         <v>54</v>
@@ -3707,7 +3698,7 @@
         <v>59</v>
       </c>
       <c r="P21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="s">
         <v>60</v>
@@ -3784,7 +3775,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F22" s="6">
         <v>200</v>
@@ -3803,7 +3794,7 @@
         <v>57</v>
       </c>
       <c r="L22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M22" t="s">
         <v>54</v>
@@ -3815,7 +3806,7 @@
         <v>59</v>
       </c>
       <c r="P22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q22" t="s">
         <v>60</v>
@@ -3833,7 +3824,7 @@
         <v>54</v>
       </c>
       <c r="X22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y22" s="12">
         <v>1</v>
@@ -3913,7 +3904,7 @@
         <v>57</v>
       </c>
       <c r="L23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M23" t="s">
         <v>54</v>
@@ -3925,7 +3916,7 @@
         <v>59</v>
       </c>
       <c r="P23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q23" t="s">
         <v>60</v>
@@ -3943,7 +3934,7 @@
         <v>54</v>
       </c>
       <c r="X23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y23" s="12">
         <v>1</v>
@@ -3984,19 +3975,19 @@
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F24" s="6">
         <v>23</v>
@@ -4015,7 +4006,7 @@
         <v>57</v>
       </c>
       <c r="L24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M24" t="s">
         <v>54</v>
@@ -4027,13 +4018,13 @@
         <v>59</v>
       </c>
       <c r="P24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q24" t="s">
         <v>60</v>
       </c>
       <c r="R24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S24" s="12">
         <v>1</v>
@@ -4045,10 +4036,10 @@
         <v>54</v>
       </c>
       <c r="W24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Y24" s="12">
         <v>1</v>
@@ -4075,7 +4066,7 @@
         <v>64</v>
       </c>
       <c r="AG24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI24" t="s">
         <v>54</v>
@@ -4087,21 +4078,21 @@
         <v>59</v>
       </c>
       <c r="AM24" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -4116,7 +4107,7 @@
         <v>59</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s">
         <v>56</v>
@@ -4125,7 +4116,7 @@
         <v>57</v>
       </c>
       <c r="L25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M25" t="s">
         <v>54</v>
@@ -4137,13 +4128,13 @@
         <v>59</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q25" t="s">
         <v>60</v>
       </c>
       <c r="R25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S25" s="12">
         <v>1</v>
@@ -4155,10 +4146,10 @@
         <v>54</v>
       </c>
       <c r="W25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X25" t="s">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="Y25" s="12">
         <v>1</v>
@@ -4185,7 +4176,7 @@
         <v>64</v>
       </c>
       <c r="AG25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI25" t="s">
         <v>54</v>
@@ -4200,21 +4191,21 @@
         <v>59</v>
       </c>
       <c r="AM25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -4229,7 +4220,7 @@
         <v>59</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
         <v>56</v>
@@ -4238,7 +4229,7 @@
         <v>57</v>
       </c>
       <c r="L26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M26" t="s">
         <v>54</v>
@@ -4250,13 +4241,13 @@
         <v>59</v>
       </c>
       <c r="P26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q26" t="s">
         <v>60</v>
       </c>
       <c r="R26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S26" s="12">
         <v>1</v>
@@ -4268,10 +4259,10 @@
         <v>54</v>
       </c>
       <c r="W26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y26" s="12">
         <v>1</v>
@@ -4298,7 +4289,7 @@
         <v>64</v>
       </c>
       <c r="AG26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI26" t="s">
         <v>54</v>
@@ -4313,21 +4304,21 @@
         <v>59</v>
       </c>
       <c r="AM26" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -4342,7 +4333,7 @@
         <v>59</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s">
         <v>56</v>
@@ -4351,7 +4342,7 @@
         <v>57</v>
       </c>
       <c r="L27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M27" t="s">
         <v>54</v>
@@ -4363,13 +4354,13 @@
         <v>59</v>
       </c>
       <c r="P27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q27" t="s">
         <v>60</v>
       </c>
       <c r="R27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S27" s="12">
         <v>1</v>
@@ -4381,10 +4372,10 @@
         <v>54</v>
       </c>
       <c r="W27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y27" s="12">
         <v>1</v>
@@ -4411,7 +4402,7 @@
         <v>64</v>
       </c>
       <c r="AG27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="s">
         <v>54</v>
@@ -4426,21 +4417,21 @@
         <v>59</v>
       </c>
       <c r="AM27" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -4455,7 +4446,7 @@
         <v>59</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s">
         <v>56</v>
@@ -4464,7 +4455,7 @@
         <v>57</v>
       </c>
       <c r="L28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M28" t="s">
         <v>54</v>
@@ -4476,13 +4467,13 @@
         <v>59</v>
       </c>
       <c r="P28" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q28" t="s">
         <v>60</v>
       </c>
       <c r="R28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S28" s="12">
         <v>1</v>
@@ -4494,10 +4485,10 @@
         <v>54</v>
       </c>
       <c r="W28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Y28" s="12">
         <v>1</v>
@@ -4524,7 +4515,7 @@
         <v>64</v>
       </c>
       <c r="AG28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI28" t="s">
         <v>54</v>
@@ -4539,21 +4530,21 @@
         <v>59</v>
       </c>
       <c r="AM28" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -4568,7 +4559,7 @@
         <v>59</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s">
         <v>56</v>
@@ -4577,7 +4568,7 @@
         <v>57</v>
       </c>
       <c r="L29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M29" t="s">
         <v>59</v>
@@ -4589,13 +4580,13 @@
         <v>59</v>
       </c>
       <c r="P29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q29" t="s">
         <v>60</v>
       </c>
       <c r="R29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S29" s="12">
         <v>1</v>
@@ -4607,10 +4598,10 @@
         <v>54</v>
       </c>
       <c r="W29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X29" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Y29" s="12">
         <v>1</v>
@@ -4637,7 +4628,7 @@
         <v>64</v>
       </c>
       <c r="AG29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI29" t="s">
         <v>59</v>
@@ -4654,16 +4645,16 @@
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
@@ -4678,7 +4669,7 @@
         <v>59</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s">
         <v>56</v>
@@ -4687,7 +4678,7 @@
         <v>57</v>
       </c>
       <c r="L30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M30" t="s">
         <v>54</v>
@@ -4699,13 +4690,13 @@
         <v>59</v>
       </c>
       <c r="P30" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q30" t="s">
         <v>60</v>
       </c>
       <c r="R30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S30" s="12">
         <v>1</v>
@@ -4717,10 +4708,10 @@
         <v>59</v>
       </c>
       <c r="W30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X30" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Y30" s="12">
         <v>1</v>
@@ -4744,13 +4735,13 @@
         <v>1</v>
       </c>
       <c r="AF30" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s">
         <v>65</v>
       </c>
       <c r="AI30" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AK30" t="s">
         <v>54</v>
@@ -4759,21 +4750,21 @@
         <v>59</v>
       </c>
       <c r="AM30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -4788,7 +4779,7 @@
         <v>59</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J31" t="s">
         <v>56</v>
@@ -4797,7 +4788,7 @@
         <v>57</v>
       </c>
       <c r="L31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M31" t="s">
         <v>54</v>
@@ -4809,13 +4800,13 @@
         <v>59</v>
       </c>
       <c r="P31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q31" t="s">
         <v>60</v>
       </c>
       <c r="R31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S31" s="12">
         <v>1</v>
@@ -4851,13 +4842,13 @@
         <v>1</v>
       </c>
       <c r="AF31" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AG31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI31" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AK31" t="s">
         <v>54</v>
@@ -4866,21 +4857,21 @@
         <v>59</v>
       </c>
       <c r="AM31" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>12</v>
@@ -4899,10 +4890,10 @@
         <v>56</v>
       </c>
       <c r="K32" t="s">
+        <v>243</v>
+      </c>
+      <c r="L32" t="s">
         <v>244</v>
-      </c>
-      <c r="L32" t="s">
-        <v>245</v>
       </c>
       <c r="M32" t="s">
         <v>54</v>
@@ -4914,13 +4905,13 @@
         <v>59</v>
       </c>
       <c r="P32" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q32" t="s">
         <v>60</v>
       </c>
       <c r="R32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S32" s="12">
         <v>1</v>
@@ -4932,10 +4923,10 @@
         <v>54</v>
       </c>
       <c r="W32" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y32" s="12">
         <v>1</v>
@@ -4974,21 +4965,21 @@
         <v>59</v>
       </c>
       <c r="AM32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
@@ -5003,7 +4994,7 @@
         <v>59</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J33" t="s">
         <v>56</v>
@@ -5012,7 +5003,7 @@
         <v>57</v>
       </c>
       <c r="L33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M33" t="s">
         <v>54</v>
@@ -5024,13 +5015,13 @@
         <v>59</v>
       </c>
       <c r="P33" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q33" t="s">
         <v>60</v>
       </c>
       <c r="R33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S33" s="12">
         <v>1</v>
@@ -5042,10 +5033,10 @@
         <v>54</v>
       </c>
       <c r="W33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X33" t="s">
-        <v>254</v>
+        <v>63</v>
       </c>
       <c r="Y33" s="12">
         <v>0</v>
@@ -5072,7 +5063,7 @@
         <v>64</v>
       </c>
       <c r="AG33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH33">
         <v>20</v>
@@ -5092,16 +5083,16 @@
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -5116,7 +5107,7 @@
         <v>59</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J34" t="s">
         <v>56</v>
@@ -5125,7 +5116,7 @@
         <v>57</v>
       </c>
       <c r="L34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M34" t="s">
         <v>54</v>
@@ -5137,13 +5128,13 @@
         <v>59</v>
       </c>
       <c r="P34" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q34" t="s">
         <v>60</v>
       </c>
       <c r="R34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S34" s="12">
         <v>1</v>
@@ -5155,10 +5146,10 @@
         <v>54</v>
       </c>
       <c r="W34" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y34" s="12">
         <v>1</v>
@@ -5185,7 +5176,7 @@
         <v>64</v>
       </c>
       <c r="AG34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI34" t="s">
         <v>54</v>
@@ -5200,21 +5191,21 @@
         <v>59</v>
       </c>
       <c r="AM34" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>12</v>
@@ -5236,7 +5227,7 @@
         <v>57</v>
       </c>
       <c r="L35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M35" t="s">
         <v>54</v>
@@ -5251,7 +5242,7 @@
         <v>60</v>
       </c>
       <c r="R35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S35" s="12">
         <v>1</v>
@@ -5263,10 +5254,10 @@
         <v>54</v>
       </c>
       <c r="W35" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X35" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Y35" s="12">
         <v>1</v>
@@ -5308,21 +5299,21 @@
         <v>59</v>
       </c>
       <c r="AM35" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -5337,7 +5328,7 @@
         <v>59</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J36" t="s">
         <v>56</v>
@@ -5346,7 +5337,7 @@
         <v>57</v>
       </c>
       <c r="L36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M36" t="s">
         <v>54</v>
@@ -5358,13 +5349,13 @@
         <v>59</v>
       </c>
       <c r="P36" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q36" t="s">
         <v>246</v>
       </c>
-      <c r="Q36" t="s">
-        <v>247</v>
-      </c>
       <c r="R36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S36" s="12">
         <v>1</v>
@@ -5376,10 +5367,10 @@
         <v>54</v>
       </c>
       <c r="W36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y36" s="12">
         <v>1</v>
@@ -5403,7 +5394,7 @@
         <v>1</v>
       </c>
       <c r="AF36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AG36" t="s">
         <v>65</v>
@@ -5421,21 +5412,21 @@
         <v>59</v>
       </c>
       <c r="AM36" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -5450,7 +5441,7 @@
         <v>59</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J37" t="s">
         <v>56</v>
@@ -5459,7 +5450,7 @@
         <v>57</v>
       </c>
       <c r="L37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M37" t="s">
         <v>59</v>
@@ -5471,13 +5462,13 @@
         <v>59</v>
       </c>
       <c r="P37" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q37" t="s">
         <v>60</v>
       </c>
       <c r="R37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S37" s="12">
         <v>1</v>
@@ -5489,7 +5480,7 @@
         <v>59</v>
       </c>
       <c r="W37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X37" t="s">
         <v>63</v>
@@ -5536,16 +5527,16 @@
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -5560,7 +5551,7 @@
         <v>59</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J38" t="s">
         <v>56</v>
@@ -5569,7 +5560,7 @@
         <v>57</v>
       </c>
       <c r="L38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M38" t="s">
         <v>54</v>
@@ -5581,13 +5572,13 @@
         <v>59</v>
       </c>
       <c r="P38" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q38" t="s">
         <v>246</v>
       </c>
-      <c r="Q38" t="s">
-        <v>247</v>
-      </c>
       <c r="R38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S38" s="12">
         <v>1</v>
@@ -5599,10 +5590,10 @@
         <v>54</v>
       </c>
       <c r="W38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y38" s="12">
         <v>1</v>
@@ -5641,24 +5632,24 @@
         <v>59</v>
       </c>
       <c r="AM38" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" s="6">
         <v>10</v>
@@ -5677,7 +5668,7 @@
         <v>57</v>
       </c>
       <c r="L39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M39" t="s">
         <v>59</v>
@@ -5689,13 +5680,13 @@
         <v>59</v>
       </c>
       <c r="P39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q39" t="s">
         <v>60</v>
       </c>
       <c r="R39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S39" s="12">
         <v>1</v>
@@ -5707,10 +5698,10 @@
         <v>54</v>
       </c>
       <c r="W39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y39" s="12">
         <v>1</v>
@@ -5752,21 +5743,21 @@
         <v>59</v>
       </c>
       <c r="AM39" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -5781,7 +5772,7 @@
         <v>59</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s">
         <v>56</v>
@@ -5790,7 +5781,7 @@
         <v>57</v>
       </c>
       <c r="L40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M40" t="s">
         <v>54</v>
@@ -5802,10 +5793,10 @@
         <v>54</v>
       </c>
       <c r="Q40" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S40" s="12">
         <v>1</v>
@@ -5817,10 +5808,10 @@
         <v>59</v>
       </c>
       <c r="W40" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y40" s="12">
         <v>1</v>
@@ -5862,21 +5853,21 @@
         <v>59</v>
       </c>
       <c r="AM40" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
@@ -5898,7 +5889,7 @@
         <v>57</v>
       </c>
       <c r="L41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M41" t="s">
         <v>54</v>
@@ -5910,13 +5901,13 @@
         <v>59</v>
       </c>
       <c r="P41" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q41" t="s">
         <v>246</v>
       </c>
-      <c r="Q41" t="s">
-        <v>247</v>
-      </c>
       <c r="R41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S41" s="12">
         <v>1</v>
@@ -5928,10 +5919,10 @@
         <v>59</v>
       </c>
       <c r="W41" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="X41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Y41" s="12">
         <v>1</v>
@@ -5973,21 +5964,21 @@
         <v>59</v>
       </c>
       <c r="AM41" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -6002,7 +5993,7 @@
         <v>59</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s">
         <v>56</v>
@@ -6011,7 +6002,7 @@
         <v>57</v>
       </c>
       <c r="L42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M42" t="s">
         <v>54</v>
@@ -6023,13 +6014,13 @@
         <v>59</v>
       </c>
       <c r="P42" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q42" t="s">
         <v>246</v>
       </c>
-      <c r="Q42" t="s">
-        <v>247</v>
-      </c>
       <c r="R42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S42" s="12">
         <v>1</v>
@@ -6041,7 +6032,7 @@
         <v>54</v>
       </c>
       <c r="X42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Y42" s="12">
         <v>1</v>
@@ -6083,7 +6074,7 @@
         <v>59</v>
       </c>
       <c r="AM42" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -6111,34 +6102,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -6849,10 +6840,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -6881,10 +6872,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -6913,10 +6904,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -6945,10 +6936,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -6977,10 +6968,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -7009,10 +7000,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -7041,10 +7032,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -7073,10 +7064,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -7105,10 +7096,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -7137,10 +7128,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -7169,10 +7160,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -7201,10 +7192,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -7233,10 +7224,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -7265,10 +7256,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -7297,10 +7288,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -7329,10 +7320,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -7361,10 +7352,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -7393,10 +7384,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -7425,10 +7416,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -7477,25 +7468,25 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>133</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -8011,10 +8002,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -8034,10 +8025,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -8057,10 +8048,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -8080,10 +8071,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -8103,10 +8094,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -8126,10 +8117,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -8149,10 +8140,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -8172,10 +8163,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -8195,10 +8186,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -8218,10 +8209,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -8241,10 +8232,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -8264,10 +8255,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -8287,10 +8278,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -8310,10 +8301,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -8333,10 +8324,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -8356,10 +8347,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -8379,10 +8370,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -8402,10 +8393,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -8425,10 +8416,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -9109,91 +9100,91 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>133</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="L1" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="N1" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="M1" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z1" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB1" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="Z1" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
@@ -9261,7 +9252,7 @@
         <v>13.599999999999994</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W2" s="22">
         <v>0.20867383512542267</v>
@@ -9350,7 +9341,7 @@
         <v>11.899999999999995</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W3" s="22">
         <v>0.22000000000019782</v>
@@ -9439,7 +9430,7 @@
         <v>66.100000000000009</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W4" s="22">
         <v>0.66333333333309008</v>
@@ -10062,7 +10053,7 @@
         <v>125.4</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="W11" s="22">
         <v>0.99032258064503076</v>
@@ -10151,7 +10142,7 @@
         <v>78.2</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="W12" s="22">
         <v>0.50000000000009537</v>
@@ -10242,7 +10233,7 @@
         <v>180</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W13" s="22">
         <v>3.1046953405016224</v>
@@ -10331,7 +10322,7 @@
         <v>460.00000000000006</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="W14" s="22">
         <v>2.723333333333263</v>
@@ -10422,7 +10413,7 @@
         <v>457</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W15" s="22">
         <v>3.7199999999998568</v>
@@ -10511,7 +10502,7 @@
         <v>457.5</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="W16" s="22">
         <v>1.25161290322564</v>
@@ -11670,7 +11661,7 @@
         <v>924</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="W29" s="22">
         <v>17.812903225806423</v>
@@ -11759,7 +11750,7 @@
         <v>400</v>
       </c>
       <c r="V30" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W30" s="22">
         <v>1.4549999999997472</v>
@@ -11848,7 +11839,7 @@
         <v>877</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W31" s="22">
         <v>27.430000000000138</v>
@@ -12293,7 +12284,7 @@
         <v>187.99999999999997</v>
       </c>
       <c r="V36" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="W36" s="22">
         <v>1.1333333333335343</v>
@@ -12382,7 +12373,7 @@
         <v>171.00000000000009</v>
       </c>
       <c r="V37" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W37" s="22">
         <v>1.0933333333336275</v>
@@ -12471,7 +12462,7 @@
         <v>314.99999999999994</v>
       </c>
       <c r="V38" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W38" s="22">
         <v>1.4544444444442524</v>
@@ -12560,7 +12551,7 @@
         <v>913.99999999999989</v>
       </c>
       <c r="V39" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W39" s="22">
         <v>6.2937499999997648</v>
@@ -12649,7 +12640,7 @@
         <v>671.99999999999989</v>
       </c>
       <c r="V40" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="W40" s="22">
         <v>2.1166666666663523</v>
@@ -12738,7 +12729,7 @@
         <v>862.33</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="W41" s="22">
         <v>2.4999999999999369</v>
@@ -12916,7 +12907,7 @@
         <v>169.00000000000003</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="W43" s="22">
         <v>0.56333333333308622</v>
@@ -13005,7 +12996,7 @@
         <v>445.00000000000011</v>
       </c>
       <c r="V44" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W44" s="22">
         <v>1.2199999999997619</v>
@@ -13094,7 +13085,7 @@
         <v>632.99999999999989</v>
       </c>
       <c r="V45" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W45" s="22">
         <v>1.2000000000000455</v>
@@ -13183,7 +13174,7 @@
         <v>603.99999999999989</v>
       </c>
       <c r="V46" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W46" s="22">
         <v>0.79666666666658636</v>
@@ -13272,7 +13263,7 @@
         <v>309.00000000000006</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W47" s="22">
         <v>0.81333333333333258</v>
@@ -13361,7 +13352,7 @@
         <v>1748</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W48" s="22">
         <v>4.956666666666365</v>
@@ -13539,7 +13530,7 @@
         <v>1755.9999999999998</v>
       </c>
       <c r="V50" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W50" s="22">
         <v>9.8999999999999009</v>
@@ -13628,7 +13619,7 @@
         <v>781</v>
       </c>
       <c r="V51" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W51" s="22">
         <v>1.9193548387096737</v>
@@ -13717,7 +13708,7 @@
         <v>756.99999999999989</v>
       </c>
       <c r="V52" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W52" s="22">
         <v>1.8777777777777436</v>
@@ -13806,7 +13797,7 @@
         <v>874</v>
       </c>
       <c r="V53" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W53" s="22">
         <v>3.9393939393938018</v>
@@ -13895,7 +13886,7 @@
         <v>1754.67</v>
       </c>
       <c r="V54" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="W54" s="22">
         <v>14.73666666666702</v>
@@ -13984,7 +13975,7 @@
         <v>1766</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W55" s="22">
         <v>4.1111111111110032</v>
@@ -14251,7 +14242,7 @@
         <v>902.99999999999989</v>
       </c>
       <c r="V58" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W58" s="22">
         <v>2.23111111111128</v>
@@ -14341,7 +14332,7 @@
         <v>718.33</v>
       </c>
       <c r="V59" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W59" s="22">
         <v>1.832258064516443</v>
@@ -14430,7 +14421,7 @@
         <v>650</v>
       </c>
       <c r="V60" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W60" s="22">
         <v>1.5031249999997165</v>
@@ -14519,7 +14510,7 @@
         <v>413.99999999999994</v>
       </c>
       <c r="V61" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="W61" s="22">
         <v>0.97509632616516206</v>
@@ -14609,7 +14600,7 @@
         <v>367.99999999999994</v>
       </c>
       <c r="V62" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W62" s="22">
         <v>0.93333333333352664</v>
@@ -14724,10 +14715,10 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C64" s="13">
         <v>45306</v>
@@ -14783,7 +14774,7 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="23" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="W64" s="22">
         <v>2.51612903225816</v>
@@ -14809,10 +14800,10 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C65" s="13">
         <v>45306</v>
@@ -14868,7 +14859,7 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="23" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="W65" s="22">
         <v>19.096774193548345</v>
@@ -14894,10 +14885,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C66" s="13">
         <v>45306</v>
@@ -14979,10 +14970,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C67" s="13">
         <v>45307</v>
@@ -15040,7 +15031,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="23" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="W67" s="22">
         <v>0.55000000000025773</v>
@@ -15066,10 +15057,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C68" s="13">
         <v>45307</v>
@@ -15129,7 +15120,7 @@
         <v>436</v>
       </c>
       <c r="V68" s="23" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="W68" s="22">
         <v>0.52459999999999996</v>
@@ -15155,10 +15146,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C69" s="13">
         <v>45307</v>
@@ -15218,7 +15209,7 @@
         <v>495</v>
       </c>
       <c r="V69" s="23" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="W69" s="22">
         <v>0.50000000000009537</v>
@@ -15244,10 +15235,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C70" s="13">
         <v>45307</v>
@@ -15305,7 +15296,7 @@
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="W70" s="22">
         <v>0.67096774193575381</v>
@@ -15331,10 +15322,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C71" s="13">
         <v>45307</v>
@@ -15392,7 +15383,7 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="23" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="W71" s="22">
         <v>0.643750000000054</v>
@@ -15418,10 +15409,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C72" s="13">
         <v>45307</v>
@@ -15479,7 +15470,7 @@
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="23" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="W72" s="22">
         <v>110.50000000000011</v>
@@ -15505,10 +15496,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C73" s="13">
         <v>45307</v>
@@ -15566,7 +15557,7 @@
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="23" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="W73" s="22">
         <v>0.64193548387096155</v>
@@ -15592,10 +15583,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C74" s="13">
         <v>45307</v>
@@ -15653,7 +15644,7 @@
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="23" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="W74" s="22">
         <v>79.343333333333277</v>
@@ -15679,10 +15670,10 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C75" s="13">
         <v>45307</v>
@@ -15742,7 +15733,7 @@
         <v>5439.9999999999991</v>
       </c>
       <c r="V75" s="23" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="W75" s="22">
         <v>216.45199134199115</v>
@@ -15768,10 +15759,10 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C76" s="13">
         <v>45307</v>
@@ -15829,7 +15820,7 @@
         <v>1016</v>
       </c>
       <c r="V76" s="23" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="W76" s="22">
         <v>0.60303030303029714</v>
@@ -15855,10 +15846,10 @@
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C77" s="13">
         <v>45307</v>
@@ -15918,7 +15909,7 @@
         <v>2375</v>
       </c>
       <c r="V77" s="23" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="W77" s="22">
         <v>48.758620689655217</v>
@@ -15944,10 +15935,10 @@
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C78" s="13">
         <v>45307</v>
@@ -16007,7 +15998,7 @@
         <v>685</v>
       </c>
       <c r="V78" s="23" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="W78" s="22">
         <v>136.87692307692299</v>
@@ -16033,10 +16024,10 @@
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C79" s="13">
         <v>45313</v>
@@ -16096,7 +16087,7 @@
         <v>296.00000000000006</v>
       </c>
       <c r="V79" s="23" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="W79" s="22">
         <v>1.1862068965516548</v>
@@ -16122,10 +16113,10 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C80" s="13">
         <v>45313</v>
@@ -16185,7 +16176,7 @@
         <v>260.00000000000006</v>
       </c>
       <c r="V80" s="23" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="W80" s="22">
         <v>1.2645161290320615</v>
@@ -16211,10 +16202,10 @@
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C81" s="13">
         <v>45313</v>
@@ -16274,7 +16265,7 @@
         <v>2103.3333333333335</v>
       </c>
       <c r="V81" s="23" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="W81" s="22">
         <v>4.5483870967743663</v>
@@ -16300,10 +16291,10 @@
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C82" s="13">
         <v>45314</v>
@@ -16363,7 +16354,7 @@
         <v>236.00000000000003</v>
       </c>
       <c r="V82" s="23" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="W82" s="22">
         <v>0.70909090909097905</v>
@@ -16389,10 +16380,10 @@
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C83" s="13">
         <v>45314</v>
@@ -16452,7 +16443,7 @@
         <v>294.00000000000006</v>
       </c>
       <c r="V83" s="23" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W83" s="22">
         <v>0.71999999999997988</v>
@@ -16478,10 +16469,10 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="13">
         <v>45314</v>
@@ -16541,7 +16532,7 @@
         <v>4746.666666666667</v>
       </c>
       <c r="V84" s="23" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="W84" s="22">
         <v>37.889841269841206</v>
@@ -16567,10 +16558,10 @@
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C85" s="13">
         <v>45320</v>
@@ -16630,7 +16621,7 @@
         <v>108.99999999999999</v>
       </c>
       <c r="V85" s="23" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="W85" s="22">
         <v>0.87419354838700769</v>
@@ -16656,10 +16647,10 @@
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C86" s="13">
         <v>45320</v>
@@ -16719,7 +16710,7 @@
         <v>795.00000000000034</v>
       </c>
       <c r="V86" s="23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="W86" s="22">
         <v>10.465624999999923</v>
@@ -16745,10 +16736,10 @@
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C87" s="13">
         <v>45320</v>
@@ -16779,10 +16770,10 @@
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C88" s="13">
         <v>45320</v>
@@ -16842,7 +16833,7 @@
         <v>83</v>
       </c>
       <c r="V88" s="23" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="W88" s="22">
         <v>0.6062500000001414</v>
@@ -16868,10 +16859,10 @@
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C89" s="13">
         <v>45320</v>
@@ -16931,7 +16922,7 @@
         <v>2429.9999999999995</v>
       </c>
       <c r="V89" s="23" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="W89" s="22">
         <v>110.45000000000016</v>
@@ -16957,10 +16948,10 @@
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C90" s="13">
         <v>45320</v>
@@ -16991,10 +16982,10 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C91" s="13">
         <v>45321</v>
@@ -17054,7 +17045,7 @@
         <v>340.00000000000006</v>
       </c>
       <c r="V91" s="23" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="W91" s="22">
         <v>0.75937499999989555</v>
@@ -17080,10 +17071,10 @@
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C92" s="13">
         <v>45321</v>
@@ -17143,7 +17134,7 @@
         <v>255.99999999999994</v>
       </c>
       <c r="V92" s="23" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="W92" s="22">
         <v>0.75333333333347241</v>
@@ -17169,10 +17160,10 @@
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C93" s="13">
         <v>45321</v>
@@ -17232,7 +17223,7 @@
         <v>3620</v>
       </c>
       <c r="V93" s="23" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="W93" s="22">
         <v>27.085714285714094</v>
@@ -17258,10 +17249,10 @@
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C94" s="13">
         <v>45321</v>
@@ -17321,7 +17312,7 @@
         <v>671</v>
       </c>
       <c r="V94" s="23" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="W94" s="22">
         <v>2.4827586206895043</v>
@@ -17347,10 +17338,10 @@
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C95" s="13">
         <v>45321</v>
@@ -17410,7 +17401,7 @@
         <v>597</v>
       </c>
       <c r="V95" s="23" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="W95" s="22">
         <v>1.0322580645162445</v>
@@ -17436,10 +17427,10 @@
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C96" s="13">
         <v>45321</v>
@@ -17499,7 +17490,7 @@
         <v>6336.666666666667</v>
       </c>
       <c r="V96" s="23" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="W96" s="22">
         <v>13.079063146997981</v>
@@ -17525,10 +17516,10 @@
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C97" s="13">
         <v>45321</v>
@@ -17588,7 +17579,7 @@
         <v>417</v>
       </c>
       <c r="V97" s="23" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="W97" s="22">
         <v>1.403333333333497</v>
@@ -17614,10 +17605,10 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C98" s="13">
         <v>45321</v>
@@ -17677,7 +17668,7 @@
         <v>238.99999999999997</v>
       </c>
       <c r="V98" s="23" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="W98" s="22">
         <v>1.0333333333332935</v>
@@ -17703,10 +17694,10 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C99" s="13">
         <v>45321</v>
@@ -17792,10 +17783,10 @@
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C100" s="13">
         <v>45327</v>
@@ -17855,7 +17846,7 @@
         <v>2530</v>
       </c>
       <c r="V100" s="23" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="W100" s="22">
         <v>42.168965517241475</v>
@@ -17881,10 +17872,10 @@
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C101" s="13">
         <v>45327</v>
@@ -17942,7 +17933,7 @@
         <v>7460</v>
       </c>
       <c r="V101" s="23" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="W101" s="22">
         <v>29.444444444444507</v>
@@ -17968,10 +17959,10 @@
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C102" s="13">
         <v>45327</v>
@@ -18002,10 +17993,10 @@
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C103" s="13">
         <v>45328</v>
@@ -18065,7 +18056,7 @@
         <v>1325</v>
       </c>
       <c r="V103" s="23" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="W103" s="22">
         <v>7.5764705882354004</v>
@@ -18091,10 +18082,10 @@
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C104" s="13">
         <v>45328</v>
@@ -18154,7 +18145,7 @@
         <v>960.00000000000034</v>
       </c>
       <c r="V104" s="23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W104" s="22">
         <v>1.0531250000000991</v>
@@ -18180,10 +18171,10 @@
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C105" s="13">
         <v>45328</v>
@@ -18243,7 +18234,7 @@
         <v>5140.0000000000009</v>
       </c>
       <c r="V105" s="23" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="W105" s="22">
         <v>138.51052631578958</v>
@@ -18269,10 +18260,10 @@
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C106" s="13">
         <v>45328</v>
@@ -18332,7 +18323,7 @@
         <v>2189.9999999999995</v>
       </c>
       <c r="V106" s="23" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="W106" s="22">
         <v>36.022727272727131</v>
@@ -18358,10 +18349,10 @@
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C107" s="13">
         <v>45328</v>
@@ -18421,7 +18412,7 @@
         <v>7280</v>
       </c>
       <c r="V107" s="23" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="W107" s="22">
         <v>126.63333333333307</v>
@@ -18447,10 +18438,10 @@
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C108" s="13">
         <v>45328</v>
@@ -18481,10 +18472,10 @@
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C109" s="13">
         <v>45334</v>
@@ -18544,7 +18535,7 @@
         <v>95.499999999999957</v>
       </c>
       <c r="V109" s="23" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="W109" s="22">
         <v>0.59687500000005222</v>
@@ -18570,10 +18561,10 @@
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C110" s="13">
         <v>45334</v>
@@ -18633,7 +18624,7 @@
         <v>64.5</v>
       </c>
       <c r="V110" s="23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="W110" s="22">
         <v>0.53225806451614921</v>
@@ -18659,10 +18650,10 @@
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C111" s="13">
         <v>45334</v>
@@ -18722,7 +18713,7 @@
         <v>1359.9999999999998</v>
       </c>
       <c r="V111" s="23" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="W111" s="22">
         <v>25.639999999999926</v>
@@ -18748,10 +18739,10 @@
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C112" s="13">
         <v>45334</v>
@@ -18811,7 +18802,7 @@
         <v>139</v>
       </c>
       <c r="V112" s="23" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="W112" s="22">
         <v>1.0555555555554639</v>
@@ -18837,10 +18828,10 @@
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C113" s="13">
         <v>45334</v>
@@ -18900,7 +18891,7 @@
         <v>147.5</v>
       </c>
       <c r="V113" s="23" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="W113" s="22">
         <v>0.95000000000000639</v>
@@ -18926,10 +18917,10 @@
     </row>
     <row r="114" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C114" s="13">
         <v>45334</v>
@@ -18989,7 +18980,7 @@
         <v>124.00000000000001</v>
       </c>
       <c r="V114" s="23" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="W114" s="22">
         <v>0.82999999999984198</v>
@@ -19015,10 +19006,10 @@
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C115" s="13">
         <v>45335</v>
@@ -19078,7 +19069,7 @@
         <v>2770</v>
       </c>
       <c r="V115" s="23" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="W115" s="22">
         <v>8.7866666666665569</v>
@@ -19104,10 +19095,10 @@
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C116" s="13">
         <v>45335</v>
@@ -19167,7 +19158,7 @@
         <v>2929.9999999999995</v>
       </c>
       <c r="V116" s="23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="W116" s="22">
         <v>6.4066666666666565</v>
@@ -19193,10 +19184,10 @@
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C117" s="13">
         <v>45335</v>
@@ -19256,7 +19247,7 @@
         <v>2719.9999999999995</v>
       </c>
       <c r="V117" s="23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="W117" s="22">
         <v>14.151808278867122</v>
@@ -19282,10 +19273,10 @@
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C118" s="13">
         <v>45335</v>
@@ -19371,10 +19362,10 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C119" s="13">
         <v>45335</v>
@@ -19434,7 +19425,7 @@
         <v>305.99999999999994</v>
       </c>
       <c r="V119" s="23" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="W119" s="22">
         <v>2.8219999999999619</v>
@@ -19460,10 +19451,10 @@
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C120" s="13">
         <v>45335</v>
@@ -19523,7 +19514,7 @@
         <v>1980.0000000000005</v>
       </c>
       <c r="V120" s="23" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="W120" s="22">
         <v>95.649999999999835</v>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F71F86-8787-44E2-9F1D-6DAAC09123F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0D57B3-C11C-444E-A722-B41D054DB846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -6193,7 +6193,7 @@
         <v>1000</v>
       </c>
       <c r="J3" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -6353,7 +6353,7 @@
         <v>91.818181818181813</v>
       </c>
       <c r="J8" s="6">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -6641,7 +6641,7 @@
         <v>27.61904761904762</v>
       </c>
       <c r="J17" s="6">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
@@ -6673,7 +6673,7 @@
         <v>92</v>
       </c>
       <c r="J18" s="6">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0D57B3-C11C-444E-A722-B41D054DB846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B937407-3842-4B78-9545-E4C9F2D4B5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" tabRatio="661" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="661" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="316">
   <si>
     <t>pH</t>
   </si>
@@ -275,12 +275,6 @@
     <t>Toilet</t>
   </si>
   <si>
-    <t xml:space="preserve">Treatment plant </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wastewater treatment unit </t>
-  </si>
-  <si>
     <t>Bio additives / enzymes</t>
   </si>
   <si>
@@ -990,6 +984,9 @@
   </si>
   <si>
     <t>19-KK-13022024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aerated Treatment plant </t>
   </si>
 </sst>
 </file>
@@ -1491,121 +1488,121 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.35">
@@ -2160,7 +2157,7 @@
         <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F7" s="6">
         <f>410</f>
@@ -2494,7 +2491,7 @@
       </c>
       <c r="I10" s="2"/>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="K10" t="s">
         <v>57</v>
@@ -2596,7 +2593,7 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" t="s">
-        <v>79</v>
+        <v>315</v>
       </c>
       <c r="K11" t="s">
         <v>57</v>
@@ -2733,13 +2730,13 @@
         <v>1</v>
       </c>
       <c r="U12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V12" t="s">
         <v>80</v>
       </c>
-      <c r="V12" t="s">
-        <v>82</v>
-      </c>
       <c r="W12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="X12" t="s">
         <v>63</v>
@@ -2849,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="V13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="X13" t="s">
         <v>63</v>
@@ -2911,7 +2908,7 @@
         <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F14" s="6">
         <v>10</v>
@@ -2960,7 +2957,7 @@
         <v>54</v>
       </c>
       <c r="X14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Y14" s="12">
         <v>1</v>
@@ -3070,7 +3067,7 @@
         <v>54</v>
       </c>
       <c r="W15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X15" t="s">
         <v>63</v>
@@ -3129,7 +3126,7 @@
         <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F16" s="6">
         <v>10</v>
@@ -3252,7 +3249,7 @@
         <v>57</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s">
         <v>54</v>
@@ -3493,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="W19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="X19" t="s">
         <v>63</v>
@@ -3567,7 +3564,7 @@
         <v>59</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J20" t="s">
         <v>56</v>
@@ -3594,7 +3591,7 @@
         <v>60</v>
       </c>
       <c r="R20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="S20" s="12">
         <v>0</v>
@@ -3775,7 +3772,7 @@
         <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F22" s="6">
         <v>200</v>
@@ -3824,7 +3821,7 @@
         <v>54</v>
       </c>
       <c r="X22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Y22" s="12">
         <v>1</v>
@@ -3934,7 +3931,7 @@
         <v>54</v>
       </c>
       <c r="X23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Y23" s="12">
         <v>1</v>
@@ -3975,19 +3972,19 @@
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F24" s="6">
         <v>23</v>
@@ -4018,7 +4015,7 @@
         <v>59</v>
       </c>
       <c r="P24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q24" t="s">
         <v>60</v>
@@ -4036,10 +4033,10 @@
         <v>54</v>
       </c>
       <c r="W24" t="s">
+        <v>246</v>
+      </c>
+      <c r="X24" t="s">
         <v>248</v>
-      </c>
-      <c r="X24" t="s">
-        <v>250</v>
       </c>
       <c r="Y24" s="12">
         <v>1</v>
@@ -4078,21 +4075,21 @@
         <v>59</v>
       </c>
       <c r="AM24" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -4107,7 +4104,7 @@
         <v>59</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
         <v>56</v>
@@ -4128,7 +4125,7 @@
         <v>59</v>
       </c>
       <c r="P25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q25" t="s">
         <v>60</v>
@@ -4146,7 +4143,7 @@
         <v>54</v>
       </c>
       <c r="W25" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X25" t="s">
         <v>63</v>
@@ -4191,21 +4188,21 @@
         <v>59</v>
       </c>
       <c r="AM25" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -4220,7 +4217,7 @@
         <v>59</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s">
         <v>56</v>
@@ -4241,7 +4238,7 @@
         <v>59</v>
       </c>
       <c r="P26" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q26" t="s">
         <v>60</v>
@@ -4259,10 +4256,10 @@
         <v>54</v>
       </c>
       <c r="W26" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Y26" s="12">
         <v>1</v>
@@ -4304,21 +4301,21 @@
         <v>59</v>
       </c>
       <c r="AM26" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -4333,7 +4330,7 @@
         <v>59</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J27" t="s">
         <v>56</v>
@@ -4354,7 +4351,7 @@
         <v>59</v>
       </c>
       <c r="P27" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q27" t="s">
         <v>60</v>
@@ -4372,10 +4369,10 @@
         <v>54</v>
       </c>
       <c r="W27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Y27" s="12">
         <v>1</v>
@@ -4417,21 +4414,21 @@
         <v>59</v>
       </c>
       <c r="AM27" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -4446,7 +4443,7 @@
         <v>59</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s">
         <v>56</v>
@@ -4467,7 +4464,7 @@
         <v>59</v>
       </c>
       <c r="P28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q28" t="s">
         <v>60</v>
@@ -4485,10 +4482,10 @@
         <v>54</v>
       </c>
       <c r="W28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Y28" s="12">
         <v>1</v>
@@ -4530,21 +4527,21 @@
         <v>59</v>
       </c>
       <c r="AM28" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -4559,7 +4556,7 @@
         <v>59</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s">
         <v>56</v>
@@ -4580,7 +4577,7 @@
         <v>59</v>
       </c>
       <c r="P29" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q29" t="s">
         <v>60</v>
@@ -4598,10 +4595,10 @@
         <v>54</v>
       </c>
       <c r="W29" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X29" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Y29" s="12">
         <v>1</v>
@@ -4645,16 +4642,16 @@
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>12</v>
@@ -4669,7 +4666,7 @@
         <v>59</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s">
         <v>56</v>
@@ -4690,7 +4687,7 @@
         <v>59</v>
       </c>
       <c r="P30" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q30" t="s">
         <v>60</v>
@@ -4708,10 +4705,10 @@
         <v>59</v>
       </c>
       <c r="W30" t="s">
+        <v>247</v>
+      </c>
+      <c r="X30" t="s">
         <v>249</v>
-      </c>
-      <c r="X30" t="s">
-        <v>251</v>
       </c>
       <c r="Y30" s="12">
         <v>1</v>
@@ -4735,13 +4732,13 @@
         <v>1</v>
       </c>
       <c r="AF30" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG30" t="s">
         <v>65</v>
       </c>
       <c r="AI30" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK30" t="s">
         <v>54</v>
@@ -4750,21 +4747,21 @@
         <v>59</v>
       </c>
       <c r="AM30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -4779,7 +4776,7 @@
         <v>59</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J31" t="s">
         <v>56</v>
@@ -4800,7 +4797,7 @@
         <v>59</v>
       </c>
       <c r="P31" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q31" t="s">
         <v>60</v>
@@ -4842,13 +4839,13 @@
         <v>1</v>
       </c>
       <c r="AF31" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG31" t="s">
         <v>74</v>
       </c>
       <c r="AI31" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AK31" t="s">
         <v>54</v>
@@ -4857,21 +4854,21 @@
         <v>59</v>
       </c>
       <c r="AM31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>12</v>
@@ -4890,10 +4887,10 @@
         <v>56</v>
       </c>
       <c r="K32" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L32" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M32" t="s">
         <v>54</v>
@@ -4905,7 +4902,7 @@
         <v>59</v>
       </c>
       <c r="P32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q32" t="s">
         <v>60</v>
@@ -4923,7 +4920,7 @@
         <v>54</v>
       </c>
       <c r="W32" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X32" t="s">
         <v>69</v>
@@ -4965,21 +4962,21 @@
         <v>59</v>
       </c>
       <c r="AM32" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>12</v>
@@ -4994,7 +4991,7 @@
         <v>59</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s">
         <v>56</v>
@@ -5015,7 +5012,7 @@
         <v>59</v>
       </c>
       <c r="P33" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q33" t="s">
         <v>60</v>
@@ -5033,7 +5030,7 @@
         <v>54</v>
       </c>
       <c r="W33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X33" t="s">
         <v>63</v>
@@ -5083,16 +5080,16 @@
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>12</v>
@@ -5107,7 +5104,7 @@
         <v>59</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J34" t="s">
         <v>56</v>
@@ -5128,7 +5125,7 @@
         <v>59</v>
       </c>
       <c r="P34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q34" t="s">
         <v>60</v>
@@ -5146,7 +5143,7 @@
         <v>54</v>
       </c>
       <c r="W34" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X34" t="s">
         <v>77</v>
@@ -5191,21 +5188,21 @@
         <v>59</v>
       </c>
       <c r="AM34" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>12</v>
@@ -5254,10 +5251,10 @@
         <v>54</v>
       </c>
       <c r="W35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Y35" s="12">
         <v>1</v>
@@ -5299,21 +5296,21 @@
         <v>59</v>
       </c>
       <c r="AM35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>12</v>
@@ -5328,7 +5325,7 @@
         <v>59</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J36" t="s">
         <v>56</v>
@@ -5349,10 +5346,10 @@
         <v>59</v>
       </c>
       <c r="P36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q36" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R36" t="s">
         <v>71</v>
@@ -5367,7 +5364,7 @@
         <v>54</v>
       </c>
       <c r="W36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X36" t="s">
         <v>77</v>
@@ -5412,21 +5409,21 @@
         <v>59</v>
       </c>
       <c r="AM36" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
@@ -5441,7 +5438,7 @@
         <v>59</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J37" t="s">
         <v>56</v>
@@ -5462,7 +5459,7 @@
         <v>59</v>
       </c>
       <c r="P37" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q37" t="s">
         <v>60</v>
@@ -5480,7 +5477,7 @@
         <v>59</v>
       </c>
       <c r="W37" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X37" t="s">
         <v>63</v>
@@ -5527,16 +5524,16 @@
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -5551,7 +5548,7 @@
         <v>59</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J38" t="s">
         <v>56</v>
@@ -5572,10 +5569,10 @@
         <v>59</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R38" t="s">
         <v>71</v>
@@ -5590,7 +5587,7 @@
         <v>54</v>
       </c>
       <c r="W38" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X38" t="s">
         <v>69</v>
@@ -5632,24 +5629,24 @@
         <v>59</v>
       </c>
       <c r="AM38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F39" s="6">
         <v>10</v>
@@ -5680,7 +5677,7 @@
         <v>59</v>
       </c>
       <c r="P39" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q39" t="s">
         <v>60</v>
@@ -5698,7 +5695,7 @@
         <v>54</v>
       </c>
       <c r="W39" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X39" t="s">
         <v>69</v>
@@ -5743,21 +5740,21 @@
         <v>59</v>
       </c>
       <c r="AM39" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
@@ -5772,7 +5769,7 @@
         <v>59</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J40" t="s">
         <v>56</v>
@@ -5793,7 +5790,7 @@
         <v>54</v>
       </c>
       <c r="Q40" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R40" t="s">
         <v>71</v>
@@ -5808,7 +5805,7 @@
         <v>59</v>
       </c>
       <c r="W40" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X40" t="s">
         <v>77</v>
@@ -5853,21 +5850,21 @@
         <v>59</v>
       </c>
       <c r="AM40" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
@@ -5901,10 +5898,10 @@
         <v>59</v>
       </c>
       <c r="P41" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q41" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R41" t="s">
         <v>71</v>
@@ -5919,7 +5916,7 @@
         <v>59</v>
       </c>
       <c r="W41" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X41" t="s">
         <v>77</v>
@@ -5964,21 +5961,21 @@
         <v>59</v>
       </c>
       <c r="AM41" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -5993,7 +5990,7 @@
         <v>59</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J42" t="s">
         <v>56</v>
@@ -6014,10 +6011,10 @@
         <v>59</v>
       </c>
       <c r="P42" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q42" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R42" t="s">
         <v>71</v>
@@ -6074,7 +6071,7 @@
         <v>59</v>
       </c>
       <c r="AM42" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -6102,34 +6099,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -6449,7 +6446,7 @@
         <v>1.6304347826086956</v>
       </c>
       <c r="J11" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -6840,10 +6837,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -6872,10 +6869,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -6904,10 +6901,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -6936,10 +6933,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -6968,10 +6965,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -7000,10 +6997,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -7032,10 +7029,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -7064,10 +7061,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -7096,10 +7093,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -7128,10 +7125,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -7160,10 +7157,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -7192,10 +7189,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -7224,10 +7221,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -7256,10 +7253,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -7288,10 +7285,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -7320,10 +7317,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -7352,10 +7349,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -7384,10 +7381,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -7416,10 +7413,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -7468,25 +7465,25 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="D1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -7715,7 +7712,7 @@
         <v>368</v>
       </c>
       <c r="E11" s="5">
-        <v>1.1288055659963265</v>
+        <v>0</v>
       </c>
       <c r="F11" s="10">
         <v>0.39877288001502859</v>
@@ -8002,10 +7999,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C24" s="13">
         <v>45306</v>
@@ -8025,10 +8022,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C25" s="13">
         <v>45307</v>
@@ -8048,10 +8045,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C26" s="13">
         <v>45307</v>
@@ -8071,10 +8068,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C27" s="13">
         <v>45307</v>
@@ -8094,10 +8091,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C28" s="13">
         <v>45307</v>
@@ -8117,10 +8114,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C29" s="13">
         <v>45313</v>
@@ -8140,10 +8137,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C30" s="13">
         <v>45314</v>
@@ -8163,10 +8160,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C31" s="13">
         <v>45320</v>
@@ -8186,10 +8183,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C32" s="13">
         <v>45320</v>
@@ -8209,10 +8206,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C33" s="13">
         <v>45321</v>
@@ -8232,10 +8229,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C34" s="13">
         <v>45321</v>
@@ -8255,10 +8252,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C35" s="13">
         <v>45321</v>
@@ -8278,10 +8275,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C36" s="13">
         <v>45327</v>
@@ -8301,10 +8298,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C37" s="13">
         <v>45328</v>
@@ -8324,10 +8321,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C38" s="13">
         <v>45328</v>
@@ -8347,10 +8344,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C39" s="13">
         <v>45334</v>
@@ -8370,10 +8367,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C40" s="13">
         <v>45334</v>
@@ -8393,10 +8390,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C41" s="13">
         <v>45335</v>
@@ -8416,10 +8413,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C42" s="13">
         <v>45335</v>
@@ -9100,91 +9097,91 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>132</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="N1" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="O1" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="P1" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q1" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="M1" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="P1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="W1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z1" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="AA1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="X1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
@@ -9252,7 +9249,7 @@
         <v>13.599999999999994</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="W2" s="22">
         <v>0.20867383512542267</v>
@@ -9341,7 +9338,7 @@
         <v>11.899999999999995</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W3" s="22">
         <v>0.22000000000019782</v>
@@ -9430,7 +9427,7 @@
         <v>66.100000000000009</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="W4" s="22">
         <v>0.66333333333309008</v>
@@ -10053,7 +10050,7 @@
         <v>125.4</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="W11" s="22">
         <v>0.99032258064503076</v>
@@ -10142,7 +10139,7 @@
         <v>78.2</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W12" s="22">
         <v>0.50000000000009537</v>
@@ -10233,7 +10230,7 @@
         <v>180</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="W13" s="22">
         <v>3.1046953405016224</v>
@@ -10322,7 +10319,7 @@
         <v>460.00000000000006</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="W14" s="22">
         <v>2.723333333333263</v>
@@ -10413,7 +10410,7 @@
         <v>457</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="W15" s="22">
         <v>3.7199999999998568</v>
@@ -10502,7 +10499,7 @@
         <v>457.5</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W16" s="22">
         <v>1.25161290322564</v>
@@ -11661,7 +11658,7 @@
         <v>924</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="W29" s="22">
         <v>17.812903225806423</v>
@@ -11750,7 +11747,7 @@
         <v>400</v>
       </c>
       <c r="V30" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="W30" s="22">
         <v>1.4549999999997472</v>
@@ -11839,7 +11836,7 @@
         <v>877</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="W31" s="22">
         <v>27.430000000000138</v>
@@ -12284,7 +12281,7 @@
         <v>187.99999999999997</v>
       </c>
       <c r="V36" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="W36" s="22">
         <v>1.1333333333335343</v>
@@ -12373,7 +12370,7 @@
         <v>171.00000000000009</v>
       </c>
       <c r="V37" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="W37" s="22">
         <v>1.0933333333336275</v>
@@ -12462,7 +12459,7 @@
         <v>314.99999999999994</v>
       </c>
       <c r="V38" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W38" s="22">
         <v>1.4544444444442524</v>
@@ -12551,7 +12548,7 @@
         <v>913.99999999999989</v>
       </c>
       <c r="V39" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W39" s="22">
         <v>6.2937499999997648</v>
@@ -12640,7 +12637,7 @@
         <v>671.99999999999989</v>
       </c>
       <c r="V40" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="W40" s="22">
         <v>2.1166666666663523</v>
@@ -12729,7 +12726,7 @@
         <v>862.33</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="W41" s="22">
         <v>2.4999999999999369</v>
@@ -12907,7 +12904,7 @@
         <v>169.00000000000003</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="W43" s="22">
         <v>0.56333333333308622</v>
@@ -12996,7 +12993,7 @@
         <v>445.00000000000011</v>
       </c>
       <c r="V44" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="W44" s="22">
         <v>1.2199999999997619</v>
@@ -13085,7 +13082,7 @@
         <v>632.99999999999989</v>
       </c>
       <c r="V45" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="W45" s="22">
         <v>1.2000000000000455</v>
@@ -13174,7 +13171,7 @@
         <v>603.99999999999989</v>
       </c>
       <c r="V46" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="W46" s="22">
         <v>0.79666666666658636</v>
@@ -13263,7 +13260,7 @@
         <v>309.00000000000006</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="W47" s="22">
         <v>0.81333333333333258</v>
@@ -13352,7 +13349,7 @@
         <v>1748</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W48" s="22">
         <v>4.956666666666365</v>
@@ -13530,7 +13527,7 @@
         <v>1755.9999999999998</v>
       </c>
       <c r="V50" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="W50" s="22">
         <v>9.8999999999999009</v>
@@ -13619,7 +13616,7 @@
         <v>781</v>
       </c>
       <c r="V51" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W51" s="22">
         <v>1.9193548387096737</v>
@@ -13708,7 +13705,7 @@
         <v>756.99999999999989</v>
       </c>
       <c r="V52" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="W52" s="22">
         <v>1.8777777777777436</v>
@@ -13797,7 +13794,7 @@
         <v>874</v>
       </c>
       <c r="V53" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="W53" s="22">
         <v>3.9393939393938018</v>
@@ -13886,7 +13883,7 @@
         <v>1754.67</v>
       </c>
       <c r="V54" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="W54" s="22">
         <v>14.73666666666702</v>
@@ -13975,7 +13972,7 @@
         <v>1766</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="W55" s="22">
         <v>4.1111111111110032</v>
@@ -14242,7 +14239,7 @@
         <v>902.99999999999989</v>
       </c>
       <c r="V58" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="W58" s="22">
         <v>2.23111111111128</v>
@@ -14332,7 +14329,7 @@
         <v>718.33</v>
       </c>
       <c r="V59" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="W59" s="22">
         <v>1.832258064516443</v>
@@ -14421,7 +14418,7 @@
         <v>650</v>
       </c>
       <c r="V60" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="W60" s="22">
         <v>1.5031249999997165</v>
@@ -14510,7 +14507,7 @@
         <v>413.99999999999994</v>
       </c>
       <c r="V61" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="W61" s="22">
         <v>0.97509632616516206</v>
@@ -14600,7 +14597,7 @@
         <v>367.99999999999994</v>
       </c>
       <c r="V62" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W62" s="22">
         <v>0.93333333333352664</v>
@@ -14715,10 +14712,10 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C64" s="13">
         <v>45306</v>
@@ -14774,7 +14771,7 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="23" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="W64" s="22">
         <v>2.51612903225816</v>
@@ -14800,10 +14797,10 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C65" s="13">
         <v>45306</v>
@@ -14859,7 +14856,7 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W65" s="22">
         <v>19.096774193548345</v>
@@ -14885,10 +14882,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C66" s="13">
         <v>45306</v>
@@ -14970,10 +14967,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C67" s="13">
         <v>45307</v>
@@ -15031,7 +15028,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="W67" s="22">
         <v>0.55000000000025773</v>
@@ -15057,10 +15054,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C68" s="13">
         <v>45307</v>
@@ -15120,7 +15117,7 @@
         <v>436</v>
       </c>
       <c r="V68" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="W68" s="22">
         <v>0.52459999999999996</v>
@@ -15146,10 +15143,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C69" s="13">
         <v>45307</v>
@@ -15209,7 +15206,7 @@
         <v>495</v>
       </c>
       <c r="V69" s="23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="W69" s="22">
         <v>0.50000000000009537</v>
@@ -15235,10 +15232,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C70" s="13">
         <v>45307</v>
@@ -15296,7 +15293,7 @@
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="W70" s="22">
         <v>0.67096774193575381</v>
@@ -15322,10 +15319,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C71" s="13">
         <v>45307</v>
@@ -15383,7 +15380,7 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="23" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="W71" s="22">
         <v>0.643750000000054</v>
@@ -15409,10 +15406,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C72" s="13">
         <v>45307</v>
@@ -15470,7 +15467,7 @@
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="23" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="W72" s="22">
         <v>110.50000000000011</v>
@@ -15496,10 +15493,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C73" s="13">
         <v>45307</v>
@@ -15557,7 +15554,7 @@
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="W73" s="22">
         <v>0.64193548387096155</v>
@@ -15583,10 +15580,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C74" s="13">
         <v>45307</v>
@@ -15644,7 +15641,7 @@
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="W74" s="22">
         <v>79.343333333333277</v>
@@ -15670,10 +15667,10 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C75" s="13">
         <v>45307</v>
@@ -15733,7 +15730,7 @@
         <v>5439.9999999999991</v>
       </c>
       <c r="V75" s="23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="W75" s="22">
         <v>216.45199134199115</v>
@@ -15759,10 +15756,10 @@
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C76" s="13">
         <v>45307</v>
@@ -15820,7 +15817,7 @@
         <v>1016</v>
       </c>
       <c r="V76" s="23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="W76" s="22">
         <v>0.60303030303029714</v>
@@ -15846,10 +15843,10 @@
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C77" s="13">
         <v>45307</v>
@@ -15909,7 +15906,7 @@
         <v>2375</v>
       </c>
       <c r="V77" s="23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="W77" s="22">
         <v>48.758620689655217</v>
@@ -15935,10 +15932,10 @@
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C78" s="13">
         <v>45307</v>
@@ -15998,7 +15995,7 @@
         <v>685</v>
       </c>
       <c r="V78" s="23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="W78" s="22">
         <v>136.87692307692299</v>
@@ -16024,10 +16021,10 @@
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C79" s="13">
         <v>45313</v>
@@ -16087,7 +16084,7 @@
         <v>296.00000000000006</v>
       </c>
       <c r="V79" s="23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="W79" s="22">
         <v>1.1862068965516548</v>
@@ -16113,10 +16110,10 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C80" s="13">
         <v>45313</v>
@@ -16176,7 +16173,7 @@
         <v>260.00000000000006</v>
       </c>
       <c r="V80" s="23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W80" s="22">
         <v>1.2645161290320615</v>
@@ -16202,10 +16199,10 @@
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C81" s="13">
         <v>45313</v>
@@ -16265,7 +16262,7 @@
         <v>2103.3333333333335</v>
       </c>
       <c r="V81" s="23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="W81" s="22">
         <v>4.5483870967743663</v>
@@ -16291,10 +16288,10 @@
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C82" s="13">
         <v>45314</v>
@@ -16354,7 +16351,7 @@
         <v>236.00000000000003</v>
       </c>
       <c r="V82" s="23" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="W82" s="22">
         <v>0.70909090909097905</v>
@@ -16380,10 +16377,10 @@
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C83" s="13">
         <v>45314</v>
@@ -16443,7 +16440,7 @@
         <v>294.00000000000006</v>
       </c>
       <c r="V83" s="23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="W83" s="22">
         <v>0.71999999999997988</v>
@@ -16469,10 +16466,10 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C84" s="13">
         <v>45314</v>
@@ -16532,7 +16529,7 @@
         <v>4746.666666666667</v>
       </c>
       <c r="V84" s="23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="W84" s="22">
         <v>37.889841269841206</v>
@@ -16558,10 +16555,10 @@
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C85" s="13">
         <v>45320</v>
@@ -16621,7 +16618,7 @@
         <v>108.99999999999999</v>
       </c>
       <c r="V85" s="23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="W85" s="22">
         <v>0.87419354838700769</v>
@@ -16647,10 +16644,10 @@
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C86" s="13">
         <v>45320</v>
@@ -16710,7 +16707,7 @@
         <v>795.00000000000034</v>
       </c>
       <c r="V86" s="23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="W86" s="22">
         <v>10.465624999999923</v>
@@ -16736,10 +16733,10 @@
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C87" s="13">
         <v>45320</v>
@@ -16770,10 +16767,10 @@
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C88" s="13">
         <v>45320</v>
@@ -16833,7 +16830,7 @@
         <v>83</v>
       </c>
       <c r="V88" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="W88" s="22">
         <v>0.6062500000001414</v>
@@ -16859,10 +16856,10 @@
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C89" s="13">
         <v>45320</v>
@@ -16922,7 +16919,7 @@
         <v>2429.9999999999995</v>
       </c>
       <c r="V89" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="W89" s="22">
         <v>110.45000000000016</v>
@@ -16948,10 +16945,10 @@
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C90" s="13">
         <v>45320</v>
@@ -16982,10 +16979,10 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C91" s="13">
         <v>45321</v>
@@ -17045,7 +17042,7 @@
         <v>340.00000000000006</v>
       </c>
       <c r="V91" s="23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="W91" s="22">
         <v>0.75937499999989555</v>
@@ -17071,10 +17068,10 @@
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C92" s="13">
         <v>45321</v>
@@ -17134,7 +17131,7 @@
         <v>255.99999999999994</v>
       </c>
       <c r="V92" s="23" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="W92" s="22">
         <v>0.75333333333347241</v>
@@ -17160,10 +17157,10 @@
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C93" s="13">
         <v>45321</v>
@@ -17223,7 +17220,7 @@
         <v>3620</v>
       </c>
       <c r="V93" s="23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="W93" s="22">
         <v>27.085714285714094</v>
@@ -17249,10 +17246,10 @@
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C94" s="13">
         <v>45321</v>
@@ -17312,7 +17309,7 @@
         <v>671</v>
       </c>
       <c r="V94" s="23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="W94" s="22">
         <v>2.4827586206895043</v>
@@ -17338,10 +17335,10 @@
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C95" s="13">
         <v>45321</v>
@@ -17401,7 +17398,7 @@
         <v>597</v>
       </c>
       <c r="V95" s="23" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="W95" s="22">
         <v>1.0322580645162445</v>
@@ -17427,10 +17424,10 @@
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C96" s="13">
         <v>45321</v>
@@ -17490,7 +17487,7 @@
         <v>6336.666666666667</v>
       </c>
       <c r="V96" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="W96" s="22">
         <v>13.079063146997981</v>
@@ -17516,10 +17513,10 @@
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C97" s="13">
         <v>45321</v>
@@ -17579,7 +17576,7 @@
         <v>417</v>
       </c>
       <c r="V97" s="23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="W97" s="22">
         <v>1.403333333333497</v>
@@ -17605,10 +17602,10 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C98" s="13">
         <v>45321</v>
@@ -17668,7 +17665,7 @@
         <v>238.99999999999997</v>
       </c>
       <c r="V98" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="W98" s="22">
         <v>1.0333333333332935</v>
@@ -17694,10 +17691,10 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C99" s="13">
         <v>45321</v>
@@ -17783,10 +17780,10 @@
     </row>
     <row r="100" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C100" s="13">
         <v>45327</v>
@@ -17846,7 +17843,7 @@
         <v>2530</v>
       </c>
       <c r="V100" s="23" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="W100" s="22">
         <v>42.168965517241475</v>
@@ -17872,10 +17869,10 @@
     </row>
     <row r="101" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C101" s="13">
         <v>45327</v>
@@ -17933,7 +17930,7 @@
         <v>7460</v>
       </c>
       <c r="V101" s="23" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="W101" s="22">
         <v>29.444444444444507</v>
@@ -17959,10 +17956,10 @@
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C102" s="13">
         <v>45327</v>
@@ -17993,10 +17990,10 @@
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C103" s="13">
         <v>45328</v>
@@ -18056,7 +18053,7 @@
         <v>1325</v>
       </c>
       <c r="V103" s="23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="W103" s="22">
         <v>7.5764705882354004</v>
@@ -18082,10 +18079,10 @@
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C104" s="13">
         <v>45328</v>
@@ -18145,7 +18142,7 @@
         <v>960.00000000000034</v>
       </c>
       <c r="V104" s="23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="W104" s="22">
         <v>1.0531250000000991</v>
@@ -18171,10 +18168,10 @@
     </row>
     <row r="105" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C105" s="13">
         <v>45328</v>
@@ -18234,7 +18231,7 @@
         <v>5140.0000000000009</v>
       </c>
       <c r="V105" s="23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="W105" s="22">
         <v>138.51052631578958</v>
@@ -18260,10 +18257,10 @@
     </row>
     <row r="106" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C106" s="13">
         <v>45328</v>
@@ -18323,7 +18320,7 @@
         <v>2189.9999999999995</v>
       </c>
       <c r="V106" s="23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="W106" s="22">
         <v>36.022727272727131</v>
@@ -18349,10 +18346,10 @@
     </row>
     <row r="107" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C107" s="13">
         <v>45328</v>
@@ -18412,7 +18409,7 @@
         <v>7280</v>
       </c>
       <c r="V107" s="23" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="W107" s="22">
         <v>126.63333333333307</v>
@@ -18438,10 +18435,10 @@
     </row>
     <row r="108" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C108" s="13">
         <v>45328</v>
@@ -18472,10 +18469,10 @@
     </row>
     <row r="109" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C109" s="13">
         <v>45334</v>
@@ -18535,7 +18532,7 @@
         <v>95.499999999999957</v>
       </c>
       <c r="V109" s="23" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="W109" s="22">
         <v>0.59687500000005222</v>
@@ -18561,10 +18558,10 @@
     </row>
     <row r="110" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C110" s="13">
         <v>45334</v>
@@ -18624,7 +18621,7 @@
         <v>64.5</v>
       </c>
       <c r="V110" s="23" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="W110" s="22">
         <v>0.53225806451614921</v>
@@ -18650,10 +18647,10 @@
     </row>
     <row r="111" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C111" s="13">
         <v>45334</v>
@@ -18713,7 +18710,7 @@
         <v>1359.9999999999998</v>
       </c>
       <c r="V111" s="23" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="W111" s="22">
         <v>25.639999999999926</v>
@@ -18739,10 +18736,10 @@
     </row>
     <row r="112" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C112" s="13">
         <v>45334</v>
@@ -18802,7 +18799,7 @@
         <v>139</v>
       </c>
       <c r="V112" s="23" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="W112" s="22">
         <v>1.0555555555554639</v>
@@ -18828,10 +18825,10 @@
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C113" s="13">
         <v>45334</v>
@@ -18891,7 +18888,7 @@
         <v>147.5</v>
       </c>
       <c r="V113" s="23" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="W113" s="22">
         <v>0.95000000000000639</v>
@@ -18917,10 +18914,10 @@
     </row>
     <row r="114" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C114" s="13">
         <v>45334</v>
@@ -18980,7 +18977,7 @@
         <v>124.00000000000001</v>
       </c>
       <c r="V114" s="23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="W114" s="22">
         <v>0.82999999999984198</v>
@@ -19006,10 +19003,10 @@
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C115" s="13">
         <v>45335</v>
@@ -19069,7 +19066,7 @@
         <v>2770</v>
       </c>
       <c r="V115" s="23" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="W115" s="22">
         <v>8.7866666666665569</v>
@@ -19095,10 +19092,10 @@
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C116" s="13">
         <v>45335</v>
@@ -19158,7 +19155,7 @@
         <v>2929.9999999999995</v>
       </c>
       <c r="V116" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="W116" s="22">
         <v>6.4066666666666565</v>
@@ -19184,10 +19181,10 @@
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C117" s="13">
         <v>45335</v>
@@ -19247,7 +19244,7 @@
         <v>2719.9999999999995</v>
       </c>
       <c r="V117" s="23" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="W117" s="22">
         <v>14.151808278867122</v>
@@ -19273,10 +19270,10 @@
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C118" s="13">
         <v>45335</v>
@@ -19362,10 +19359,10 @@
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C119" s="13">
         <v>45335</v>
@@ -19425,7 +19422,7 @@
         <v>305.99999999999994</v>
       </c>
       <c r="V119" s="23" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="W119" s="22">
         <v>2.8219999999999619</v>
@@ -19451,10 +19448,10 @@
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C120" s="13">
         <v>45335</v>
@@ -19514,7 +19511,7 @@
         <v>1980.0000000000005</v>
       </c>
       <c r="V120" s="23" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="W120" s="22">
         <v>95.649999999999835</v>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B937407-3842-4B78-9545-E4C9F2D4B5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FD6697-2F79-4023-A55A-E77D6A3C6600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="661" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="661" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="16" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="gas" sheetId="28" r:id="rId3"/>
     <sheet name="parameters" sheetId="15" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1058,7 +1058,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1123,6 +1123,17 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="fmtMidLeft" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -11408,10 +11419,10 @@
         <v>3.3333333333333361E-2</v>
       </c>
       <c r="AB26" s="3">
-        <v>4.3333333333334112E-2</v>
+        <v>3.3333333333333361E-2</v>
       </c>
       <c r="AC26" s="3">
-        <v>1.3000000000000222</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.35">
@@ -11498,10 +11509,10 @@
         <v>6.3333333333333755E-2</v>
       </c>
       <c r="AB27" s="3">
-        <v>8.3333333333333412E-2</v>
+        <v>6.3333333333333755E-2</v>
       </c>
       <c r="AC27" s="3">
-        <v>1.3157894736842031</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.35">
@@ -11854,10 +11865,10 @@
         <v>25.2</v>
       </c>
       <c r="AB31" s="3">
-        <v>25.79999999999999</v>
+        <v>25.2</v>
       </c>
       <c r="AC31" s="3">
-        <v>1.0238095238095235</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.35">
@@ -16369,10 +16380,10 @@
         <v>8.4210526315790429E-2</v>
       </c>
       <c r="AB82" s="3">
-        <v>0.16315789473684167</v>
+        <v>8.4210526315790429E-2</v>
       </c>
       <c r="AC82" s="3">
-        <v>1.9374999999999729</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.35">
@@ -16458,10 +16469,10 @@
         <v>9.000000000000119E-2</v>
       </c>
       <c r="AB83" s="3">
-        <v>0.14500000000000068</v>
+        <v>9.000000000000119E-2</v>
       </c>
       <c r="AC83" s="3">
-        <v>1.6111111111110974</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.35">
@@ -18467,270 +18478,270 @@
       <c r="U108" s="5"/>
       <c r="V108" s="24"/>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A109" s="2" t="s">
+    <row r="109" spans="1:29" s="25" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C109" s="13">
+      <c r="C109" s="26">
         <v>45334</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E109" s="10">
-        <v>0</v>
-      </c>
-      <c r="F109" s="10">
+      <c r="E109" s="27">
+        <v>0</v>
+      </c>
+      <c r="F109" s="27">
         <v>24.6</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="23">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H109" s="5">
+      <c r="H109" s="23">
         <v>7.22</v>
       </c>
-      <c r="I109" s="10">
+      <c r="I109" s="27">
         <v>-290.2</v>
       </c>
-      <c r="J109" s="6">
+      <c r="J109" s="28">
         <v>1373</v>
       </c>
-      <c r="K109" s="16">
+      <c r="K109" s="18">
         <v>153</v>
       </c>
-      <c r="L109" s="16">
+      <c r="L109" s="18">
         <v>93.7</v>
       </c>
-      <c r="M109" s="17">
-        <v>0</v>
-      </c>
-      <c r="N109" s="17">
+      <c r="M109" s="20">
+        <v>0</v>
+      </c>
+      <c r="N109" s="20">
         <v>190.6</v>
       </c>
-      <c r="O109" s="17">
+      <c r="O109" s="20">
         <v>2.4E-2</v>
       </c>
-      <c r="P109" s="17">
+      <c r="P109" s="20">
         <v>0.373</v>
       </c>
-      <c r="Q109" s="17">
+      <c r="Q109" s="20">
         <v>154.80000000000001</v>
       </c>
-      <c r="R109" s="17">
+      <c r="R109" s="20">
         <v>190.203</v>
       </c>
-      <c r="S109" s="17">
+      <c r="S109" s="20">
         <v>16.7</v>
       </c>
-      <c r="T109" s="17">
+      <c r="T109" s="20">
         <v>17.3</v>
       </c>
-      <c r="U109" s="5">
+      <c r="U109" s="23">
         <v>95.499999999999957</v>
       </c>
       <c r="V109" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="W109" s="22">
+      <c r="W109" s="29">
         <v>0.59687500000005222</v>
       </c>
-      <c r="X109" s="22">
+      <c r="X109" s="29">
         <v>0.1343750000000199</v>
       </c>
-      <c r="Y109" s="12">
+      <c r="Y109" s="30">
         <v>22.513089005236967</v>
       </c>
-      <c r="Z109" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA109" s="3">
+      <c r="Z109" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="24">
         <v>0.10499999999999954</v>
       </c>
-      <c r="AB109" s="3">
+      <c r="AB109" s="24">
         <v>2.5000000000000022E-2</v>
       </c>
-      <c r="AC109" s="3">
+      <c r="AC109" s="24">
         <v>0.23809523809523936</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A110" s="2" t="s">
+    <row r="110" spans="1:29" s="25" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C110" s="13">
+      <c r="C110" s="26">
         <v>45334</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="D110" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E110" s="10">
+      <c r="E110" s="27">
         <v>0.7</v>
       </c>
-      <c r="F110" s="10">
+      <c r="F110" s="27">
         <v>24.550999999999998</v>
       </c>
-      <c r="G110" s="5">
+      <c r="G110" s="23">
         <v>0.13</v>
       </c>
-      <c r="H110" s="5">
+      <c r="H110" s="23">
         <v>7.12</v>
       </c>
-      <c r="I110" s="10">
+      <c r="I110" s="27">
         <v>-299.10000000000002</v>
       </c>
-      <c r="J110" s="6">
+      <c r="J110" s="28">
         <v>1444</v>
       </c>
-      <c r="K110" s="16">
+      <c r="K110" s="18">
         <v>141</v>
       </c>
-      <c r="L110" s="16">
+      <c r="L110" s="18">
         <v>88.5</v>
       </c>
-      <c r="M110" s="17">
-        <v>0</v>
-      </c>
-      <c r="N110" s="17">
+      <c r="M110" s="20">
+        <v>0</v>
+      </c>
+      <c r="N110" s="20">
         <v>308</v>
       </c>
-      <c r="O110" s="17">
+      <c r="O110" s="20">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="P110" s="17">
+      <c r="P110" s="20">
         <v>0.44900000000000001</v>
       </c>
-      <c r="Q110" s="17">
+      <c r="Q110" s="20">
         <v>159.60000000000002</v>
       </c>
-      <c r="R110" s="17">
+      <c r="R110" s="20">
         <v>307.53999999999996</v>
       </c>
-      <c r="S110" s="17">
+      <c r="S110" s="20">
         <v>16.5</v>
       </c>
-      <c r="T110" s="17">
+      <c r="T110" s="20">
         <v>17.8</v>
       </c>
-      <c r="U110" s="5">
+      <c r="U110" s="23">
         <v>64.5</v>
       </c>
       <c r="V110" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="W110" s="22">
+      <c r="W110" s="29">
         <v>0.53225806451614921</v>
       </c>
-      <c r="X110" s="22">
+      <c r="X110" s="29">
         <v>9.0322580645179992E-2</v>
       </c>
-      <c r="Y110" s="12">
+      <c r="Y110" s="30">
         <v>16.969696969699839</v>
       </c>
-      <c r="Z110" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA110" s="3">
+      <c r="Z110" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="24">
         <v>8.0000000000000904E-2</v>
       </c>
-      <c r="AB110" s="3">
+      <c r="AB110" s="24">
         <v>5.0000000000008371E-3</v>
       </c>
-      <c r="AC110" s="3">
+      <c r="AC110" s="24">
         <v>6.2500000000009756E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A111" s="2" t="s">
+    <row r="111" spans="1:29" s="25" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C111" s="13">
+      <c r="C111" s="26">
         <v>45334</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E111" s="10">
+      <c r="E111" s="27">
         <v>1.35</v>
       </c>
-      <c r="F111" s="10">
+      <c r="F111" s="27">
         <v>24.556999999999999</v>
       </c>
-      <c r="G111" s="5">
+      <c r="G111" s="23">
         <v>0.125</v>
       </c>
-      <c r="H111" s="5">
+      <c r="H111" s="23">
         <v>6.85</v>
       </c>
-      <c r="I111" s="10">
+      <c r="I111" s="27">
         <v>-284.89999999999998</v>
       </c>
-      <c r="J111" s="6">
+      <c r="J111" s="28">
         <v>1784</v>
       </c>
-      <c r="K111" s="16">
+      <c r="K111" s="18">
         <v>33700</v>
       </c>
-      <c r="L111" s="16">
+      <c r="L111" s="18">
         <v>1350</v>
       </c>
-      <c r="M111" s="17">
+      <c r="M111" s="20">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="N111" s="17">
+      <c r="N111" s="20">
         <v>145.5</v>
       </c>
-      <c r="O111" s="17">
+      <c r="O111" s="20">
         <v>0.62</v>
       </c>
-      <c r="P111" s="17">
+      <c r="P111" s="20">
         <v>5.36</v>
       </c>
-      <c r="Q111" s="17">
+      <c r="Q111" s="20">
         <v>560</v>
       </c>
-      <c r="R111" s="17">
+      <c r="R111" s="20">
         <v>139.51999999999998</v>
       </c>
-      <c r="S111" s="17">
+      <c r="S111" s="20">
         <v>3.27</v>
       </c>
-      <c r="T111" s="17">
+      <c r="T111" s="20">
         <v>13.900000000000002</v>
       </c>
-      <c r="U111" s="5">
+      <c r="U111" s="23">
         <v>1359.9999999999998</v>
       </c>
       <c r="V111" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="W111" s="22">
+      <c r="W111" s="29">
         <v>25.639999999999926</v>
       </c>
-      <c r="X111" s="22">
+      <c r="X111" s="29">
         <v>17.54400000000004</v>
       </c>
-      <c r="Y111" s="12">
+      <c r="Y111" s="30">
         <v>68.424336973479299</v>
       </c>
-      <c r="Z111" s="3">
+      <c r="Z111" s="24">
         <v>7.68</v>
       </c>
-      <c r="AA111" s="3">
+      <c r="AA111" s="24">
         <v>18.933333333333341</v>
       </c>
-      <c r="AB111" s="3">
+      <c r="AB111" s="24">
         <v>12.133333333333331</v>
       </c>
-      <c r="AC111" s="3">
+      <c r="AC111" s="24">
         <v>0.6408450704225348</v>
       </c>
     </row>

--- a/data-raw/rawdata_edited.xlsx
+++ b/data-raw/rawdata_edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawkels\Kelsey - Caetano - Linda\5_Data\01_field_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FD6697-2F79-4023-A55A-E77D6A3C6600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC7CF9A-DD2D-405D-92E3-2765F8D99260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="661" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15146,10 +15146,10 @@
         <v>1.456E-2</v>
       </c>
       <c r="AB68" s="3">
-        <v>3.456E-2</v>
+        <v>1.456E-2</v>
       </c>
       <c r="AC68" s="3">
-        <v>2.3736263736263736</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.35">
